--- a/results/ncbc_s13/norm/reference_waveforms_L.xlsx
+++ b/results/ncbc_s13/norm/reference_waveforms_L.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,625 +417,377 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>step_1</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>step_2</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>step_3</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>step_4</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>step_5</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>step_6</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>step_7</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>step_8</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>step_9</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>step_10</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>step_11</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>step_12</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>step_13</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>step_14</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>step_15</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>step_16</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>step_17</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>step_18</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>step_19</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>step_20</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>step_21</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>step_22</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>step_23</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>step_24</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>step_25</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>step_26</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>step_27</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>step_28</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>step_29</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>step_30</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>step_31</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>step_32</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>step_33</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>step_34</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>step_35</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>step_36</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>step_37</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>step_38</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>step_39</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>step_40</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>step_41</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>step_42</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>step_43</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>step_44</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>step_45</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>step_46</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>step_47</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>step_48</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>step_49</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>step_50</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>step_51</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>step_52</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>step_53</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>step_54</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>step_55</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>step_56</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>step_57</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>step_58</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>step_59</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>step_60</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>step_61</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>step_62</t>
-        </is>
-      </c>
-      <c r="BK1" s="1" t="inlineStr">
-        <is>
-          <t>step_63</t>
-        </is>
-      </c>
-      <c r="BL1" s="1" t="inlineStr">
-        <is>
-          <t>step_64</t>
-        </is>
-      </c>
-      <c r="BM1" s="1" t="inlineStr">
-        <is>
-          <t>step_65</t>
-        </is>
-      </c>
-      <c r="BN1" s="1" t="inlineStr">
-        <is>
-          <t>step_66</t>
-        </is>
-      </c>
-      <c r="BO1" s="1" t="inlineStr">
-        <is>
-          <t>step_67</t>
-        </is>
-      </c>
-      <c r="BP1" s="1" t="inlineStr">
-        <is>
-          <t>step_68</t>
-        </is>
-      </c>
-      <c r="BQ1" s="1" t="inlineStr">
-        <is>
-          <t>step_69</t>
-        </is>
-      </c>
-      <c r="BR1" s="1" t="inlineStr">
-        <is>
-          <t>step_70</t>
-        </is>
-      </c>
-      <c r="BS1" s="1" t="inlineStr">
-        <is>
-          <t>step_71</t>
-        </is>
-      </c>
-      <c r="BT1" s="1" t="inlineStr">
-        <is>
-          <t>step_72</t>
-        </is>
-      </c>
-      <c r="BU1" s="1" t="inlineStr">
-        <is>
-          <t>step_73</t>
-        </is>
-      </c>
-      <c r="BV1" s="1" t="inlineStr">
-        <is>
-          <t>step_74</t>
-        </is>
-      </c>
-      <c r="BW1" s="1" t="inlineStr">
-        <is>
-          <t>step_75</t>
-        </is>
-      </c>
-      <c r="BX1" s="1" t="inlineStr">
-        <is>
-          <t>step_76</t>
-        </is>
-      </c>
-      <c r="BY1" s="1" t="inlineStr">
-        <is>
-          <t>step_77</t>
-        </is>
-      </c>
-      <c r="BZ1" s="1" t="inlineStr">
-        <is>
-          <t>step_78</t>
-        </is>
-      </c>
-      <c r="CA1" s="1" t="inlineStr">
-        <is>
-          <t>step_79</t>
-        </is>
-      </c>
-      <c r="CB1" s="1" t="inlineStr">
-        <is>
-          <t>step_80</t>
-        </is>
-      </c>
-      <c r="CC1" s="1" t="inlineStr">
-        <is>
-          <t>step_81</t>
-        </is>
-      </c>
-      <c r="CD1" s="1" t="inlineStr">
-        <is>
-          <t>step_82</t>
-        </is>
-      </c>
-      <c r="CE1" s="1" t="inlineStr">
-        <is>
-          <t>step_83</t>
-        </is>
-      </c>
-      <c r="CF1" s="1" t="inlineStr">
-        <is>
-          <t>step_84</t>
-        </is>
-      </c>
-      <c r="CG1" s="1" t="inlineStr">
-        <is>
-          <t>step_85</t>
-        </is>
-      </c>
-      <c r="CH1" s="1" t="inlineStr">
-        <is>
-          <t>step_86</t>
-        </is>
-      </c>
-      <c r="CI1" s="1" t="inlineStr">
-        <is>
-          <t>step_87</t>
-        </is>
-      </c>
-      <c r="CJ1" s="1" t="inlineStr">
-        <is>
-          <t>step_88</t>
-        </is>
-      </c>
-      <c r="CK1" s="1" t="inlineStr">
-        <is>
-          <t>step_89</t>
-        </is>
-      </c>
-      <c r="CL1" s="1" t="inlineStr">
-        <is>
-          <t>step_90</t>
-        </is>
-      </c>
-      <c r="CM1" s="1" t="inlineStr">
-        <is>
-          <t>step_91</t>
-        </is>
-      </c>
-      <c r="CN1" s="1" t="inlineStr">
-        <is>
-          <t>step_92</t>
-        </is>
-      </c>
-      <c r="CO1" s="1" t="inlineStr">
-        <is>
-          <t>step_93</t>
-        </is>
-      </c>
-      <c r="CP1" s="1" t="inlineStr">
-        <is>
-          <t>step_94</t>
-        </is>
-      </c>
-      <c r="CQ1" s="1" t="inlineStr">
-        <is>
-          <t>step_95</t>
-        </is>
-      </c>
-      <c r="CR1" s="1" t="inlineStr">
-        <is>
-          <t>step_96</t>
-        </is>
-      </c>
-      <c r="CS1" s="1" t="inlineStr">
-        <is>
-          <t>step_97</t>
-        </is>
-      </c>
-      <c r="CT1" s="1" t="inlineStr">
-        <is>
-          <t>step_98</t>
-        </is>
-      </c>
-      <c r="CU1" s="1" t="inlineStr">
-        <is>
-          <t>step_99</t>
-        </is>
-      </c>
-      <c r="CV1" s="1" t="inlineStr">
-        <is>
-          <t>step_100</t>
-        </is>
-      </c>
-      <c r="CW1" s="1" t="inlineStr">
-        <is>
-          <t>step_101</t>
-        </is>
-      </c>
-      <c r="CX1" s="1" t="inlineStr">
-        <is>
-          <t>step_102</t>
-        </is>
-      </c>
-      <c r="CY1" s="1" t="inlineStr">
-        <is>
-          <t>step_103</t>
-        </is>
-      </c>
-      <c r="CZ1" s="1" t="inlineStr">
-        <is>
-          <t>step_104</t>
-        </is>
-      </c>
-      <c r="DA1" s="1" t="inlineStr">
-        <is>
-          <t>step_105</t>
-        </is>
-      </c>
-      <c r="DB1" s="1" t="inlineStr">
-        <is>
-          <t>step_106</t>
-        </is>
-      </c>
-      <c r="DC1" s="1" t="inlineStr">
-        <is>
-          <t>step_107</t>
-        </is>
-      </c>
-      <c r="DD1" s="1" t="inlineStr">
-        <is>
-          <t>step_108</t>
-        </is>
-      </c>
-      <c r="DE1" s="1" t="inlineStr">
-        <is>
-          <t>step_109</t>
-        </is>
-      </c>
-      <c r="DF1" s="1" t="inlineStr">
-        <is>
-          <t>step_110</t>
-        </is>
-      </c>
-      <c r="DG1" s="1" t="inlineStr">
-        <is>
-          <t>step_111</t>
-        </is>
-      </c>
-      <c r="DH1" s="1" t="inlineStr">
-        <is>
-          <t>step_112</t>
-        </is>
-      </c>
-      <c r="DI1" s="1" t="inlineStr">
-        <is>
-          <t>step_113</t>
-        </is>
-      </c>
-      <c r="DJ1" s="1" t="inlineStr">
-        <is>
-          <t>step_114</t>
-        </is>
-      </c>
-      <c r="DK1" s="1" t="inlineStr">
-        <is>
-          <t>step_115</t>
-        </is>
-      </c>
-      <c r="DL1" s="1" t="inlineStr">
-        <is>
-          <t>step_116</t>
-        </is>
-      </c>
-      <c r="DM1" s="1" t="inlineStr">
-        <is>
-          <t>step_117</t>
-        </is>
-      </c>
-      <c r="DN1" s="1" t="inlineStr">
-        <is>
-          <t>step_118</t>
-        </is>
-      </c>
-      <c r="DO1" s="1" t="inlineStr">
-        <is>
-          <t>step_119</t>
-        </is>
-      </c>
-      <c r="DP1" s="1" t="inlineStr">
-        <is>
-          <t>step_120</t>
-        </is>
-      </c>
-      <c r="DQ1" s="1" t="inlineStr">
-        <is>
-          <t>step_121</t>
-        </is>
-      </c>
-      <c r="DR1" s="1" t="inlineStr">
-        <is>
-          <t>step_122</t>
-        </is>
-      </c>
-      <c r="DS1" s="1" t="inlineStr">
-        <is>
-          <t>step_123</t>
-        </is>
-      </c>
-      <c r="DT1" s="1" t="inlineStr">
-        <is>
-          <t>step_124</t>
-        </is>
+      <c r="A1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1" t="n">
+        <v>8</v>
+      </c>
+      <c r="J1" t="n">
+        <v>9</v>
+      </c>
+      <c r="K1" t="n">
+        <v>10</v>
+      </c>
+      <c r="L1" t="n">
+        <v>11</v>
+      </c>
+      <c r="M1" t="n">
+        <v>12</v>
+      </c>
+      <c r="N1" t="n">
+        <v>13</v>
+      </c>
+      <c r="O1" t="n">
+        <v>14</v>
+      </c>
+      <c r="P1" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="n">
+        <v>16</v>
+      </c>
+      <c r="R1" t="n">
+        <v>17</v>
+      </c>
+      <c r="S1" t="n">
+        <v>18</v>
+      </c>
+      <c r="T1" t="n">
+        <v>19</v>
+      </c>
+      <c r="U1" t="n">
+        <v>20</v>
+      </c>
+      <c r="V1" t="n">
+        <v>21</v>
+      </c>
+      <c r="W1" t="n">
+        <v>22</v>
+      </c>
+      <c r="X1" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="n">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="n">
+        <v>28</v>
+      </c>
+      <c r="AD1" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE1" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF1" t="n">
+        <v>31</v>
+      </c>
+      <c r="AG1" t="n">
+        <v>32</v>
+      </c>
+      <c r="AH1" t="n">
+        <v>33</v>
+      </c>
+      <c r="AI1" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ1" t="n">
+        <v>35</v>
+      </c>
+      <c r="AK1" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL1" t="n">
+        <v>37</v>
+      </c>
+      <c r="AM1" t="n">
+        <v>38</v>
+      </c>
+      <c r="AN1" t="n">
+        <v>39</v>
+      </c>
+      <c r="AO1" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP1" t="n">
+        <v>41</v>
+      </c>
+      <c r="AQ1" t="n">
+        <v>42</v>
+      </c>
+      <c r="AR1" t="n">
+        <v>43</v>
+      </c>
+      <c r="AS1" t="n">
+        <v>44</v>
+      </c>
+      <c r="AT1" t="n">
+        <v>45</v>
+      </c>
+      <c r="AU1" t="n">
+        <v>46</v>
+      </c>
+      <c r="AV1" t="n">
+        <v>47</v>
+      </c>
+      <c r="AW1" t="n">
+        <v>48</v>
+      </c>
+      <c r="AX1" t="n">
+        <v>49</v>
+      </c>
+      <c r="AY1" t="n">
+        <v>50</v>
+      </c>
+      <c r="AZ1" t="n">
+        <v>51</v>
+      </c>
+      <c r="BA1" t="n">
+        <v>52</v>
+      </c>
+      <c r="BB1" t="n">
+        <v>53</v>
+      </c>
+      <c r="BC1" t="n">
+        <v>54</v>
+      </c>
+      <c r="BD1" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE1" t="n">
+        <v>56</v>
+      </c>
+      <c r="BF1" t="n">
+        <v>57</v>
+      </c>
+      <c r="BG1" t="n">
+        <v>58</v>
+      </c>
+      <c r="BH1" t="n">
+        <v>59</v>
+      </c>
+      <c r="BI1" t="n">
+        <v>60</v>
+      </c>
+      <c r="BJ1" t="n">
+        <v>61</v>
+      </c>
+      <c r="BK1" t="n">
+        <v>62</v>
+      </c>
+      <c r="BL1" t="n">
+        <v>63</v>
+      </c>
+      <c r="BM1" t="n">
+        <v>64</v>
+      </c>
+      <c r="BN1" t="n">
+        <v>65</v>
+      </c>
+      <c r="BO1" t="n">
+        <v>66</v>
+      </c>
+      <c r="BP1" t="n">
+        <v>67</v>
+      </c>
+      <c r="BQ1" t="n">
+        <v>68</v>
+      </c>
+      <c r="BR1" t="n">
+        <v>69</v>
+      </c>
+      <c r="BS1" t="n">
+        <v>70</v>
+      </c>
+      <c r="BT1" t="n">
+        <v>71</v>
+      </c>
+      <c r="BU1" t="n">
+        <v>72</v>
+      </c>
+      <c r="BV1" t="n">
+        <v>73</v>
+      </c>
+      <c r="BW1" t="n">
+        <v>74</v>
+      </c>
+      <c r="BX1" t="n">
+        <v>75</v>
+      </c>
+      <c r="BY1" t="n">
+        <v>76</v>
+      </c>
+      <c r="BZ1" t="n">
+        <v>77</v>
+      </c>
+      <c r="CA1" t="n">
+        <v>78</v>
+      </c>
+      <c r="CB1" t="n">
+        <v>79</v>
+      </c>
+      <c r="CC1" t="n">
+        <v>80</v>
+      </c>
+      <c r="CD1" t="n">
+        <v>81</v>
+      </c>
+      <c r="CE1" t="n">
+        <v>82</v>
+      </c>
+      <c r="CF1" t="n">
+        <v>83</v>
+      </c>
+      <c r="CG1" t="n">
+        <v>84</v>
+      </c>
+      <c r="CH1" t="n">
+        <v>85</v>
+      </c>
+      <c r="CI1" t="n">
+        <v>86</v>
+      </c>
+      <c r="CJ1" t="n">
+        <v>87</v>
+      </c>
+      <c r="CK1" t="n">
+        <v>88</v>
+      </c>
+      <c r="CL1" t="n">
+        <v>89</v>
+      </c>
+      <c r="CM1" t="n">
+        <v>90</v>
+      </c>
+      <c r="CN1" t="n">
+        <v>91</v>
+      </c>
+      <c r="CO1" t="n">
+        <v>92</v>
+      </c>
+      <c r="CP1" t="n">
+        <v>93</v>
+      </c>
+      <c r="CQ1" t="n">
+        <v>94</v>
+      </c>
+      <c r="CR1" t="n">
+        <v>95</v>
+      </c>
+      <c r="CS1" t="n">
+        <v>96</v>
+      </c>
+      <c r="CT1" t="n">
+        <v>97</v>
+      </c>
+      <c r="CU1" t="n">
+        <v>98</v>
+      </c>
+      <c r="CV1" t="n">
+        <v>99</v>
+      </c>
+      <c r="CW1" t="n">
+        <v>100</v>
+      </c>
+      <c r="CX1" t="n">
+        <v>101</v>
+      </c>
+      <c r="CY1" t="n">
+        <v>102</v>
+      </c>
+      <c r="CZ1" t="n">
+        <v>103</v>
+      </c>
+      <c r="DA1" t="n">
+        <v>104</v>
+      </c>
+      <c r="DB1" t="n">
+        <v>105</v>
+      </c>
+      <c r="DC1" t="n">
+        <v>106</v>
+      </c>
+      <c r="DD1" t="n">
+        <v>107</v>
+      </c>
+      <c r="DE1" t="n">
+        <v>108</v>
+      </c>
+      <c r="DF1" t="n">
+        <v>109</v>
+      </c>
+      <c r="DG1" t="n">
+        <v>110</v>
+      </c>
+      <c r="DH1" t="n">
+        <v>111</v>
+      </c>
+      <c r="DI1" t="n">
+        <v>112</v>
+      </c>
+      <c r="DJ1" t="n">
+        <v>113</v>
+      </c>
+      <c r="DK1" t="n">
+        <v>114</v>
+      </c>
+      <c r="DL1" t="n">
+        <v>115</v>
+      </c>
+      <c r="DM1" t="n">
+        <v>116</v>
+      </c>
+      <c r="DN1" t="n">
+        <v>117</v>
+      </c>
+      <c r="DO1" t="n">
+        <v>118</v>
+      </c>
+      <c r="DP1" t="n">
+        <v>119</v>
+      </c>
+      <c r="DQ1" t="n">
+        <v>120</v>
+      </c>
+      <c r="DR1" t="n">
+        <v>121</v>
+      </c>
+      <c r="DS1" t="n">
+        <v>122</v>
+      </c>
+      <c r="DT1" t="n">
+        <v>123</v>
       </c>
     </row>
     <row r="2">
@@ -1432,7 +1172,7 @@
         <v>0.03540311384156093</v>
       </c>
       <c r="C3" t="n">
-        <v>0.06243347764943056</v>
+        <v>0.06243347764943057</v>
       </c>
       <c r="D3" t="n">
         <v>0.02626069918617681</v>
@@ -1495,7 +1235,7 @@
         <v>0.03667942249783417</v>
       </c>
       <c r="X3" t="n">
-        <v>0.03901997778101678</v>
+        <v>0.03901997778101677</v>
       </c>
       <c r="Y3" t="n">
         <v>0.02459152847927043</v>
@@ -1612,7 +1352,7 @@
         <v>0.0408444033980943</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.04494132633688063</v>
+        <v>0.04494132633688062</v>
       </c>
       <c r="BL3" t="n">
         <v>0.05555182258837763</v>
@@ -1645,7 +1385,7 @@
         <v>0.04743742152226069</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.03267610817277768</v>
+        <v>0.03267610817277769</v>
       </c>
       <c r="BW3" t="n">
         <v>0.04132514694457963</v>
@@ -1711,10 +1451,10 @@
         <v>0.0467610320154788</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.01892355170450834</v>
+        <v>0.01892355170450835</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.05334522369686205</v>
+        <v>0.05334522369686204</v>
       </c>
       <c r="CT3" t="n">
         <v>0.04301335960676056</v>
@@ -1833,7 +1573,7 @@
         <v>0.05670037217949769</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06377988895602049</v>
+        <v>0.06377988895602051</v>
       </c>
       <c r="M4" t="n">
         <v>0.07993746791869111</v>
@@ -1848,7 +1588,7 @@
         <v>0.07476019231409835</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.06714584179709703</v>
+        <v>0.06714584179709701</v>
       </c>
       <c r="R4" t="n">
         <v>0.08652197328176472</v>
@@ -1869,13 +1609,13 @@
         <v>0.08629040085565856</v>
       </c>
       <c r="X4" t="n">
-        <v>0.08955545333955806</v>
+        <v>0.08955545333955803</v>
       </c>
       <c r="Y4" t="n">
         <v>0.07290829883039712</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.09376370174968862</v>
+        <v>0.09376370174968865</v>
       </c>
       <c r="AA4" t="n">
         <v>0.0722848344975706</v>
@@ -2001,7 +1741,7 @@
         <v>0.08068252566355064</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.06859215410469628</v>
+        <v>0.0685921541046963</v>
       </c>
       <c r="BQ4" t="n">
         <v>0.06447479717338835</v>
@@ -2010,7 +1750,7 @@
         <v>0.07793768239029418</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.09263402621663466</v>
+        <v>0.09263402621663464</v>
       </c>
       <c r="BT4" t="n">
         <v>0.06200632466626519</v>
@@ -2073,7 +1813,7 @@
         <v>0.0590749460707905</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.06862220371576133</v>
+        <v>0.06862220371576132</v>
       </c>
       <c r="CO4" t="n">
         <v>0.1155146175604249</v>
@@ -2109,7 +1849,7 @@
         <v>0.1149964920005718</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.05555202874624956</v>
+        <v>0.05555202874624957</v>
       </c>
       <c r="DA4" t="n">
         <v>0.07420207427362753</v>
@@ -2145,7 +1885,7 @@
         <v>0.1107162777659974</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.09286417691711481</v>
+        <v>0.09286417691711484</v>
       </c>
       <c r="DM4" t="n">
         <v>0.1068833855326486</v>
@@ -2315,7 +2055,7 @@
         <v>0.1627879044493431</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.1460759706134355</v>
+        <v>0.1460759706134356</v>
       </c>
       <c r="AW5" t="n">
         <v>0.1842161282688851</v>
@@ -2408,7 +2148,7 @@
         <v>0.1642361765844089</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.1460839917650043</v>
+        <v>0.1460839917650044</v>
       </c>
       <c r="CB5" t="n">
         <v>0.1965779185239988</v>
@@ -2501,7 +2241,7 @@
         <v>0.1318495446493934</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.1672178460082179</v>
+        <v>0.167217846008218</v>
       </c>
       <c r="DG5" t="n">
         <v>0.1623400127545578</v>
@@ -2614,7 +2354,7 @@
         <v>0.1931205634839185</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2699062957125844</v>
+        <v>0.2699062957125845</v>
       </c>
       <c r="X6" t="n">
         <v>0.2611146650280092</v>
@@ -2650,7 +2390,7 @@
         <v>0.2637276978194868</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.3236003300124736</v>
+        <v>0.3236003300124737</v>
       </c>
       <c r="AJ6" t="n">
         <v>0.2079808264831283</v>
@@ -2692,7 +2432,7 @@
         <v>0.2380184165013059</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.2938017240762088</v>
+        <v>0.2938017240762087</v>
       </c>
       <c r="AX6" t="n">
         <v>0.245685013808482</v>
@@ -2701,7 +2441,7 @@
         <v>0.1954608514151333</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.2327410093078761</v>
+        <v>0.2327410093078762</v>
       </c>
       <c r="BA6" t="n">
         <v>0.2280291074896777</v>
@@ -2782,7 +2522,7 @@
         <v>0.2715844101074998</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.2571401542557755</v>
+        <v>0.2571401542557756</v>
       </c>
       <c r="CB6" t="n">
         <v>0.3185443002594299</v>
@@ -2842,7 +2582,7 @@
         <v>0.356935417695331</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.3424443447324174</v>
+        <v>0.3424443447324175</v>
       </c>
       <c r="CV6" t="n">
         <v>0.3315546423404442</v>
@@ -2914,7 +2654,7 @@
         <v>0.1187337999914438</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.09689002335531001</v>
+        <v>0.09689002335531</v>
       </c>
       <c r="DT6" t="n">
         <v>0.1116518101748926</v>
@@ -2961,7 +2701,7 @@
         <v>0.3167978955154407</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3521177595370068</v>
+        <v>0.3521177595370069</v>
       </c>
       <c r="O7" t="n">
         <v>0.3678661624969584</v>
@@ -3003,7 +2743,7 @@
         <v>0.4247712969752305</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.3891159169364951</v>
+        <v>0.389115916936495</v>
       </c>
       <c r="AC7" t="n">
         <v>0.4414118472564849</v>
@@ -3093,7 +2833,7 @@
         <v>0.3910238940584823</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.4204795724974663</v>
+        <v>0.4204795724974664</v>
       </c>
       <c r="BG7" t="n">
         <v>0.3667150072076917</v>
@@ -3135,7 +2875,7 @@
         <v>0.4346467973487899</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.3730552987189159</v>
+        <v>0.3730552987189158</v>
       </c>
       <c r="BU7" t="n">
         <v>0.3580662656234691</v>
@@ -3165,13 +2905,13 @@
         <v>0.494027090963939</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.4419745454798912</v>
+        <v>0.4419745454798911</v>
       </c>
       <c r="CE7" t="n">
         <v>0.4715438156914921</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.4719158794031736</v>
+        <v>0.4719158794031735</v>
       </c>
       <c r="CG7" t="n">
         <v>0.3962199725192864</v>
@@ -3210,10 +2950,10 @@
         <v>0.3610434159767685</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.4530849188109771</v>
+        <v>0.4530849188109772</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.5011968558731208</v>
+        <v>0.5011968558731207</v>
       </c>
       <c r="CU7" t="n">
         <v>0.4829220493104086</v>
@@ -3237,7 +2977,7 @@
         <v>0.3622659307911473</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.4372950382714377</v>
+        <v>0.4372950382714378</v>
       </c>
       <c r="DC7" t="n">
         <v>0.4333341749572107</v>
@@ -3353,7 +3093,7 @@
         <v>0.5220323022294527</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4439578130828981</v>
+        <v>0.443957813082898</v>
       </c>
       <c r="U8" t="n">
         <v>0.6588588644715734</v>
@@ -3428,16 +3168,16 @@
         <v>0.4612043052020134</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.486902064443997</v>
+        <v>0.4869020644439969</v>
       </c>
       <c r="AT8" t="n">
         <v>0.3474618683042784</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.5200886371653195</v>
+        <v>0.5200886371653196</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.4775217141119171</v>
+        <v>0.477521714111917</v>
       </c>
       <c r="AW8" t="n">
         <v>0.551835869322481</v>
@@ -3479,7 +3219,7 @@
         <v>0.5826808398954981</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.5891830723220679</v>
+        <v>0.5891830723220678</v>
       </c>
       <c r="BK8" t="n">
         <v>0.4916816378264038</v>
@@ -3512,7 +3252,7 @@
         <v>0.5191491118761995</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.4769296713867527</v>
+        <v>0.4769296713867526</v>
       </c>
       <c r="BV8" t="n">
         <v>0.5156155566814347</v>
@@ -3557,7 +3297,7 @@
         <v>0.5866381339626021</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.4872117065170711</v>
+        <v>0.4872117065170712</v>
       </c>
       <c r="CK8" t="n">
         <v>0.4881687081708185</v>
@@ -3575,7 +3315,7 @@
         <v>0.6211533489114346</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.5230029660848284</v>
+        <v>0.5230029660848285</v>
       </c>
       <c r="CQ8" t="n">
         <v>0.5448320903120815</v>
@@ -3599,7 +3339,7 @@
         <v>0.5337364387362261</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.467350861116649</v>
+        <v>0.4673508611166489</v>
       </c>
       <c r="CY8" t="n">
         <v>0.6190148299894364</v>
@@ -3611,7 +3351,7 @@
         <v>0.5032858933586656</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.5711607468021633</v>
+        <v>0.5711607468021632</v>
       </c>
       <c r="DC8" t="n">
         <v>0.5681864868448102</v>
@@ -3641,7 +3381,7 @@
         <v>0.6118138632261905</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.5676841410164644</v>
+        <v>0.5676841410164645</v>
       </c>
       <c r="DM8" t="n">
         <v>0.5752637214691428</v>
@@ -3685,7 +3425,7 @@
         <v>0.2866702331043653</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6182436550156585</v>
+        <v>0.6182436550156584</v>
       </c>
       <c r="G9" t="n">
         <v>0.748035388847484</v>
@@ -3724,7 +3464,7 @@
         <v>0.6308143794425706</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6485523720886102</v>
+        <v>0.6485523720886103</v>
       </c>
       <c r="T9" t="n">
         <v>0.5673321182411386</v>
@@ -3748,7 +3488,7 @@
         <v>0.6936987704904231</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.7399142851392719</v>
+        <v>0.739914285139272</v>
       </c>
       <c r="AB9" t="n">
         <v>0.6723265046699674</v>
@@ -3760,7 +3500,7 @@
         <v>0.7397305148609397</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.7261222172996709</v>
+        <v>0.726122217299671</v>
       </c>
       <c r="AF9" t="n">
         <v>0.7463115294032147</v>
@@ -3781,13 +3521,13 @@
         <v>0.6892893991133809</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.4387427998650188</v>
+        <v>0.4387427998650187</v>
       </c>
       <c r="AM9" t="n">
         <v>0.7526988204873321</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.6532442437054509</v>
+        <v>0.653244243705451</v>
       </c>
       <c r="AO9" t="n">
         <v>0.5692213303720955</v>
@@ -3796,7 +3536,7 @@
         <v>0.6145994657922084</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.7762065038192024</v>
+        <v>0.7762065038192023</v>
       </c>
       <c r="AR9" t="n">
         <v>0.5987378305089073</v>
@@ -3898,7 +3638,7 @@
         <v>0.669009434159089</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.5786333435979404</v>
+        <v>0.5786333435979405</v>
       </c>
       <c r="BZ9" t="n">
         <v>0.6655355898579789</v>
@@ -3910,7 +3650,7 @@
         <v>0.7396664583384929</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.7774986997906966</v>
+        <v>0.7774986997906964</v>
       </c>
       <c r="CD9" t="n">
         <v>0.704670679419236</v>
@@ -3919,7 +3659,7 @@
         <v>0.7291073949977269</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.7537790667581964</v>
+        <v>0.7537790667581966</v>
       </c>
       <c r="CG9" t="n">
         <v>0.687900812539794</v>
@@ -3964,10 +3704,10 @@
         <v>0.7589781654412001</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.7561290363607935</v>
+        <v>0.7561290363607936</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.7559406868955942</v>
+        <v>0.7559406868955943</v>
       </c>
       <c r="CW9" t="n">
         <v>0.6718044832031934</v>
@@ -3988,7 +3728,7 @@
         <v>0.6993892625450462</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.6975195904664749</v>
+        <v>0.6975195904664748</v>
       </c>
       <c r="DD9" t="n">
         <v>0.8187931785273284</v>
@@ -4077,7 +3817,7 @@
         <v>0.7514892050542834</v>
       </c>
       <c r="L10" t="n">
-        <v>0.716219157705592</v>
+        <v>0.7162191577055919</v>
       </c>
       <c r="M10" t="n">
         <v>0.6659682420071734</v>
@@ -4104,7 +3844,7 @@
         <v>0.6856079661993556</v>
       </c>
       <c r="U10" t="n">
-        <v>0.9073949032993555</v>
+        <v>0.9073949032993553</v>
       </c>
       <c r="V10" t="n">
         <v>0.6500433224828622</v>
@@ -4155,7 +3895,7 @@
         <v>0.8073457739242951</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.5588496923457068</v>
+        <v>0.5588496923457069</v>
       </c>
       <c r="AM10" t="n">
         <v>0.8708718414765062</v>
@@ -4164,7 +3904,7 @@
         <v>0.7916045713816091</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.6969471313818763</v>
+        <v>0.6969471313818764</v>
       </c>
       <c r="AP10" t="n">
         <v>0.7327614225898287</v>
@@ -4236,7 +3976,7 @@
         <v>0.8396182830464096</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.8020696735754693</v>
+        <v>0.8020696735754695</v>
       </c>
       <c r="BN10" t="n">
         <v>0.8923749343352136</v>
@@ -4299,7 +4039,7 @@
         <v>0.8152504946414841</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.7841895482769209</v>
+        <v>0.784189548276921</v>
       </c>
       <c r="CI10" t="n">
         <v>0.8441168577625566</v>
@@ -4317,7 +4057,7 @@
         <v>0.6920115465922995</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.7407826044619669</v>
+        <v>0.740782604461967</v>
       </c>
       <c r="CO10" t="n">
         <v>0.8487138200270518</v>
@@ -4404,7 +4144,7 @@
         <v>0.6627788042232988</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.6490504203491434</v>
+        <v>0.6490504203491435</v>
       </c>
       <c r="DR10" t="n">
         <v>0.2025262883472242</v>
@@ -4478,7 +4218,7 @@
         <v>0.7904821090612116</v>
       </c>
       <c r="U11" t="n">
-        <v>0.9908462941231556</v>
+        <v>0.9908462941231555</v>
       </c>
       <c r="V11" t="n">
         <v>0.7515121659773901</v>
@@ -4496,7 +4236,7 @@
         <v>0.9082552747198382</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.9757730204177222</v>
+        <v>0.9757730204177221</v>
       </c>
       <c r="AB11" t="n">
         <v>0.8999493314692919</v>
@@ -4505,7 +4245,7 @@
         <v>0.9500658379961208</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.9610305999406079</v>
+        <v>0.9610305999406077</v>
       </c>
       <c r="AE11" t="n">
         <v>0.9274830892056247</v>
@@ -4649,7 +4389,7 @@
         <v>0.834596677557969</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.8783915268881263</v>
+        <v>0.8783915268881264</v>
       </c>
       <c r="CA11" t="n">
         <v>0.8983442148986158</v>
@@ -4718,7 +4458,7 @@
         <v>0.9531380621547796</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.8974412248914273</v>
+        <v>0.8974412248914274</v>
       </c>
       <c r="CX11" t="n">
         <v>0.8297252126187347</v>
@@ -4810,7 +4550,7 @@
         <v>0.8737275230422252</v>
       </c>
       <c r="G12" t="n">
-        <v>0.95741258772173</v>
+        <v>0.9574125877217299</v>
       </c>
       <c r="H12" t="n">
         <v>1.009939442858486</v>
@@ -4858,7 +4598,7 @@
         <v>0.8350459262792983</v>
       </c>
       <c r="W12" t="n">
-        <v>0.9630616326405864</v>
+        <v>0.9630616326405863</v>
       </c>
       <c r="X12" t="n">
         <v>0.8867556604421324</v>
@@ -4906,10 +4646,10 @@
         <v>0.7812306022647157</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.034254966717926</v>
+        <v>1.034254966717927</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.9834647220876466</v>
+        <v>0.9834647220876467</v>
       </c>
       <c r="AO12" t="n">
         <v>0.8975385950150274</v>
@@ -4930,7 +4670,7 @@
         <v>0.7755562422299774</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.9531296120869905</v>
+        <v>0.9531296120869908</v>
       </c>
       <c r="AV12" t="n">
         <v>0.9090140838203019</v>
@@ -4996,7 +4736,7 @@
         <v>0.9791008849471217</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.9387431567713511</v>
+        <v>0.9387431567713512</v>
       </c>
       <c r="BR12" t="n">
         <v>0.9143679177374873</v>
@@ -5053,7 +4793,7 @@
         <v>1.009168888665763</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.9537331944619651</v>
+        <v>0.953733194461965</v>
       </c>
       <c r="CK12" t="n">
         <v>0.88198046272533</v>
@@ -5095,7 +4835,7 @@
         <v>0.9774986149186859</v>
       </c>
       <c r="CX12" t="n">
-        <v>0.9152077880793997</v>
+        <v>0.9152077880793998</v>
       </c>
       <c r="CY12" t="n">
         <v>1.059703223767356</v>
@@ -5119,7 +4859,7 @@
         <v>0.9465523904825368</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.9893220442471754</v>
+        <v>0.9893220442471753</v>
       </c>
       <c r="DG12" t="n">
         <v>1.008933956923908</v>
@@ -5196,7 +4936,7 @@
         <v>1.120095351076308</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9923821497260011</v>
+        <v>0.9923821497260013</v>
       </c>
       <c r="L13" t="n">
         <v>0.957289448922918</v>
@@ -5208,7 +4948,7 @@
         <v>1.008964087058253</v>
       </c>
       <c r="O13" t="n">
-        <v>0.9608119348271383</v>
+        <v>0.9608119348271384</v>
       </c>
       <c r="P13" t="n">
         <v>1.009078011246063</v>
@@ -5235,7 +4975,7 @@
         <v>1.01252353521626</v>
       </c>
       <c r="X13" t="n">
-        <v>0.9404762404726371</v>
+        <v>0.940476240472637</v>
       </c>
       <c r="Y13" t="n">
         <v>1.077564351760705</v>
@@ -5298,7 +5038,7 @@
         <v>1.002349990046762</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.9494704511666904</v>
+        <v>0.9494704511666906</v>
       </c>
       <c r="AT13" t="n">
         <v>0.8558385301743456</v>
@@ -5307,7 +5047,7 @@
         <v>1.01670603082929</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.9673679332136891</v>
+        <v>0.967367933213689</v>
       </c>
       <c r="AW13" t="n">
         <v>1.025992038284212</v>
@@ -5322,7 +5062,7 @@
         <v>0.9474520944167742</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.9151310984489082</v>
+        <v>0.9151310984489079</v>
       </c>
       <c r="BB13" t="n">
         <v>1.087629370438292</v>
@@ -5385,7 +5125,7 @@
         <v>0.9340302090148976</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.9811723945205298</v>
+        <v>0.98117239452053</v>
       </c>
       <c r="BW13" t="n">
         <v>1.092889254518784</v>
@@ -5430,7 +5170,7 @@
         <v>1.020552963765565</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.9473897097719828</v>
+        <v>0.9473897097719826</v>
       </c>
       <c r="CL13" t="n">
         <v>1.090756914894951</v>
@@ -5609,7 +5349,7 @@
         <v>1.046006049575196</v>
       </c>
       <c r="X14" t="n">
-        <v>0.9803553533206527</v>
+        <v>0.9803553533206528</v>
       </c>
       <c r="Y14" t="n">
         <v>1.102330019525016</v>
@@ -5738,7 +5478,7 @@
         <v>1.129173287011678</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.017632170473603</v>
+        <v>1.017632170473602</v>
       </c>
       <c r="BP14" t="n">
         <v>1.066854628344074</v>
@@ -5914,7 +5654,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.3957917605322644</v>
+        <v>0.3957917605322643</v>
       </c>
       <c r="B15" t="n">
         <v>0.4702999158710057</v>
@@ -5923,7 +5663,7 @@
         <v>0.3740161878502473</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6729011984846327</v>
+        <v>0.6729011984846329</v>
       </c>
       <c r="E15" t="n">
         <v>0.6459467494133847</v>
@@ -6277,7 +6017,7 @@
         <v>0.86506874173099</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.2378689612353602</v>
+        <v>0.2378689612353603</v>
       </c>
       <c r="DS15" t="n">
         <v>0.5210909780129029</v>
@@ -6306,7 +6046,7 @@
         <v>0.9461123624077876</v>
       </c>
       <c r="G16" t="n">
-        <v>1.058465652685765</v>
+        <v>1.058465652685766</v>
       </c>
       <c r="H16" t="n">
         <v>1.072637216222088</v>
@@ -6348,7 +6088,7 @@
         <v>1.049707978033549</v>
       </c>
       <c r="U16" t="n">
-        <v>1.104930900849787</v>
+        <v>1.104930900849788</v>
       </c>
       <c r="V16" t="n">
         <v>1.003086463638058</v>
@@ -6456,7 +6196,7 @@
         <v>1.092186044284524</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.048280462195976</v>
+        <v>1.048280462195975</v>
       </c>
       <c r="BF16" t="n">
         <v>1.129426113112427</v>
@@ -6501,7 +6241,7 @@
         <v>1.072520554939705</v>
       </c>
       <c r="BT16" t="n">
-        <v>1.108611553171189</v>
+        <v>1.10861155317119</v>
       </c>
       <c r="BU16" t="n">
         <v>1.022017246660591</v>
@@ -6734,7 +6474,7 @@
         <v>1.042848905976599</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.1030309277256</v>
+        <v>1.103030927725599</v>
       </c>
       <c r="Z17" t="n">
         <v>1.111762402528524</v>
@@ -6905,7 +6645,7 @@
         <v>1.120991565391058</v>
       </c>
       <c r="CD17" t="n">
-        <v>1.083708439058835</v>
+        <v>1.083708439058834</v>
       </c>
       <c r="CE17" t="n">
         <v>1.065875656839893</v>
@@ -7063,7 +6803,7 @@
         <v>1.078470356941038</v>
       </c>
       <c r="J18" t="n">
-        <v>1.079297228614751</v>
+        <v>1.07929722861475</v>
       </c>
       <c r="K18" t="n">
         <v>1.075722028379679</v>
@@ -7087,7 +6827,7 @@
         <v>1.105538742813977</v>
       </c>
       <c r="R18" t="n">
-        <v>1.068639736359673</v>
+        <v>1.068639736359672</v>
       </c>
       <c r="S18" t="n">
         <v>1.049300353281369</v>
@@ -7177,7 +6917,7 @@
         <v>1.125219437271701</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.044121172947547</v>
+        <v>1.044121172947548</v>
       </c>
       <c r="AW18" t="n">
         <v>1.094110115391597</v>
@@ -7378,7 +7118,7 @@
         <v>1.088030114112302</v>
       </c>
       <c r="DK18" t="n">
-        <v>1.080511037503741</v>
+        <v>1.08051103750374</v>
       </c>
       <c r="DL18" t="n">
         <v>1.090462730803249</v>
@@ -7402,10 +7142,10 @@
         <v>0.2641020356464049</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.6423800993135194</v>
+        <v>0.6423800993135192</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.3981267502341888</v>
+        <v>0.3981267502341889</v>
       </c>
     </row>
     <row r="19">
@@ -7413,7 +7153,7 @@
         <v>0.3965899820879795</v>
       </c>
       <c r="B19" t="n">
-        <v>0.5251454450472856</v>
+        <v>0.5251454450472854</v>
       </c>
       <c r="C19" t="n">
         <v>0.4505460456657953</v>
@@ -7521,7 +7261,7 @@
         <v>1.097734780274959</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.069635433299878</v>
+        <v>1.069635433299877</v>
       </c>
       <c r="AM19" t="n">
         <v>1.121147622350001</v>
@@ -7557,7 +7297,7 @@
         <v>1.072829216335363</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.038325855211077</v>
+        <v>1.038325855211076</v>
       </c>
       <c r="AY19" t="n">
         <v>0.9381207618094479</v>
@@ -7596,7 +7336,7 @@
         <v>1.039702043084429</v>
       </c>
       <c r="BK19" t="n">
-        <v>1.010436128291701</v>
+        <v>1.0104361282917</v>
       </c>
       <c r="BL19" t="n">
         <v>1.064609730904088</v>
@@ -7767,7 +7507,7 @@
         <v>1.072124343588712</v>
       </c>
       <c r="DP19" t="n">
-        <v>0.9699934794292103</v>
+        <v>0.9699934794292105</v>
       </c>
       <c r="DQ19" t="n">
         <v>0.9235956552241456</v>
@@ -7776,7 +7516,7 @@
         <v>0.2775709112391526</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.6879316562760407</v>
+        <v>0.6879316562760408</v>
       </c>
       <c r="DT19" t="n">
         <v>0.4131940876111986</v>
@@ -7817,7 +7557,7 @@
         <v>1.039857980127075</v>
       </c>
       <c r="L20" t="n">
-        <v>1.034404464799465</v>
+        <v>1.034404464799466</v>
       </c>
       <c r="M20" t="n">
         <v>1.013538679353581</v>
@@ -7844,7 +7584,7 @@
         <v>1.020242952200506</v>
       </c>
       <c r="U20" t="n">
-        <v>1.028718901423432</v>
+        <v>1.028718901423433</v>
       </c>
       <c r="V20" t="n">
         <v>0.9761147694570965</v>
@@ -7934,7 +7674,7 @@
         <v>1.01118653681796</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.9163319145490076</v>
+        <v>0.9163319145490075</v>
       </c>
       <c r="AZ20" t="n">
         <v>1.018210374186013</v>
@@ -8141,7 +7881,7 @@
         <v>1.041899948469514</v>
       </c>
       <c r="DP20" t="n">
-        <v>0.9726162911690049</v>
+        <v>0.9726162911690052</v>
       </c>
       <c r="DQ20" t="n">
         <v>0.9345924974242825</v>
@@ -8164,22 +7904,22 @@
         <v>0.5792627777841831</v>
       </c>
       <c r="C21" t="n">
-        <v>0.4889975615743659</v>
+        <v>0.488997561574366</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7988581346167334</v>
+        <v>0.7988581346167335</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7926598668786383</v>
+        <v>0.7926598668786382</v>
       </c>
       <c r="F21" t="n">
         <v>0.9566215597851471</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9992759209657534</v>
+        <v>0.9992759209657532</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9662796765751224</v>
+        <v>0.9662796765751223</v>
       </c>
       <c r="I21" t="n">
         <v>0.9835453501946354</v>
@@ -8191,7 +7931,7 @@
         <v>1.006912354294473</v>
       </c>
       <c r="L21" t="n">
-        <v>1.009419261685371</v>
+        <v>1.00941926168537</v>
       </c>
       <c r="M21" t="n">
         <v>0.9782070992787493</v>
@@ -8218,7 +7958,7 @@
         <v>0.989604661787915</v>
       </c>
       <c r="U21" t="n">
-        <v>0.9920105078056279</v>
+        <v>0.9920105078056278</v>
       </c>
       <c r="V21" t="n">
         <v>0.9436479533699869</v>
@@ -8227,10 +7967,10 @@
         <v>1.004086478523397</v>
       </c>
       <c r="X21" t="n">
-        <v>0.9909160632275184</v>
+        <v>0.9909160632275182</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.9974452124250081</v>
+        <v>0.9974452124250082</v>
       </c>
       <c r="Z21" t="n">
         <v>1.009611013429872</v>
@@ -8248,7 +7988,7 @@
         <v>1.013465866905157</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.9864750396574478</v>
+        <v>0.9864750396574475</v>
       </c>
       <c r="AF21" t="n">
         <v>0.9939973268053183</v>
@@ -8311,7 +8051,7 @@
         <v>0.8880250709589816</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.9950901693969486</v>
+        <v>0.9950901693969487</v>
       </c>
       <c r="BA21" t="n">
         <v>0.9604918362985794</v>
@@ -8404,7 +8144,7 @@
         <v>0.9957815404544708</v>
       </c>
       <c r="CE21" t="n">
-        <v>0.9672380842561414</v>
+        <v>0.9672380842561413</v>
       </c>
       <c r="CF21" t="n">
         <v>1.002132539166077</v>
@@ -8476,7 +8216,7 @@
         <v>0.9908063343723501</v>
       </c>
       <c r="DC21" t="n">
-        <v>0.9993754747974223</v>
+        <v>0.9993754747974222</v>
       </c>
       <c r="DD21" t="n">
         <v>1.00937224380725</v>
@@ -8512,7 +8252,7 @@
         <v>0.997677866291908</v>
       </c>
       <c r="DO21" t="n">
-        <v>1.002840608472987</v>
+        <v>1.002840608472986</v>
       </c>
       <c r="DP21" t="n">
         <v>0.9681078967241129</v>
@@ -8532,7 +8272,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.3970659020024629</v>
+        <v>0.3970659020024628</v>
       </c>
       <c r="B22" t="n">
         <v>0.6107966293523864</v>
@@ -8547,7 +8287,7 @@
         <v>0.8163665546488306</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9359864729077576</v>
+        <v>0.9359864729077577</v>
       </c>
       <c r="G22" t="n">
         <v>0.9592592661045285</v>
@@ -8556,7 +8296,7 @@
         <v>0.9220336681835233</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9380651468431699</v>
+        <v>0.9380651468431701</v>
       </c>
       <c r="J22" t="n">
         <v>0.9090844419940214</v>
@@ -8583,10 +8323,10 @@
         <v>0.9954619467164383</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9635333094378982</v>
+        <v>0.9635333094378983</v>
       </c>
       <c r="S22" t="n">
-        <v>0.9364964299705574</v>
+        <v>0.9364964299705576</v>
       </c>
       <c r="T22" t="n">
         <v>0.9519135404016507</v>
@@ -8607,7 +8347,7 @@
         <v>0.9536993831678459</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.9645138376745718</v>
+        <v>0.964513837674572</v>
       </c>
       <c r="AA22" t="n">
         <v>0.9597990062487933</v>
@@ -8634,10 +8374,10 @@
         <v>0.9747848205743769</v>
       </c>
       <c r="AI22" t="n">
-        <v>0.9621168630467198</v>
+        <v>0.9621168630467196</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.9349750539928211</v>
+        <v>0.9349750539928213</v>
       </c>
       <c r="AK22" t="n">
         <v>1.009775673597363</v>
@@ -8703,7 +8443,7 @@
         <v>0.9184052880410347</v>
       </c>
       <c r="BF22" t="n">
-        <v>0.9935232357871595</v>
+        <v>0.9935232357871596</v>
       </c>
       <c r="BG22" t="n">
         <v>0.9719993595416833</v>
@@ -8718,13 +8458,13 @@
         <v>0.9331868848841344</v>
       </c>
       <c r="BK22" t="n">
-        <v>0.9129932368266682</v>
+        <v>0.912993236826668</v>
       </c>
       <c r="BL22" t="n">
         <v>0.9728345478753334</v>
       </c>
       <c r="BM22" t="n">
-        <v>0.9497567018882649</v>
+        <v>0.949756701888265</v>
       </c>
       <c r="BN22" t="n">
         <v>0.9875734403471399</v>
@@ -8748,7 +8488,7 @@
         <v>1.002054432652802</v>
       </c>
       <c r="BU22" t="n">
-        <v>0.9377000194823043</v>
+        <v>0.9377000194823042</v>
       </c>
       <c r="BV22" t="n">
         <v>0.9720549229490807</v>
@@ -8811,16 +8551,16 @@
         <v>0.955266178214685</v>
       </c>
       <c r="CP22" t="n">
-        <v>0.9705191018725006</v>
+        <v>0.9705191018725005</v>
       </c>
       <c r="CQ22" t="n">
-        <v>0.9740414307916738</v>
+        <v>0.9740414307916736</v>
       </c>
       <c r="CR22" t="n">
         <v>0.9973742755485772</v>
       </c>
       <c r="CS22" t="n">
-        <v>0.9366614833768526</v>
+        <v>0.9366614833768525</v>
       </c>
       <c r="CT22" t="n">
         <v>0.9504565565126859</v>
@@ -8841,7 +8581,7 @@
         <v>0.9463358506922879</v>
       </c>
       <c r="CZ22" t="n">
-        <v>0.9797322388245717</v>
+        <v>0.9797322388245718</v>
       </c>
       <c r="DA22" t="n">
         <v>0.9592385435040957</v>
@@ -8853,7 +8593,7 @@
         <v>0.9626903187474035</v>
       </c>
       <c r="DD22" t="n">
-        <v>0.9653317235542671</v>
+        <v>0.965331723554267</v>
       </c>
       <c r="DE22" t="n">
         <v>1.003427612936635</v>
@@ -8865,10 +8605,10 @@
         <v>0.9698787546466522</v>
       </c>
       <c r="DH22" t="n">
-        <v>0.9836363806851347</v>
+        <v>0.9836363806851346</v>
       </c>
       <c r="DI22" t="n">
-        <v>0.9849201866726013</v>
+        <v>0.9849201866726014</v>
       </c>
       <c r="DJ22" t="n">
         <v>0.989428413511461</v>
@@ -8880,7 +8620,7 @@
         <v>0.958139868046753</v>
       </c>
       <c r="DM22" t="n">
-        <v>0.9618136354790298</v>
+        <v>0.9618136354790299</v>
       </c>
       <c r="DN22" t="n">
         <v>0.9618536158905302</v>
@@ -8927,7 +8667,7 @@
         <v>0.9145777061729808</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8753156552140051</v>
+        <v>0.8753156552140052</v>
       </c>
       <c r="I23" t="n">
         <v>0.8904034353729388</v>
@@ -8951,7 +8691,7 @@
         <v>0.9442127642204998</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9051307212494769</v>
+        <v>0.905130721249477</v>
       </c>
       <c r="Q23" t="n">
         <v>0.9499908866441691</v>
@@ -9011,10 +8751,10 @@
         <v>0.9172528613267317</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.8943525612029523</v>
+        <v>0.8943525612029524</v>
       </c>
       <c r="AK23" t="n">
-        <v>0.9663712104027923</v>
+        <v>0.9663712104027922</v>
       </c>
       <c r="AL23" t="n">
         <v>0.9741108132569785</v>
@@ -9029,10 +8769,10 @@
         <v>0.9466680093529356</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.9135298182109375</v>
+        <v>0.9135298182109376</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.9321614043281933</v>
+        <v>0.9321614043281935</v>
       </c>
       <c r="AR23" t="n">
         <v>0.9634499141845756</v>
@@ -9104,7 +8844,7 @@
         <v>0.9416806580414885</v>
       </c>
       <c r="BO23" t="n">
-        <v>0.9124470016598881</v>
+        <v>0.9124470016598883</v>
       </c>
       <c r="BP23" t="n">
         <v>0.924530561411914</v>
@@ -9170,10 +8910,10 @@
         <v>0.9502384846165205</v>
       </c>
       <c r="CK23" t="n">
-        <v>0.920630270552969</v>
+        <v>0.9206302705529688</v>
       </c>
       <c r="CL23" t="n">
-        <v>0.9593539871618431</v>
+        <v>0.9593539871618433</v>
       </c>
       <c r="CM23" t="n">
         <v>0.9358645178971813</v>
@@ -9188,7 +8928,7 @@
         <v>0.9260997734171242</v>
       </c>
       <c r="CQ23" t="n">
-        <v>0.9245444108876936</v>
+        <v>0.9245444108876935</v>
       </c>
       <c r="CR23" t="n">
         <v>0.9509752561208824</v>
@@ -9254,10 +8994,10 @@
         <v>0.9085071787657343</v>
       </c>
       <c r="DM23" t="n">
-        <v>0.9209424231046128</v>
+        <v>0.9209424231046126</v>
       </c>
       <c r="DN23" t="n">
-        <v>0.9221822036852696</v>
+        <v>0.9221822036852695</v>
       </c>
       <c r="DO23" t="n">
         <v>0.9063197585379108</v>
@@ -9283,7 +9023,7 @@
         <v>0.3974310669794059</v>
       </c>
       <c r="B24" t="n">
-        <v>0.6632883035166286</v>
+        <v>0.6632883035166285</v>
       </c>
       <c r="C24" t="n">
         <v>0.5447267184203974</v>
@@ -9295,7 +9035,7 @@
         <v>0.8516570987393022</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8809172004826858</v>
+        <v>0.8809172004826856</v>
       </c>
       <c r="G24" t="n">
         <v>0.8681697090852942</v>
@@ -9316,7 +9056,7 @@
         <v>0.8949017547371387</v>
       </c>
       <c r="M24" t="n">
-        <v>0.8425463394608148</v>
+        <v>0.8425463394608146</v>
       </c>
       <c r="N24" t="n">
         <v>0.863550728167832</v>
@@ -9325,7 +9065,7 @@
         <v>0.9006467252294154</v>
       </c>
       <c r="P24" t="n">
-        <v>0.8579726529752942</v>
+        <v>0.8579726529752943</v>
       </c>
       <c r="Q24" t="n">
         <v>0.9022673841748755</v>
@@ -9370,7 +9110,7 @@
         <v>0.8710550353234721</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.857686302223084</v>
+        <v>0.8576863022230841</v>
       </c>
       <c r="AF24" t="n">
         <v>0.8685339105123389</v>
@@ -9430,7 +9170,7 @@
         <v>0.8383814341305607</v>
       </c>
       <c r="AY24" t="n">
-        <v>0.7849937610576329</v>
+        <v>0.7849937610576327</v>
       </c>
       <c r="AZ24" t="n">
         <v>0.8912699471104613</v>
@@ -9442,7 +9182,7 @@
         <v>0.8355092368618224</v>
       </c>
       <c r="BC24" t="n">
-        <v>0.8443385352134704</v>
+        <v>0.8443385352134705</v>
       </c>
       <c r="BD24" t="n">
         <v>0.8867774494753136</v>
@@ -9511,7 +9251,7 @@
         <v>0.9188773265466552</v>
       </c>
       <c r="BZ24" t="n">
-        <v>0.8783770509281283</v>
+        <v>0.8783770509281282</v>
       </c>
       <c r="CA24" t="n">
         <v>0.867775595076572</v>
@@ -9526,13 +9266,13 @@
         <v>0.8544935984293498</v>
       </c>
       <c r="CE24" t="n">
-        <v>0.8372944799599029</v>
+        <v>0.837294479959903</v>
       </c>
       <c r="CF24" t="n">
         <v>0.8561295275077293</v>
       </c>
       <c r="CG24" t="n">
-        <v>0.8613661819613598</v>
+        <v>0.8613661819613599</v>
       </c>
       <c r="CH24" t="n">
         <v>0.8852194721680072</v>
@@ -9559,7 +9299,7 @@
         <v>0.849937132280396</v>
       </c>
       <c r="CP24" t="n">
-        <v>0.8803396317490153</v>
+        <v>0.8803396317490154</v>
       </c>
       <c r="CQ24" t="n">
         <v>0.8739893031587354</v>
@@ -9595,7 +9335,7 @@
         <v>0.8612633125566667</v>
       </c>
       <c r="DB24" t="n">
-        <v>0.8518038128351409</v>
+        <v>0.8518038128351408</v>
       </c>
       <c r="DC24" t="n">
         <v>0.8787554591383423</v>
@@ -9607,7 +9347,7 @@
         <v>0.9012875758613302</v>
       </c>
       <c r="DF24" t="n">
-        <v>0.8704717082701461</v>
+        <v>0.8704717082701462</v>
       </c>
       <c r="DG24" t="n">
         <v>0.8743700707941118</v>
@@ -9637,7 +9377,7 @@
         <v>0.8547454303445314</v>
       </c>
       <c r="DP24" t="n">
-        <v>0.9112793049987179</v>
+        <v>0.9112793049987178</v>
       </c>
       <c r="DQ24" t="n">
         <v>0.9093460071361755</v>
@@ -9705,7 +9445,7 @@
         <v>0.8548750667401729</v>
       </c>
       <c r="R25" t="n">
-        <v>0.8408840330618509</v>
+        <v>0.840884033061851</v>
       </c>
       <c r="S25" t="n">
         <v>0.8102845599540728</v>
@@ -9720,13 +9460,13 @@
         <v>0.77153730868653</v>
       </c>
       <c r="W25" t="n">
-        <v>0.8197091210322697</v>
+        <v>0.8197091210322698</v>
       </c>
       <c r="X25" t="n">
         <v>0.8360463636137845</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.8099341311293582</v>
+        <v>0.8099341311293583</v>
       </c>
       <c r="Z25" t="n">
         <v>0.8181984175241286</v>
@@ -9738,7 +9478,7 @@
         <v>0.7996843463806295</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.8338735503424132</v>
+        <v>0.8338735503424131</v>
       </c>
       <c r="AD25" t="n">
         <v>0.825628936114567</v>
@@ -9756,7 +9496,7 @@
         <v>0.8224203768388729</v>
       </c>
       <c r="AI25" t="n">
-        <v>0.8275169002570796</v>
+        <v>0.8275169002570797</v>
       </c>
       <c r="AJ25" t="n">
         <v>0.8116264175534436</v>
@@ -9804,7 +9544,7 @@
         <v>0.7934154711689674</v>
       </c>
       <c r="AY25" t="n">
-        <v>0.7516507978448465</v>
+        <v>0.7516507978448466</v>
       </c>
       <c r="AZ25" t="n">
         <v>0.853263747856952</v>
@@ -9834,7 +9574,7 @@
         <v>0.859248877137163</v>
       </c>
       <c r="BI25" t="n">
-        <v>0.7826050627122888</v>
+        <v>0.7826050627122889</v>
       </c>
       <c r="BJ25" t="n">
         <v>0.7949650412595467</v>
@@ -9846,7 +9586,7 @@
         <v>0.8455620234763079</v>
       </c>
       <c r="BM25" t="n">
-        <v>0.8264302604533914</v>
+        <v>0.8264302604533915</v>
       </c>
       <c r="BN25" t="n">
         <v>0.8468441214641536</v>
@@ -9870,7 +9610,7 @@
         <v>0.8958755290710094</v>
       </c>
       <c r="BU25" t="n">
-        <v>0.8074829402248533</v>
+        <v>0.8074829402248532</v>
       </c>
       <c r="BV25" t="n">
         <v>0.8416317555011759</v>
@@ -9903,10 +9643,10 @@
         <v>0.795785714009558</v>
       </c>
       <c r="CF25" t="n">
-        <v>0.8089149830681658</v>
+        <v>0.8089149830681656</v>
       </c>
       <c r="CG25" t="n">
-        <v>0.8129609526464066</v>
+        <v>0.8129609526464067</v>
       </c>
       <c r="CH25" t="n">
         <v>0.8432375004531804</v>
@@ -10031,7 +9771,7 @@
         <v>0.3978163578098273</v>
       </c>
       <c r="B26" t="n">
-        <v>0.6924950015541265</v>
+        <v>0.6924950015541262</v>
       </c>
       <c r="C26" t="n">
         <v>0.5852629384262658</v>
@@ -10106,7 +9846,7 @@
         <v>0.7732029176803112</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.7767629170402237</v>
+        <v>0.7767629170402238</v>
       </c>
       <c r="AB26" t="n">
         <v>0.7660248749543075</v>
@@ -10148,7 +9888,7 @@
         <v>0.8184383335647001</v>
       </c>
       <c r="AO26" t="n">
-        <v>0.8072215332506769</v>
+        <v>0.8072215332506771</v>
       </c>
       <c r="AP26" t="n">
         <v>0.7694010094923796</v>
@@ -10226,10 +9966,10 @@
         <v>0.8022260101857938</v>
       </c>
       <c r="BO26" t="n">
-        <v>0.778941045041565</v>
+        <v>0.7789410450415648</v>
       </c>
       <c r="BP26" t="n">
-        <v>0.8015773657560724</v>
+        <v>0.8015773657560723</v>
       </c>
       <c r="BQ26" t="n">
         <v>0.8019542857206146</v>
@@ -10262,7 +10002,7 @@
         <v>0.79338295637853</v>
       </c>
       <c r="CA26" t="n">
-        <v>0.7823570869930891</v>
+        <v>0.782357086993089</v>
       </c>
       <c r="CB26" t="n">
         <v>0.76934186692183</v>
@@ -10274,7 +10014,7 @@
         <v>0.7650390640289439</v>
       </c>
       <c r="CE26" t="n">
-        <v>0.7588159468648186</v>
+        <v>0.7588159468648187</v>
       </c>
       <c r="CF26" t="n">
         <v>0.7657879314673283</v>
@@ -10292,7 +10032,7 @@
         <v>0.801042738246895</v>
       </c>
       <c r="CK26" t="n">
-        <v>0.7989008005730206</v>
+        <v>0.7989008005730208</v>
       </c>
       <c r="CL26" t="n">
         <v>0.8112369660325212</v>
@@ -10322,7 +10062,7 @@
         <v>0.7866122492094331</v>
       </c>
       <c r="CU26" t="n">
-        <v>0.7581171492744178</v>
+        <v>0.7581171492744176</v>
       </c>
       <c r="CV26" t="n">
         <v>0.7603301063378267</v>
@@ -10343,7 +10083,7 @@
         <v>0.7703049258665212</v>
       </c>
       <c r="DB26" t="n">
-        <v>0.7629048270313523</v>
+        <v>0.7629048270313522</v>
       </c>
       <c r="DC26" t="n">
         <v>0.7965926891644672</v>
@@ -10367,7 +10107,7 @@
         <v>0.7790715653244796</v>
       </c>
       <c r="DJ26" t="n">
-        <v>0.814903948172169</v>
+        <v>0.8149039481721689</v>
       </c>
       <c r="DK26" t="n">
         <v>0.7563039100738286</v>
@@ -10376,7 +10116,7 @@
         <v>0.7681201594431164</v>
       </c>
       <c r="DM26" t="n">
-        <v>0.7992463608671289</v>
+        <v>0.7992463608671286</v>
       </c>
       <c r="DN26" t="n">
         <v>0.8018988879673697</v>
@@ -10438,7 +10178,7 @@
         <v>0.7729574591464468</v>
       </c>
       <c r="M27" t="n">
-        <v>0.7263855575922982</v>
+        <v>0.7263855575922983</v>
       </c>
       <c r="N27" t="n">
         <v>0.7291481153788427</v>
@@ -10477,7 +10217,7 @@
         <v>0.729352793078372</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.7326440708597122</v>
+        <v>0.7326440708597119</v>
       </c>
       <c r="AA27" t="n">
         <v>0.7371728352946337</v>
@@ -10492,7 +10232,7 @@
         <v>0.747507483837922</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.7498824031617143</v>
+        <v>0.7498824031617144</v>
       </c>
       <c r="AF27" t="n">
         <v>0.7493387262813911</v>
@@ -10516,7 +10256,7 @@
         <v>0.7866666649687137</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.75759407104895</v>
+        <v>0.7575940710489498</v>
       </c>
       <c r="AN27" t="n">
         <v>0.7710620439884848</v>
@@ -10531,7 +10271,7 @@
         <v>0.7304790517381634</v>
       </c>
       <c r="AR27" t="n">
-        <v>0.7845774150521717</v>
+        <v>0.7845774150521719</v>
       </c>
       <c r="AS27" t="n">
         <v>0.7859545344326934</v>
@@ -10612,7 +10352,7 @@
         <v>0.7493726680975913</v>
       </c>
       <c r="BS27" t="n">
-        <v>0.7946382856042226</v>
+        <v>0.7946382856042224</v>
       </c>
       <c r="BT27" t="n">
         <v>0.8201928749304879</v>
@@ -10642,7 +10382,7 @@
         <v>0.7297997215656911</v>
       </c>
       <c r="CC27" t="n">
-        <v>0.7096908181405085</v>
+        <v>0.7096908181405083</v>
       </c>
       <c r="CD27" t="n">
         <v>0.7289054945452531</v>
@@ -10690,7 +10430,7 @@
         <v>0.7648439558615624</v>
       </c>
       <c r="CS27" t="n">
-        <v>0.7202195540829539</v>
+        <v>0.7202195540829537</v>
       </c>
       <c r="CT27" t="n">
         <v>0.7489616049234341</v>
@@ -10699,7 +10439,7 @@
         <v>0.7218128953944178</v>
       </c>
       <c r="CV27" t="n">
-        <v>0.7274869057881437</v>
+        <v>0.7274869057881436</v>
       </c>
       <c r="CW27" t="n">
         <v>0.7729990078785651</v>
@@ -10803,7 +10543,7 @@
         <v>0.6923139205776215</v>
       </c>
       <c r="J28" t="n">
-        <v>0.671159413230178</v>
+        <v>0.6711594132301778</v>
       </c>
       <c r="K28" t="n">
         <v>0.7156974447661657</v>
@@ -10818,7 +10558,7 @@
         <v>0.6955475353760664</v>
       </c>
       <c r="O28" t="n">
-        <v>0.7370616209442259</v>
+        <v>0.7370616209442261</v>
       </c>
       <c r="P28" t="n">
         <v>0.7044312640647933</v>
@@ -10830,7 +10570,7 @@
         <v>0.7331472355299082</v>
       </c>
       <c r="S28" t="n">
-        <v>0.698546151309533</v>
+        <v>0.6985461513095329</v>
       </c>
       <c r="T28" t="n">
         <v>0.7023199417193142</v>
@@ -10848,7 +10588,7 @@
         <v>0.7331148831374713</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.697800344885535</v>
+        <v>0.6978003448855349</v>
       </c>
       <c r="Z28" t="n">
         <v>0.6971631346822635</v>
@@ -10860,7 +10600,7 @@
         <v>0.7152618877397131</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.7134586245423969</v>
+        <v>0.7134586245423972</v>
       </c>
       <c r="AD28" t="n">
         <v>0.7156089344605998</v>
@@ -10878,7 +10618,7 @@
         <v>0.6970305145280606</v>
       </c>
       <c r="AI28" t="n">
-        <v>0.7135031473592728</v>
+        <v>0.7135031473592726</v>
       </c>
       <c r="AJ28" t="n">
         <v>0.7062491076830618</v>
@@ -10890,7 +10630,7 @@
         <v>0.7458745908465448</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.7181994920410186</v>
+        <v>0.7181994920410185</v>
       </c>
       <c r="AN28" t="n">
         <v>0.7288249970235264</v>
@@ -10920,13 +10660,13 @@
         <v>0.7134533114651802</v>
       </c>
       <c r="AW28" t="n">
-        <v>0.6888854341606845</v>
+        <v>0.6888854341606847</v>
       </c>
       <c r="AX28" t="n">
         <v>0.6885784631735087</v>
       </c>
       <c r="AY28" t="n">
-        <v>0.6715202455877085</v>
+        <v>0.6715202455877086</v>
       </c>
       <c r="AZ28" t="n">
         <v>0.7561047773001858</v>
@@ -10953,7 +10693,7 @@
         <v>0.7002669952885173</v>
       </c>
       <c r="BH28" t="n">
-        <v>0.7534127294030101</v>
+        <v>0.7534127294030099</v>
       </c>
       <c r="BI28" t="n">
         <v>0.6658751795606731</v>
@@ -10965,7 +10705,7 @@
         <v>0.6673088260622819</v>
       </c>
       <c r="BL28" t="n">
-        <v>0.7342298785475735</v>
+        <v>0.7342298785475737</v>
       </c>
       <c r="BM28" t="n">
         <v>0.7203104542630696</v>
@@ -10974,10 +10714,10 @@
         <v>0.7250520627891588</v>
       </c>
       <c r="BO28" t="n">
-        <v>0.709108371724404</v>
+        <v>0.7091083717244042</v>
       </c>
       <c r="BP28" t="n">
-        <v>0.7333436304254588</v>
+        <v>0.7333436304254589</v>
       </c>
       <c r="BQ28" t="n">
         <v>0.7325369432020529</v>
@@ -11022,13 +10762,13 @@
         <v>0.6993505107500655</v>
       </c>
       <c r="CE28" t="n">
-        <v>0.7022187866490175</v>
+        <v>0.7022187866490176</v>
       </c>
       <c r="CF28" t="n">
         <v>0.6952739894433114</v>
       </c>
       <c r="CG28" t="n">
-        <v>0.6909722772273157</v>
+        <v>0.6909722772273155</v>
       </c>
       <c r="CH28" t="n">
         <v>0.7334423927972821</v>
@@ -11076,7 +10816,7 @@
         <v>0.7001493108908703</v>
       </c>
       <c r="CW28" t="n">
-        <v>0.7381217401901361</v>
+        <v>0.7381217401901362</v>
       </c>
       <c r="CX28" t="n">
         <v>0.7415525426986918</v>
@@ -11094,7 +10834,7 @@
         <v>0.6925119141579198</v>
       </c>
       <c r="DC28" t="n">
-        <v>0.728750472582009</v>
+        <v>0.7287504725820091</v>
       </c>
       <c r="DD28" t="n">
         <v>0.7089386036772632</v>
@@ -11112,7 +10852,7 @@
         <v>0.7350437152830932</v>
       </c>
       <c r="DI28" t="n">
-        <v>0.6984966465828323</v>
+        <v>0.6984966465828324</v>
       </c>
       <c r="DJ28" t="n">
         <v>0.7353955741637977</v>
@@ -11171,7 +10911,7 @@
         <v>0.6768391457011285</v>
       </c>
       <c r="H29" t="n">
-        <v>0.6693667250952691</v>
+        <v>0.6693667250952688</v>
       </c>
       <c r="I29" t="n">
         <v>0.6681443524157059</v>
@@ -11201,7 +10941,7 @@
         <v>0.7005601686234844</v>
       </c>
       <c r="R29" t="n">
-        <v>0.7055534992482624</v>
+        <v>0.7055534992482626</v>
       </c>
       <c r="S29" t="n">
         <v>0.670576826925642</v>
@@ -11222,7 +10962,7 @@
         <v>0.7076986510544944</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.6719882702976951</v>
+        <v>0.671988270297695</v>
       </c>
       <c r="Z29" t="n">
         <v>0.6669507779240357</v>
@@ -11240,7 +10980,7 @@
         <v>0.6883663917260037</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.6994240275193312</v>
+        <v>0.6994240275193314</v>
       </c>
       <c r="AF29" t="n">
         <v>0.6965685002014228</v>
@@ -11300,7 +11040,7 @@
         <v>0.6653047028177119</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.6527107233758987</v>
+        <v>0.6527107233758989</v>
       </c>
       <c r="AZ29" t="n">
         <v>0.7315694210606962</v>
@@ -11312,7 +11052,7 @@
         <v>0.660596196701532</v>
       </c>
       <c r="BC29" t="n">
-        <v>0.6585603946485588</v>
+        <v>0.6585603946485589</v>
       </c>
       <c r="BD29" t="n">
         <v>0.6916312732647565</v>
@@ -11321,7 +11061,7 @@
         <v>0.6601589511270812</v>
       </c>
       <c r="BF29" t="n">
-        <v>0.7078345520314986</v>
+        <v>0.7078345520314988</v>
       </c>
       <c r="BG29" t="n">
         <v>0.6714990076232346</v>
@@ -11357,7 +11097,7 @@
         <v>0.7054045936461676</v>
       </c>
       <c r="BR29" t="n">
-        <v>0.6866301378843871</v>
+        <v>0.686630137884387</v>
       </c>
       <c r="BS29" t="n">
         <v>0.7285161260811371</v>
@@ -11375,10 +11115,10 @@
         <v>0.6622882469220552</v>
       </c>
       <c r="BX29" t="n">
-        <v>0.6854095742129822</v>
+        <v>0.6854095742129821</v>
       </c>
       <c r="BY29" t="n">
-        <v>0.7136818655621732</v>
+        <v>0.7136818655621729</v>
       </c>
       <c r="BZ29" t="n">
         <v>0.6990804726517547</v>
@@ -11393,7 +11133,7 @@
         <v>0.6554653933449301</v>
       </c>
       <c r="CD29" t="n">
-        <v>0.6759097401525495</v>
+        <v>0.6759097401525493</v>
       </c>
       <c r="CE29" t="n">
         <v>0.6827642308261198</v>
@@ -11423,7 +11163,7 @@
         <v>0.6833002279038152</v>
       </c>
       <c r="CN29" t="n">
-        <v>0.7049595222051822</v>
+        <v>0.7049595222051821</v>
       </c>
       <c r="CO29" t="n">
         <v>0.6420013758956491</v>
@@ -11432,7 +11172,7 @@
         <v>0.6900510670166944</v>
       </c>
       <c r="CQ29" t="n">
-        <v>0.6729376968128675</v>
+        <v>0.6729376968128676</v>
       </c>
       <c r="CR29" t="n">
         <v>0.6977767515002017</v>
@@ -11492,7 +11232,7 @@
         <v>0.7012371107726323</v>
       </c>
       <c r="DK29" t="n">
-        <v>0.6733705168025521</v>
+        <v>0.673370516802552</v>
       </c>
       <c r="DL29" t="n">
         <v>0.6748651713547964</v>
@@ -11507,7 +11247,7 @@
         <v>0.662571906079253</v>
       </c>
       <c r="DP29" t="n">
-        <v>0.786669916250896</v>
+        <v>0.7866699162508959</v>
       </c>
       <c r="DQ29" t="n">
         <v>0.8215920687871446</v>
@@ -11539,7 +11279,7 @@
         <v>0.8661970084800312</v>
       </c>
       <c r="F30" t="n">
-        <v>0.7512184461935028</v>
+        <v>0.751218446193503</v>
       </c>
       <c r="G30" t="n">
         <v>0.6517032911236723</v>
@@ -11569,7 +11309,7 @@
         <v>0.6795892127745934</v>
       </c>
       <c r="P30" t="n">
-        <v>0.6596514078144889</v>
+        <v>0.6596514078144888</v>
       </c>
       <c r="Q30" t="n">
         <v>0.6734476537450715</v>
@@ -11611,7 +11351,7 @@
         <v>0.6605635137870354</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.6656033495223119</v>
+        <v>0.6656033495223121</v>
       </c>
       <c r="AE30" t="n">
         <v>0.680505757547726</v>
@@ -11632,7 +11372,7 @@
         <v>0.6588444089493273</v>
       </c>
       <c r="AK30" t="n">
-        <v>0.6951554245032413</v>
+        <v>0.6951554245032414</v>
       </c>
       <c r="AL30" t="n">
         <v>0.6802870069192092</v>
@@ -11644,7 +11384,7 @@
         <v>0.6626290386436947</v>
       </c>
       <c r="AO30" t="n">
-        <v>0.6716737737577964</v>
+        <v>0.6716737737577961</v>
       </c>
       <c r="AP30" t="n">
         <v>0.6516525451758745</v>
@@ -11677,7 +11417,7 @@
         <v>0.6381167493497379</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0.7106865451070972</v>
+        <v>0.7106865451070973</v>
       </c>
       <c r="BA30" t="n">
         <v>0.6410161030875864</v>
@@ -11707,7 +11447,7 @@
         <v>0.6293015486052231</v>
       </c>
       <c r="BJ30" t="n">
-        <v>0.6435770356748359</v>
+        <v>0.6435770356748358</v>
       </c>
       <c r="BK30" t="n">
         <v>0.6293007679808735</v>
@@ -11734,7 +11474,7 @@
         <v>0.6634707936416101</v>
       </c>
       <c r="BS30" t="n">
-        <v>0.7002654788833205</v>
+        <v>0.7002654788833207</v>
       </c>
       <c r="BT30" t="n">
         <v>0.7200256981178241</v>
@@ -11743,7 +11483,7 @@
         <v>0.6640399587282737</v>
       </c>
       <c r="BV30" t="n">
-        <v>0.6656927106835634</v>
+        <v>0.6656927106835633</v>
       </c>
       <c r="BW30" t="n">
         <v>0.6389089506430548</v>
@@ -11761,13 +11501,13 @@
         <v>0.6615051608490636</v>
       </c>
       <c r="CB30" t="n">
-        <v>0.6532661126175922</v>
+        <v>0.6532661126175923</v>
       </c>
       <c r="CC30" t="n">
         <v>0.6372156690841644</v>
       </c>
       <c r="CD30" t="n">
-        <v>0.6577066040735349</v>
+        <v>0.6577066040735348</v>
       </c>
       <c r="CE30" t="n">
         <v>0.6683184286118846</v>
@@ -11803,7 +11543,7 @@
         <v>0.6197938354978193</v>
       </c>
       <c r="CP30" t="n">
-        <v>0.6668226419977078</v>
+        <v>0.6668226419977077</v>
       </c>
       <c r="CQ30" t="n">
         <v>0.6494502191825507</v>
@@ -11818,7 +11558,7 @@
         <v>0.6594363868565269</v>
       </c>
       <c r="CU30" t="n">
-        <v>0.6445984007214047</v>
+        <v>0.6445984007214048</v>
       </c>
       <c r="CV30" t="n">
         <v>0.6620057226023056</v>
@@ -11887,13 +11627,13 @@
         <v>0.8099753466652965</v>
       </c>
       <c r="DR30" t="n">
-        <v>0.4077630953335254</v>
+        <v>0.4077630953335255</v>
       </c>
       <c r="DS30" t="n">
         <v>0.8331428836110462</v>
       </c>
       <c r="DT30" t="n">
-        <v>0.8238823513063253</v>
+        <v>0.8238823513063254</v>
       </c>
     </row>
     <row r="31">
@@ -11919,7 +11659,7 @@
         <v>0.6310089933544639</v>
       </c>
       <c r="H31" t="n">
-        <v>0.6395190736134847</v>
+        <v>0.6395190736134848</v>
       </c>
       <c r="I31" t="n">
         <v>0.6335706643705667</v>
@@ -11928,7 +11668,7 @@
         <v>0.6295156783532239</v>
       </c>
       <c r="K31" t="n">
-        <v>0.6534718416977554</v>
+        <v>0.6534718416977555</v>
       </c>
       <c r="L31" t="n">
         <v>0.6764074820570253</v>
@@ -11976,7 +11716,7 @@
         <v>0.6216996212967218</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.6258513826213545</v>
+        <v>0.6258513826213544</v>
       </c>
       <c r="AB31" t="n">
         <v>0.6664450608793091</v>
@@ -11997,16 +11737,16 @@
         <v>0.6378038500034114</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.6232515172537504</v>
+        <v>0.6232515172537505</v>
       </c>
       <c r="AI31" t="n">
         <v>0.6372704037650371</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.6428543180288021</v>
+        <v>0.6428543180288022</v>
       </c>
       <c r="AK31" t="n">
-        <v>0.6718726646470153</v>
+        <v>0.6718726646470154</v>
       </c>
       <c r="AL31" t="n">
         <v>0.6556393628519618</v>
@@ -12018,7 +11758,7 @@
         <v>0.6386403466810677</v>
       </c>
       <c r="AO31" t="n">
-        <v>0.6536941707608203</v>
+        <v>0.6536941707608201</v>
       </c>
       <c r="AP31" t="n">
         <v>0.6355973323463778</v>
@@ -12042,7 +11782,7 @@
         <v>0.6526319526023751</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.6138954053989732</v>
+        <v>0.6138954053989731</v>
       </c>
       <c r="AX31" t="n">
         <v>0.6348503363033046</v>
@@ -12051,7 +11791,7 @@
         <v>0.6276004565739867</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0.6929286019971186</v>
+        <v>0.6929286019971187</v>
       </c>
       <c r="BA31" t="n">
         <v>0.6317390215027353</v>
@@ -12108,7 +11848,7 @@
         <v>0.6451127991889711</v>
       </c>
       <c r="BS31" t="n">
-        <v>0.6753261323357087</v>
+        <v>0.6753261323357089</v>
       </c>
       <c r="BT31" t="n">
         <v>0.692478733011044</v>
@@ -12290,7 +12030,7 @@
         <v>0.7369156313575232</v>
       </c>
       <c r="G32" t="n">
-        <v>0.6145754380382153</v>
+        <v>0.6145754380382152</v>
       </c>
       <c r="H32" t="n">
         <v>0.6301772730159955</v>
@@ -12305,7 +12045,7 @@
         <v>0.642568278606208</v>
       </c>
       <c r="L32" t="n">
-        <v>0.6616074634390159</v>
+        <v>0.6616074634390157</v>
       </c>
       <c r="M32" t="n">
         <v>0.6424869072005671</v>
@@ -12344,13 +12084,13 @@
         <v>0.6557256063259245</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.6226431241629795</v>
+        <v>0.6226431241629796</v>
       </c>
       <c r="Z32" t="n">
         <v>0.6060694933815964</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.6108705707062506</v>
+        <v>0.6108705707062507</v>
       </c>
       <c r="AB32" t="n">
         <v>0.6543039116017429</v>
@@ -12368,7 +12108,7 @@
         <v>0.6543974859048699</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.6282984489728314</v>
+        <v>0.6282984489728315</v>
       </c>
       <c r="AH32" t="n">
         <v>0.6091020672921686</v>
@@ -12425,7 +12165,7 @@
         <v>0.6207035741838723</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0.6778211769020499</v>
+        <v>0.6778211769020498</v>
       </c>
       <c r="BA32" t="n">
         <v>0.6258688703734501</v>
@@ -12446,7 +12186,7 @@
         <v>0.6378822835449889</v>
       </c>
       <c r="BG32" t="n">
-        <v>0.6230265791586346</v>
+        <v>0.6230265791586347</v>
       </c>
       <c r="BH32" t="n">
         <v>0.6588121751867734</v>
@@ -12557,7 +12297,7 @@
         <v>0.6181167561283174</v>
       </c>
       <c r="CR32" t="n">
-        <v>0.6337311620472443</v>
+        <v>0.6337311620472444</v>
       </c>
       <c r="CS32" t="n">
         <v>0.6308387720475169</v>
@@ -12602,7 +12342,7 @@
         <v>0.6178764728604995</v>
       </c>
       <c r="DG32" t="n">
-        <v>0.6281501929302885</v>
+        <v>0.6281501929302884</v>
       </c>
       <c r="DH32" t="n">
         <v>0.6520388127610113</v>
@@ -12629,10 +12369,10 @@
         <v>0.6233905400973128</v>
       </c>
       <c r="DP32" t="n">
-        <v>0.7459502667447394</v>
+        <v>0.7459502667447396</v>
       </c>
       <c r="DQ32" t="n">
-        <v>0.7925488859354056</v>
+        <v>0.7925488859354055</v>
       </c>
       <c r="DR32" t="n">
         <v>0.4170513211296294</v>
@@ -12691,7 +12431,7 @@
         <v>0.6237298519973962</v>
       </c>
       <c r="P33" t="n">
-        <v>0.6218358742458616</v>
+        <v>0.6218358742458615</v>
       </c>
       <c r="Q33" t="n">
         <v>0.6227619034892287</v>
@@ -12700,7 +12440,7 @@
         <v>0.6377526092404707</v>
       </c>
       <c r="S33" t="n">
-        <v>0.614649456978858</v>
+        <v>0.6146494569788579</v>
       </c>
       <c r="T33" t="n">
         <v>0.6278868573105713</v>
@@ -12766,7 +12506,7 @@
         <v>0.6068100317331733</v>
       </c>
       <c r="AO33" t="n">
-        <v>0.6325192740233193</v>
+        <v>0.6325192740233192</v>
       </c>
       <c r="AP33" t="n">
         <v>0.6149570676633715</v>
@@ -12802,7 +12542,7 @@
         <v>0.6650492699357612</v>
       </c>
       <c r="BA33" t="n">
-        <v>0.6221282789457144</v>
+        <v>0.6221282789457145</v>
       </c>
       <c r="BB33" t="n">
         <v>0.6083527756099407</v>
@@ -12820,7 +12560,7 @@
         <v>0.6238083989948973</v>
       </c>
       <c r="BG33" t="n">
-        <v>0.6179837303865429</v>
+        <v>0.6179837303865428</v>
       </c>
       <c r="BH33" t="n">
         <v>0.6438116043653965</v>
@@ -12832,7 +12572,7 @@
         <v>0.6148166360110852</v>
       </c>
       <c r="BK33" t="n">
-        <v>0.6162745900358535</v>
+        <v>0.6162745900358536</v>
       </c>
       <c r="BL33" t="n">
         <v>0.6283867150719864</v>
@@ -12919,19 +12659,19 @@
         <v>0.6217357061469626</v>
       </c>
       <c r="CN33" t="n">
-        <v>0.6341534911939022</v>
+        <v>0.6341534911939023</v>
       </c>
       <c r="CO33" t="n">
         <v>0.5897284255356579</v>
       </c>
       <c r="CP33" t="n">
-        <v>0.6244786840330706</v>
+        <v>0.6244786840330705</v>
       </c>
       <c r="CQ33" t="n">
         <v>0.6087738033062199</v>
       </c>
       <c r="CR33" t="n">
-        <v>0.6201238291593828</v>
+        <v>0.6201238291593829</v>
       </c>
       <c r="CS33" t="n">
         <v>0.6260256948049325</v>
@@ -13015,7 +12755,7 @@
         <v>0.7960862658714074</v>
       </c>
       <c r="DT33" t="n">
-        <v>0.9337832564079436</v>
+        <v>0.9337832564079437</v>
       </c>
     </row>
     <row r="34">
@@ -13029,7 +12769,7 @@
         <v>0.8019170042810664</v>
       </c>
       <c r="D34" t="n">
-        <v>0.8187138375547914</v>
+        <v>0.8187138375547915</v>
       </c>
       <c r="E34" t="n">
         <v>0.8292364759661354</v>
@@ -13056,7 +12796,7 @@
         <v>0.6385001445395398</v>
       </c>
       <c r="M34" t="n">
-        <v>0.6337222981951661</v>
+        <v>0.633722298195166</v>
       </c>
       <c r="N34" t="n">
         <v>0.6021654316269376</v>
@@ -13128,7 +12868,7 @@
         <v>0.619800714889844</v>
       </c>
       <c r="AK34" t="n">
-        <v>0.6185089478960974</v>
+        <v>0.6185089478960976</v>
       </c>
       <c r="AL34" t="n">
         <v>0.6134944316149336</v>
@@ -13158,7 +12898,7 @@
         <v>0.65087905181677</v>
       </c>
       <c r="AU34" t="n">
-        <v>0.6193120931568041</v>
+        <v>0.6193120931568042</v>
       </c>
       <c r="AV34" t="n">
         <v>0.6276623422994103</v>
@@ -13182,7 +12922,7 @@
         <v>0.6059053889759336</v>
       </c>
       <c r="BC34" t="n">
-        <v>0.6098380272866247</v>
+        <v>0.6098380272866248</v>
       </c>
       <c r="BD34" t="n">
         <v>0.6193529422329703</v>
@@ -13209,7 +12949,7 @@
         <v>0.6201750651924388</v>
       </c>
       <c r="BL34" t="n">
-        <v>0.6182247494210802</v>
+        <v>0.6182247494210801</v>
       </c>
       <c r="BM34" t="n">
         <v>0.6233237963698345</v>
@@ -13230,7 +12970,7 @@
         <v>0.6139536576867434</v>
       </c>
       <c r="BS34" t="n">
-        <v>0.6198970924473211</v>
+        <v>0.6198970924473209</v>
       </c>
       <c r="BT34" t="n">
         <v>0.6314927298447011</v>
@@ -13305,7 +13045,7 @@
         <v>0.6028527714176601</v>
       </c>
       <c r="CR34" t="n">
-        <v>0.609629701857728</v>
+        <v>0.6096297018577281</v>
       </c>
       <c r="CS34" t="n">
         <v>0.6240661064088783</v>
@@ -13320,13 +13060,13 @@
         <v>0.6321693788044926</v>
       </c>
       <c r="CW34" t="n">
-        <v>0.6312861310734034</v>
+        <v>0.6312861310734035</v>
       </c>
       <c r="CX34" t="n">
         <v>0.6235539080703077</v>
       </c>
       <c r="CY34" t="n">
-        <v>0.6203100450091712</v>
+        <v>0.6203100450091711</v>
       </c>
       <c r="CZ34" t="n">
         <v>0.616896662128215</v>
@@ -13353,7 +13093,7 @@
         <v>0.6087461427245126</v>
       </c>
       <c r="DH34" t="n">
-        <v>0.6317282225126631</v>
+        <v>0.6317282225126633</v>
       </c>
       <c r="DI34" t="n">
         <v>0.5908501853653145</v>
@@ -13409,7 +13149,7 @@
         <v>0.8188959240300135</v>
       </c>
       <c r="F35" t="n">
-        <v>0.7287886104681899</v>
+        <v>0.7287886104681897</v>
       </c>
       <c r="G35" t="n">
         <v>0.5904258376132531</v>
@@ -13433,7 +13173,7 @@
         <v>0.6320890796836273</v>
       </c>
       <c r="N35" t="n">
-        <v>0.6034495303190163</v>
+        <v>0.6034495303190164</v>
       </c>
       <c r="O35" t="n">
         <v>0.6054362146211179</v>
@@ -13511,7 +13251,7 @@
         <v>0.5850309973240144</v>
       </c>
       <c r="AN35" t="n">
-        <v>0.5937302444034157</v>
+        <v>0.5937302444034158</v>
       </c>
       <c r="AO35" t="n">
         <v>0.6244749212730282</v>
@@ -13547,7 +13287,7 @@
         <v>0.6147260791808412</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0.6463830237397455</v>
+        <v>0.6463830237397457</v>
       </c>
       <c r="BA35" t="n">
         <v>0.6191670853084403</v>
@@ -13661,7 +13401,7 @@
         <v>0.6382918088323511</v>
       </c>
       <c r="CL35" t="n">
-        <v>0.5932574406079035</v>
+        <v>0.5932574406079034</v>
       </c>
       <c r="CM35" t="n">
         <v>0.6210630866220056</v>
@@ -13679,7 +13419,7 @@
         <v>0.6002560813293727</v>
       </c>
       <c r="CR35" t="n">
-        <v>0.6019490900804886</v>
+        <v>0.6019490900804885</v>
       </c>
       <c r="CS35" t="n">
         <v>0.624981963240184</v>
@@ -13760,7 +13500,7 @@
         <v>0.4266151038282575</v>
       </c>
       <c r="DS35" t="n">
-        <v>0.7655779911685388</v>
+        <v>0.7655779911685389</v>
       </c>
       <c r="DT35" t="n">
         <v>0.9759567218058666</v>
@@ -13780,7 +13520,7 @@
         <v>0.7962980567445723</v>
       </c>
       <c r="E36" t="n">
-        <v>0.808690317734639</v>
+        <v>0.8086903177346392</v>
       </c>
       <c r="F36" t="n">
         <v>0.7272983839329578</v>
@@ -13804,7 +13544,7 @@
         <v>0.6256747269860999</v>
       </c>
       <c r="M36" t="n">
-        <v>0.6323589385630757</v>
+        <v>0.6323589385630758</v>
       </c>
       <c r="N36" t="n">
         <v>0.6089698542011798</v>
@@ -13843,13 +13583,13 @@
         <v>0.6026591369301618</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.5877881906542619</v>
+        <v>0.587788190654262</v>
       </c>
       <c r="AA36" t="n">
         <v>0.5902514407718967</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.629413761227311</v>
+        <v>0.6294137612273111</v>
       </c>
       <c r="AC36" t="n">
         <v>0.6099946980984664</v>
@@ -13864,10 +13604,10 @@
         <v>0.6323388986091504</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.6178962556869882</v>
+        <v>0.6178962556869884</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.5968391855814364</v>
+        <v>0.5968391855814366</v>
       </c>
       <c r="AI36" t="n">
         <v>0.5952532998493832</v>
@@ -13906,7 +13646,7 @@
         <v>0.6333874547694344</v>
       </c>
       <c r="AU36" t="n">
-        <v>0.6049254410500196</v>
+        <v>0.6049254410500194</v>
       </c>
       <c r="AV36" t="n">
         <v>0.6259754714989558</v>
@@ -13966,7 +13706,7 @@
         <v>0.6035694661025601</v>
       </c>
       <c r="BO36" t="n">
-        <v>0.6281443944113918</v>
+        <v>0.6281443944113919</v>
       </c>
       <c r="BP36" t="n">
         <v>0.6343106067027218</v>
@@ -13978,7 +13718,7 @@
         <v>0.6134008706463088</v>
       </c>
       <c r="BS36" t="n">
-        <v>0.5994110452111091</v>
+        <v>0.5994110452111092</v>
       </c>
       <c r="BT36" t="n">
         <v>0.6097655278357511</v>
@@ -13990,7 +13730,7 @@
         <v>0.6111494133453128</v>
       </c>
       <c r="BW36" t="n">
-        <v>0.6013435301091624</v>
+        <v>0.6013435301091625</v>
       </c>
       <c r="BX36" t="n">
         <v>0.620540611068072</v>
@@ -14086,7 +13826,7 @@
         <v>0.6085714144654349</v>
       </c>
       <c r="DC36" t="n">
-        <v>0.614917559646234</v>
+        <v>0.6149175596462341</v>
       </c>
       <c r="DD36" t="n">
         <v>0.60269867047584</v>
@@ -14113,7 +13853,7 @@
         <v>0.6349516607682772</v>
       </c>
       <c r="DL36" t="n">
-        <v>0.631331854586482</v>
+        <v>0.6313318545864821</v>
       </c>
       <c r="DM36" t="n">
         <v>0.6179978176710565</v>
@@ -14151,7 +13891,7 @@
         <v>0.8372171068814586</v>
       </c>
       <c r="D37" t="n">
-        <v>0.7874577320561071</v>
+        <v>0.7874577320561074</v>
       </c>
       <c r="E37" t="n">
         <v>0.7988967837408949</v>
@@ -14166,7 +13906,7 @@
         <v>0.6275218608693395</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6074635152679587</v>
+        <v>0.6074635152679586</v>
       </c>
       <c r="J37" t="n">
         <v>0.6506137885699264</v>
@@ -14181,7 +13921,7 @@
         <v>0.634974942420506</v>
       </c>
       <c r="N37" t="n">
-        <v>0.6180239226836446</v>
+        <v>0.6180239226836445</v>
       </c>
       <c r="O37" t="n">
         <v>0.6055401848096301</v>
@@ -14244,13 +13984,13 @@
         <v>0.6035644975151336</v>
       </c>
       <c r="AI37" t="n">
-        <v>0.6001155043332123</v>
+        <v>0.6001155043332124</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.6240540704678723</v>
+        <v>0.6240540704678722</v>
       </c>
       <c r="AK37" t="n">
-        <v>0.5982063141539925</v>
+        <v>0.5982063141539926</v>
       </c>
       <c r="AL37" t="n">
         <v>0.6127123558520455</v>
@@ -14262,7 +14002,7 @@
         <v>0.5988095767509802</v>
       </c>
       <c r="AO37" t="n">
-        <v>0.6260435847028714</v>
+        <v>0.6260435847028715</v>
       </c>
       <c r="AP37" t="n">
         <v>0.6155413686770511</v>
@@ -14301,7 +14041,7 @@
         <v>0.6245155303877343</v>
       </c>
       <c r="BB37" t="n">
-        <v>0.6190093865775521</v>
+        <v>0.619009386577552</v>
       </c>
       <c r="BC37" t="n">
         <v>0.6218777149105232</v>
@@ -14325,7 +14065,7 @@
         <v>0.64080654705664</v>
       </c>
       <c r="BJ37" t="n">
-        <v>0.627687935865989</v>
+        <v>0.6276879358659891</v>
       </c>
       <c r="BK37" t="n">
         <v>0.642515085562364</v>
@@ -14472,7 +14212,7 @@
         <v>0.6130312071686539</v>
       </c>
       <c r="DG37" t="n">
-        <v>0.6066904783556227</v>
+        <v>0.6066904783556228</v>
       </c>
       <c r="DH37" t="n">
         <v>0.6216853831231463</v>
@@ -14543,7 +14283,7 @@
         <v>0.61681106943065</v>
       </c>
       <c r="J38" t="n">
-        <v>0.6642899805609833</v>
+        <v>0.6642899805609834</v>
       </c>
       <c r="K38" t="n">
         <v>0.6414967851770664</v>
@@ -14642,7 +14382,7 @@
         <v>0.6247561533920989</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.6262063978257906</v>
+        <v>0.6262063978257907</v>
       </c>
       <c r="AR38" t="n">
         <v>0.6139830872011811</v>
@@ -14660,7 +14400,7 @@
         <v>0.6365944229514633</v>
       </c>
       <c r="AW38" t="n">
-        <v>0.6066033543489083</v>
+        <v>0.6066033543489084</v>
       </c>
       <c r="AX38" t="n">
         <v>0.6377824850602744</v>
@@ -14714,7 +14454,7 @@
         <v>0.6167128809426554</v>
       </c>
       <c r="BO38" t="n">
-        <v>0.6383643300560451</v>
+        <v>0.6383643300560452</v>
       </c>
       <c r="BP38" t="n">
         <v>0.6392932903593727</v>
@@ -14741,7 +14481,7 @@
         <v>0.6255539733038327</v>
       </c>
       <c r="BX38" t="n">
-        <v>0.6395669139961287</v>
+        <v>0.6395669139961286</v>
       </c>
       <c r="BY38" t="n">
         <v>0.6134232883989096</v>
@@ -14768,7 +14508,7 @@
         <v>0.6457339231492989</v>
       </c>
       <c r="CG38" t="n">
-        <v>0.6421523612114265</v>
+        <v>0.6421523612114266</v>
       </c>
       <c r="CH38" t="n">
         <v>0.6311497344637778</v>
@@ -14789,7 +14529,7 @@
         <v>0.6386193322019788</v>
       </c>
       <c r="CN38" t="n">
-        <v>0.6249089298930864</v>
+        <v>0.6249089298930863</v>
       </c>
       <c r="CO38" t="n">
         <v>0.6103853300229097</v>
@@ -14798,7 +14538,7 @@
         <v>0.6227893482210537</v>
       </c>
       <c r="CQ38" t="n">
-        <v>0.6157375039531738</v>
+        <v>0.6157375039531737</v>
       </c>
       <c r="CR38" t="n">
         <v>0.59675693608864</v>
@@ -14849,7 +14589,7 @@
         <v>0.6137249377547983</v>
       </c>
       <c r="DH38" t="n">
-        <v>0.6244063586858148</v>
+        <v>0.624406358685815</v>
       </c>
       <c r="DI38" t="n">
         <v>0.6151844255832629</v>
@@ -14861,7 +14601,7 @@
         <v>0.6526003976880835</v>
       </c>
       <c r="DL38" t="n">
-        <v>0.6490549250155644</v>
+        <v>0.6490549250155643</v>
       </c>
       <c r="DM38" t="n">
         <v>0.6196618971238909</v>
@@ -14876,7 +14616,7 @@
         <v>0.7175057856525995</v>
       </c>
       <c r="DQ38" t="n">
-        <v>0.7580015010194684</v>
+        <v>0.7580015010194683</v>
       </c>
       <c r="DR38" t="n">
         <v>0.4388273958790163</v>
@@ -14911,7 +14651,7 @@
         <v>0.6356788243299202</v>
       </c>
       <c r="H39" t="n">
-        <v>0.6455790089956585</v>
+        <v>0.6455790089956586</v>
       </c>
       <c r="I39" t="n">
         <v>0.6307563636809611</v>
@@ -14950,7 +14690,7 @@
         <v>0.6521088923696068</v>
       </c>
       <c r="U39" t="n">
-        <v>0.6486447683522767</v>
+        <v>0.6486447683522766</v>
       </c>
       <c r="V39" t="n">
         <v>0.6519680232387876</v>
@@ -14965,7 +14705,7 @@
         <v>0.6172495098139065</v>
       </c>
       <c r="Z39" t="n">
-        <v>0.6191542818451178</v>
+        <v>0.6191542818451179</v>
       </c>
       <c r="AA39" t="n">
         <v>0.6065663927861378</v>
@@ -14974,7 +14714,7 @@
         <v>0.6428144749122029</v>
       </c>
       <c r="AC39" t="n">
-        <v>0.6255901931349188</v>
+        <v>0.6255901931349189</v>
       </c>
       <c r="AD39" t="n">
         <v>0.6230478672444136</v>
@@ -15004,7 +14744,7 @@
         <v>0.6269390818806924</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.6079880684733819</v>
+        <v>0.607988068473382</v>
       </c>
       <c r="AN39" t="n">
         <v>0.6216497381030623</v>
@@ -15016,22 +14756,22 @@
         <v>0.637279728565585</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.6385036390303858</v>
+        <v>0.6385036390303859</v>
       </c>
       <c r="AR39" t="n">
         <v>0.6218504186102592</v>
       </c>
       <c r="AS39" t="n">
-        <v>0.6159437091070966</v>
+        <v>0.6159437091070965</v>
       </c>
       <c r="AT39" t="n">
         <v>0.6382338826889489</v>
       </c>
       <c r="AU39" t="n">
-        <v>0.6091414149475302</v>
+        <v>0.60914141494753</v>
       </c>
       <c r="AV39" t="n">
-        <v>0.6467789147583269</v>
+        <v>0.6467789147583268</v>
       </c>
       <c r="AW39" t="n">
         <v>0.6202220620723381</v>
@@ -15097,13 +14837,13 @@
         <v>0.644673550026903</v>
       </c>
       <c r="BR39" t="n">
-        <v>0.6418384044096377</v>
+        <v>0.6418384044096378</v>
       </c>
       <c r="BS39" t="n">
         <v>0.6001374410402098</v>
       </c>
       <c r="BT39" t="n">
-        <v>0.6094625388993447</v>
+        <v>0.6094625388993448</v>
       </c>
       <c r="BU39" t="n">
         <v>0.6839435838977975</v>
@@ -15166,7 +14906,7 @@
         <v>0.6335010108978286</v>
       </c>
       <c r="CO39" t="n">
-        <v>0.6235975899032473</v>
+        <v>0.6235975899032474</v>
       </c>
       <c r="CP39" t="n">
         <v>0.632596282198527</v>
@@ -15178,10 +14918,10 @@
         <v>0.6029511921172651</v>
       </c>
       <c r="CS39" t="n">
-        <v>0.6641229410190395</v>
+        <v>0.6641229410190393</v>
       </c>
       <c r="CT39" t="n">
-        <v>0.6041875615908024</v>
+        <v>0.6041875615908023</v>
       </c>
       <c r="CU39" t="n">
         <v>0.6496949521229531</v>
@@ -15250,7 +14990,7 @@
         <v>0.7178550389301673</v>
       </c>
       <c r="DQ39" t="n">
-        <v>0.7556254728344693</v>
+        <v>0.7556254728344696</v>
       </c>
       <c r="DR39" t="n">
         <v>0.4451565806891999</v>
@@ -15300,7 +15040,7 @@
         <v>0.6447659147691216</v>
       </c>
       <c r="M40" t="n">
-        <v>0.6620306745980252</v>
+        <v>0.6620306745980253</v>
       </c>
       <c r="N40" t="n">
         <v>0.6580494664010181</v>
@@ -15312,7 +15052,7 @@
         <v>0.6362041648284303</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.6468346380638657</v>
+        <v>0.6468346380638655</v>
       </c>
       <c r="R40" t="n">
         <v>0.6440541786647836</v>
@@ -15321,7 +15061,7 @@
         <v>0.6644007995813348</v>
       </c>
       <c r="T40" t="n">
-        <v>0.6656316413777565</v>
+        <v>0.6656316413777564</v>
       </c>
       <c r="U40" t="n">
         <v>0.6683778910521659</v>
@@ -15342,7 +15082,7 @@
         <v>0.6358514368141701</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.6213187014424405</v>
+        <v>0.6213187014424404</v>
       </c>
       <c r="AB40" t="n">
         <v>0.6528823545548491</v>
@@ -15393,7 +15133,7 @@
         <v>0.651986263354175</v>
       </c>
       <c r="AR40" t="n">
-        <v>0.6328824409988618</v>
+        <v>0.6328824409988619</v>
       </c>
       <c r="AS40" t="n">
         <v>0.6275721260571046</v>
@@ -15492,7 +15232,7 @@
         <v>0.6665519452261977</v>
       </c>
       <c r="BY40" t="n">
-        <v>0.637062187224026</v>
+        <v>0.6370621872240259</v>
       </c>
       <c r="BZ40" t="n">
         <v>0.6681360687057833</v>
@@ -15504,13 +15244,13 @@
         <v>0.6710473446405167</v>
       </c>
       <c r="CC40" t="n">
-        <v>0.6686389948473287</v>
+        <v>0.6686389948473288</v>
       </c>
       <c r="CD40" t="n">
         <v>0.6841214942866871</v>
       </c>
       <c r="CE40" t="n">
-        <v>0.6709937652512022</v>
+        <v>0.6709937652512021</v>
       </c>
       <c r="CF40" t="n">
         <v>0.6750555451438339</v>
@@ -15528,7 +15268,7 @@
         <v>0.6449555164071387</v>
       </c>
       <c r="CK40" t="n">
-        <v>0.6622958890841638</v>
+        <v>0.662295889084164</v>
       </c>
       <c r="CL40" t="n">
         <v>0.6580184846789722</v>
@@ -15591,10 +15331,10 @@
         <v>0.6411672114018406</v>
       </c>
       <c r="DF40" t="n">
-        <v>0.6551869902869971</v>
+        <v>0.655186990286997</v>
       </c>
       <c r="DG40" t="n">
-        <v>0.6399394538346838</v>
+        <v>0.6399394538346839</v>
       </c>
       <c r="DH40" t="n">
         <v>0.6408932080628044</v>
@@ -15603,16 +15343,16 @@
         <v>0.6511693890175275</v>
       </c>
       <c r="DJ40" t="n">
-        <v>0.632314202356638</v>
+        <v>0.6323142023566379</v>
       </c>
       <c r="DK40" t="n">
         <v>0.6817862207284717</v>
       </c>
       <c r="DL40" t="n">
-        <v>0.6762830331737663</v>
+        <v>0.6762830331737664</v>
       </c>
       <c r="DM40" t="n">
-        <v>0.6351312548187875</v>
+        <v>0.6351312548187876</v>
       </c>
       <c r="DN40" t="n">
         <v>0.6585274417773415</v>
@@ -15644,7 +15384,7 @@
         <v>0.7834882109373001</v>
       </c>
       <c r="C41" t="n">
-        <v>0.8182639295249413</v>
+        <v>0.8182639295249412</v>
       </c>
       <c r="D41" t="n">
         <v>0.7679322442837097</v>
@@ -15656,7 +15396,7 @@
         <v>0.7235584255327446</v>
       </c>
       <c r="G41" t="n">
-        <v>0.695589529205797</v>
+        <v>0.6955895292057969</v>
       </c>
       <c r="H41" t="n">
         <v>0.6767616163467653</v>
@@ -15665,19 +15405,19 @@
         <v>0.6706746932254566</v>
       </c>
       <c r="J41" t="n">
-        <v>0.7149220340791597</v>
+        <v>0.7149220340791596</v>
       </c>
       <c r="K41" t="n">
         <v>0.6777310299968088</v>
       </c>
       <c r="L41" t="n">
-        <v>0.6577303890608209</v>
+        <v>0.6577303890608208</v>
       </c>
       <c r="M41" t="n">
         <v>0.6781487961912549</v>
       </c>
       <c r="N41" t="n">
-        <v>0.6743332759541224</v>
+        <v>0.6743332759541226</v>
       </c>
       <c r="O41" t="n">
         <v>0.6563611392934698</v>
@@ -15692,7 +15432,7 @@
         <v>0.6587347259054313</v>
       </c>
       <c r="S41" t="n">
-        <v>0.6792795868366682</v>
+        <v>0.679279586836668</v>
       </c>
       <c r="T41" t="n">
         <v>0.6822220548492672</v>
@@ -15713,13 +15453,13 @@
         <v>0.6429413965250037</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.6547609172342475</v>
+        <v>0.6547609172342473</v>
       </c>
       <c r="AA41" t="n">
         <v>0.6419560610776446</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.665813094288413</v>
+        <v>0.6658130942884132</v>
       </c>
       <c r="AC41" t="n">
         <v>0.6548356114580119</v>
@@ -15740,7 +15480,7 @@
         <v>0.6630491473973174</v>
       </c>
       <c r="AI41" t="n">
-        <v>0.6603508589097276</v>
+        <v>0.6603508589097278</v>
       </c>
       <c r="AJ41" t="n">
         <v>0.6693952951951109</v>
@@ -15755,7 +15495,7 @@
         <v>0.6378194711117787</v>
       </c>
       <c r="AN41" t="n">
-        <v>0.6579214668320902</v>
+        <v>0.6579214668320903</v>
       </c>
       <c r="AO41" t="n">
         <v>0.6585629161389375</v>
@@ -15791,7 +15531,7 @@
         <v>0.6522074779574513</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0.6691695924412111</v>
+        <v>0.6691695924412113</v>
       </c>
       <c r="BA41" t="n">
         <v>0.6779083346413206</v>
@@ -15884,16 +15624,16 @@
         <v>0.700450481927944</v>
       </c>
       <c r="CE41" t="n">
-        <v>0.6843614728474164</v>
+        <v>0.6843614728474167</v>
       </c>
       <c r="CF41" t="n">
         <v>0.692094890741171</v>
       </c>
       <c r="CG41" t="n">
-        <v>0.6959714534790196</v>
+        <v>0.6959714534790197</v>
       </c>
       <c r="CH41" t="n">
-        <v>0.6667429355166341</v>
+        <v>0.666742935516634</v>
       </c>
       <c r="CI41" t="n">
         <v>0.6875610474714066</v>
@@ -15935,7 +15675,7 @@
         <v>0.6890288937316567</v>
       </c>
       <c r="CV41" t="n">
-        <v>0.6912681318760894</v>
+        <v>0.6912681318760895</v>
       </c>
       <c r="CW41" t="n">
         <v>0.6644214885141588</v>
@@ -15944,7 +15684,7 @@
         <v>0.6513861292920059</v>
       </c>
       <c r="CY41" t="n">
-        <v>0.6816539503611745</v>
+        <v>0.6816539503611746</v>
       </c>
       <c r="CZ41" t="n">
         <v>0.6752516443004692</v>
@@ -15971,7 +15711,7 @@
         <v>0.6580520594148594</v>
       </c>
       <c r="DH41" t="n">
-        <v>0.6547988664077137</v>
+        <v>0.6547988664077138</v>
       </c>
       <c r="DI41" t="n">
         <v>0.6730916129195305</v>
@@ -15980,7 +15720,7 @@
         <v>0.6521547396177229</v>
       </c>
       <c r="DK41" t="n">
-        <v>0.7000714343447374</v>
+        <v>0.7000714343447375</v>
       </c>
       <c r="DL41" t="n">
         <v>0.6931053416523278</v>
@@ -16018,7 +15758,7 @@
         <v>0.7739579131844876</v>
       </c>
       <c r="C42" t="n">
-        <v>0.8059648414420609</v>
+        <v>0.8059648414420607</v>
       </c>
       <c r="D42" t="n">
         <v>0.7661852611709767</v>
@@ -16156,7 +15896,7 @@
         <v>0.6974058553277812</v>
       </c>
       <c r="AW42" t="n">
-        <v>0.6768592543849774</v>
+        <v>0.6768592543849775</v>
       </c>
       <c r="AX42" t="n">
         <v>0.6974316826966369</v>
@@ -16180,7 +15920,7 @@
         <v>0.6570032754569134</v>
       </c>
       <c r="BE42" t="n">
-        <v>0.6983106549472032</v>
+        <v>0.6983106549472033</v>
       </c>
       <c r="BF42" t="n">
         <v>0.6675879314162351</v>
@@ -16213,7 +15953,7 @@
         <v>0.6845911731547188</v>
       </c>
       <c r="BP42" t="n">
-        <v>0.6819459697249231</v>
+        <v>0.6819459697249229</v>
       </c>
       <c r="BQ42" t="n">
         <v>0.6796365447358774</v>
@@ -16285,7 +16025,7 @@
         <v>0.6828211663963771</v>
       </c>
       <c r="CN42" t="n">
-        <v>0.6791924120840904</v>
+        <v>0.6791924120840905</v>
       </c>
       <c r="CO42" t="n">
         <v>0.6941254009427035</v>
@@ -16324,7 +16064,7 @@
         <v>0.69657961815359</v>
       </c>
       <c r="DA42" t="n">
-        <v>0.7166378492067708</v>
+        <v>0.7166378492067705</v>
       </c>
       <c r="DB42" t="n">
         <v>0.705614291705758</v>
@@ -16342,7 +16082,7 @@
         <v>0.7031295145383258</v>
       </c>
       <c r="DG42" t="n">
-        <v>0.6782136575249105</v>
+        <v>0.6782136575249103</v>
       </c>
       <c r="DH42" t="n">
         <v>0.6720017845675429</v>
@@ -16422,7 +16162,7 @@
         <v>0.6884885662948109</v>
       </c>
       <c r="M43" t="n">
-        <v>0.719217916002675</v>
+        <v>0.7192179160026752</v>
       </c>
       <c r="N43" t="n">
         <v>0.7129614749617141</v>
@@ -16440,7 +16180,7 @@
         <v>0.6979068211134685</v>
       </c>
       <c r="S43" t="n">
-        <v>0.7153737552444877</v>
+        <v>0.7153737552444875</v>
       </c>
       <c r="T43" t="n">
         <v>0.7232453126474422</v>
@@ -16464,7 +16204,7 @@
         <v>0.6979804316391264</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.6973062589719753</v>
+        <v>0.6973062589719755</v>
       </c>
       <c r="AB43" t="n">
         <v>0.7016290179478822</v>
@@ -16506,7 +16246,7 @@
         <v>0.7012707521877978</v>
       </c>
       <c r="AO43" t="n">
-        <v>0.6876511751358321</v>
+        <v>0.687651175135832</v>
       </c>
       <c r="AP43" t="n">
         <v>0.7087606735435358</v>
@@ -16542,7 +16282,7 @@
         <v>0.7033470381175212</v>
       </c>
       <c r="BA43" t="n">
-        <v>0.7210770386445768</v>
+        <v>0.7210770386445771</v>
       </c>
       <c r="BB43" t="n">
         <v>0.7224046779991798</v>
@@ -16566,22 +16306,22 @@
         <v>0.6706186331408788</v>
       </c>
       <c r="BI43" t="n">
-        <v>0.7388808847557529</v>
+        <v>0.7388808847557528</v>
       </c>
       <c r="BJ43" t="n">
-        <v>0.7202064871020148</v>
+        <v>0.7202064871020147</v>
       </c>
       <c r="BK43" t="n">
         <v>0.7167332941694335</v>
       </c>
       <c r="BL43" t="n">
-        <v>0.671952765697012</v>
+        <v>0.6719527656970119</v>
       </c>
       <c r="BM43" t="n">
-        <v>0.6927034965372755</v>
+        <v>0.6927034965372753</v>
       </c>
       <c r="BN43" t="n">
-        <v>0.7037003830218951</v>
+        <v>0.703700383021895</v>
       </c>
       <c r="BO43" t="n">
         <v>0.7040642269147798</v>
@@ -16590,7 +16330,7 @@
         <v>0.6997276580752185</v>
       </c>
       <c r="BQ43" t="n">
-        <v>0.6987161979079196</v>
+        <v>0.6987161979079194</v>
       </c>
       <c r="BR43" t="n">
         <v>0.7151509680990735</v>
@@ -16599,7 +16339,7 @@
         <v>0.6615549686318807</v>
       </c>
       <c r="BT43" t="n">
-        <v>0.6800852978884933</v>
+        <v>0.6800852978884934</v>
       </c>
       <c r="BU43" t="n">
         <v>0.7350109169216403</v>
@@ -16617,7 +16357,7 @@
         <v>0.6901895455378589</v>
       </c>
       <c r="BZ43" t="n">
-        <v>0.722695263532198</v>
+        <v>0.7226952635321982</v>
       </c>
       <c r="CA43" t="n">
         <v>0.727829734653662</v>
@@ -16665,10 +16405,10 @@
         <v>0.7261323725005906</v>
       </c>
       <c r="CP43" t="n">
-        <v>0.7084306379615293</v>
+        <v>0.7084306379615294</v>
       </c>
       <c r="CQ43" t="n">
-        <v>0.7131074123114575</v>
+        <v>0.7131074123114572</v>
       </c>
       <c r="CR43" t="n">
         <v>0.6887455713590729</v>
@@ -16683,7 +16423,7 @@
         <v>0.7348225661036479</v>
       </c>
       <c r="CV43" t="n">
-        <v>0.7330197880363419</v>
+        <v>0.7330197880363418</v>
       </c>
       <c r="CW43" t="n">
         <v>0.7042914866272968</v>
@@ -16734,7 +16474,7 @@
         <v>0.7321202335723755</v>
       </c>
       <c r="DM43" t="n">
-        <v>0.6860221452848367</v>
+        <v>0.6860221452848368</v>
       </c>
       <c r="DN43" t="n">
         <v>0.7015563996685916</v>
@@ -16805,7 +16545,7 @@
         <v>0.7235145532691242</v>
       </c>
       <c r="P44" t="n">
-        <v>0.7139496907757256</v>
+        <v>0.7139496907757257</v>
       </c>
       <c r="Q44" t="n">
         <v>0.7100762981801731</v>
@@ -16841,7 +16581,7 @@
         <v>0.7278462776012266</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.7248038691005202</v>
+        <v>0.7248038691005201</v>
       </c>
       <c r="AC44" t="n">
         <v>0.7223196139695746</v>
@@ -16895,7 +16635,7 @@
         <v>0.7075439256847881</v>
       </c>
       <c r="AT44" t="n">
-        <v>0.7055909124292516</v>
+        <v>0.7055909124292514</v>
       </c>
       <c r="AU44" t="n">
         <v>0.691109427796189</v>
@@ -16931,13 +16671,13 @@
         <v>0.7391404591365522</v>
       </c>
       <c r="BF44" t="n">
-        <v>0.7135155781941326</v>
+        <v>0.7135155781941327</v>
       </c>
       <c r="BG44" t="n">
-        <v>0.7044857192563336</v>
+        <v>0.7044857192563335</v>
       </c>
       <c r="BH44" t="n">
-        <v>0.6900847779097025</v>
+        <v>0.6900847779097026</v>
       </c>
       <c r="BI44" t="n">
         <v>0.7607083597681485</v>
@@ -16973,7 +16713,7 @@
         <v>0.6842039129639229</v>
       </c>
       <c r="BT44" t="n">
-        <v>0.7079658956498879</v>
+        <v>0.7079658956498881</v>
       </c>
       <c r="BU44" t="n">
         <v>0.7518619890895801</v>
@@ -16991,7 +16731,7 @@
         <v>0.7110537679667253</v>
       </c>
       <c r="BZ44" t="n">
-        <v>0.7437764720696263</v>
+        <v>0.7437764720696264</v>
       </c>
       <c r="CA44" t="n">
         <v>0.7506284370576329</v>
@@ -17018,7 +16758,7 @@
         <v>0.7200694568609251</v>
       </c>
       <c r="CI44" t="n">
-        <v>0.7406355636506531</v>
+        <v>0.7406355636506533</v>
       </c>
       <c r="CJ44" t="n">
         <v>0.7398458507522331</v>
@@ -17096,7 +16836,7 @@
         <v>0.7133540896876327</v>
       </c>
       <c r="DI44" t="n">
-        <v>0.7504205508402777</v>
+        <v>0.7504205508402775</v>
       </c>
       <c r="DJ44" t="n">
         <v>0.7316924024515147</v>
@@ -17182,7 +16922,7 @@
         <v>0.7392511919311082</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.7314883666310927</v>
+        <v>0.731488366631093</v>
       </c>
       <c r="R45" t="n">
         <v>0.7452953339145599</v>
@@ -17242,7 +16982,7 @@
         <v>0.7506258937130181</v>
       </c>
       <c r="AK45" t="n">
-        <v>0.7173891718505593</v>
+        <v>0.7173891718505594</v>
       </c>
       <c r="AL45" t="n">
         <v>0.7310091027378537</v>
@@ -17254,7 +16994,7 @@
         <v>0.746213240643824</v>
       </c>
       <c r="AO45" t="n">
-        <v>0.7246193873515032</v>
+        <v>0.724619387351503</v>
       </c>
       <c r="AP45" t="n">
         <v>0.7515889183594614</v>
@@ -17296,7 +17036,7 @@
         <v>0.7759779597769969</v>
       </c>
       <c r="BC45" t="n">
-        <v>0.7645080511330274</v>
+        <v>0.7645080511330273</v>
       </c>
       <c r="BD45" t="n">
         <v>0.7311237205926175</v>
@@ -17308,7 +17048,7 @@
         <v>0.7393014971831978</v>
       </c>
       <c r="BG45" t="n">
-        <v>0.7208778347685131</v>
+        <v>0.720877834768513</v>
       </c>
       <c r="BH45" t="n">
         <v>0.7121589549177398</v>
@@ -17347,7 +17087,7 @@
         <v>0.7087501467060621</v>
       </c>
       <c r="BT45" t="n">
-        <v>0.7377985835567459</v>
+        <v>0.7377985835567458</v>
       </c>
       <c r="BU45" t="n">
         <v>0.7711204221661591</v>
@@ -17389,7 +17129,7 @@
         <v>0.7842192824857163</v>
       </c>
       <c r="CH45" t="n">
-        <v>0.7424882078873498</v>
+        <v>0.7424882078873499</v>
       </c>
       <c r="CI45" t="n">
         <v>0.7597891363355137</v>
@@ -17419,7 +17159,7 @@
         <v>0.7631757924600316</v>
       </c>
       <c r="CR45" t="n">
-        <v>0.7577257559986798</v>
+        <v>0.7577257559986799</v>
       </c>
       <c r="CS45" t="n">
         <v>0.7828081487384808</v>
@@ -17446,7 +17186,7 @@
         <v>0.7661827351867316</v>
       </c>
       <c r="DA45" t="n">
-        <v>0.7845334802012643</v>
+        <v>0.7845334802012645</v>
       </c>
       <c r="DB45" t="n">
         <v>0.7748265476891272</v>
@@ -17461,10 +17201,10 @@
         <v>0.7393041900809058</v>
       </c>
       <c r="DF45" t="n">
-        <v>0.7840790827020994</v>
+        <v>0.7840790827020993</v>
       </c>
       <c r="DG45" t="n">
-        <v>0.7457006839853475</v>
+        <v>0.7457006839853476</v>
       </c>
       <c r="DH45" t="n">
         <v>0.7359095622818507</v>
@@ -17580,7 +17320,7 @@
         <v>0.7678203436315556</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.7602356729269099</v>
+        <v>0.76023567292691</v>
       </c>
       <c r="Z46" t="n">
         <v>0.7719645350489217</v>
@@ -17622,10 +17362,10 @@
         <v>0.7580755753043913</v>
       </c>
       <c r="AM46" t="n">
-        <v>0.7809242316153635</v>
+        <v>0.7809242316153634</v>
       </c>
       <c r="AN46" t="n">
-        <v>0.7677408163111135</v>
+        <v>0.7677408163111137</v>
       </c>
       <c r="AO46" t="n">
         <v>0.7458049804881655</v>
@@ -17643,7 +17383,7 @@
         <v>0.760017823444312</v>
       </c>
       <c r="AT46" t="n">
-        <v>0.7479575062162073</v>
+        <v>0.7479575062162075</v>
       </c>
       <c r="AU46" t="n">
         <v>0.7444273994151074</v>
@@ -17679,10 +17419,10 @@
         <v>0.7851070438009445</v>
       </c>
       <c r="BF46" t="n">
-        <v>0.7657473866575768</v>
+        <v>0.7657473866575766</v>
       </c>
       <c r="BG46" t="n">
-        <v>0.7389074000444326</v>
+        <v>0.7389074000444324</v>
       </c>
       <c r="BH46" t="n">
         <v>0.7364121491482869</v>
@@ -17715,7 +17455,7 @@
         <v>0.770741489897195</v>
       </c>
       <c r="BR46" t="n">
-        <v>0.7862996935143571</v>
+        <v>0.7862996935143574</v>
       </c>
       <c r="BS46" t="n">
         <v>0.7351694398733094</v>
@@ -17733,10 +17473,10 @@
         <v>0.8151289379082746</v>
       </c>
       <c r="BX46" t="n">
-        <v>0.7871521052709122</v>
+        <v>0.7871521052709124</v>
       </c>
       <c r="BY46" t="n">
-        <v>0.7571568383294408</v>
+        <v>0.7571568383294409</v>
       </c>
       <c r="BZ46" t="n">
         <v>0.7869489739343817</v>
@@ -17796,7 +17536,7 @@
         <v>0.7909452691809796</v>
       </c>
       <c r="CS46" t="n">
-        <v>0.8060017804975365</v>
+        <v>0.8060017804975366</v>
       </c>
       <c r="CT46" t="n">
         <v>0.8048198196164998</v>
@@ -17894,7 +17634,7 @@
         <v>0.7755782081987203</v>
       </c>
       <c r="E47" t="n">
-        <v>0.7815709281861434</v>
+        <v>0.7815709281861433</v>
       </c>
       <c r="F47" t="n">
         <v>0.7588069756921586</v>
@@ -17903,7 +17643,7 @@
         <v>0.8255805083974193</v>
       </c>
       <c r="H47" t="n">
-        <v>0.832264104863183</v>
+        <v>0.8322641048631829</v>
       </c>
       <c r="I47" t="n">
         <v>0.8355836277414493</v>
@@ -17939,7 +17679,7 @@
         <v>0.8037698867211618</v>
       </c>
       <c r="T47" t="n">
-        <v>0.8150867142581961</v>
+        <v>0.8150867142581959</v>
       </c>
       <c r="U47" t="n">
         <v>0.8308369586111984</v>
@@ -17957,7 +17697,7 @@
         <v>0.7864778618942495</v>
       </c>
       <c r="Z47" t="n">
-        <v>0.7977164250747181</v>
+        <v>0.7977164250747182</v>
       </c>
       <c r="AA47" t="n">
         <v>0.8074512744022888</v>
@@ -17990,13 +17730,13 @@
         <v>0.7969666764739037</v>
       </c>
       <c r="AK47" t="n">
-        <v>0.7661629667659455</v>
+        <v>0.7661629667659456</v>
       </c>
       <c r="AL47" t="n">
         <v>0.7854110662409125</v>
       </c>
       <c r="AM47" t="n">
-        <v>0.8131817767942554</v>
+        <v>0.8131817767942552</v>
       </c>
       <c r="AN47" t="n">
         <v>0.7879513194515023</v>
@@ -18023,7 +17763,7 @@
         <v>0.7723482236504992</v>
       </c>
       <c r="AV47" t="n">
-        <v>0.8145857293450784</v>
+        <v>0.8145857293450783</v>
       </c>
       <c r="AW47" t="n">
         <v>0.8075525777870199</v>
@@ -18032,7 +17772,7 @@
         <v>0.8020418419167126</v>
       </c>
       <c r="AY47" t="n">
-        <v>0.7563604064174783</v>
+        <v>0.7563604064174781</v>
       </c>
       <c r="AZ47" t="n">
         <v>0.7817325732114805</v>
@@ -18050,7 +17790,7 @@
         <v>0.7861940300444664</v>
       </c>
       <c r="BE47" t="n">
-        <v>0.8095956797685961</v>
+        <v>0.8095956797685959</v>
       </c>
       <c r="BF47" t="n">
         <v>0.7919314266419546</v>
@@ -18068,7 +17808,7 @@
         <v>0.8067382335950924</v>
       </c>
       <c r="BK47" t="n">
-        <v>0.7953768145319214</v>
+        <v>0.7953768145319212</v>
       </c>
       <c r="BL47" t="n">
         <v>0.7806440320692597</v>
@@ -18080,7 +17820,7 @@
         <v>0.8087787135514591</v>
       </c>
       <c r="BO47" t="n">
-        <v>0.7952575159599672</v>
+        <v>0.795257515959967</v>
       </c>
       <c r="BP47" t="n">
         <v>0.7840721175450742</v>
@@ -18110,7 +17850,7 @@
         <v>0.8114561115874372</v>
       </c>
       <c r="BY47" t="n">
-        <v>0.7822209260354438</v>
+        <v>0.7822209260354436</v>
       </c>
       <c r="BZ47" t="n">
         <v>0.8074316833100087</v>
@@ -18161,7 +17901,7 @@
         <v>0.8428564962408838</v>
       </c>
       <c r="CP47" t="n">
-        <v>0.809108344530417</v>
+        <v>0.8091083445304169</v>
       </c>
       <c r="CQ47" t="n">
         <v>0.8137376348614108</v>
@@ -18185,10 +17925,10 @@
         <v>0.8059438001285194</v>
       </c>
       <c r="CX47" t="n">
-        <v>0.7811030399960889</v>
+        <v>0.781103039996089</v>
       </c>
       <c r="CY47" t="n">
-        <v>0.8256297201122951</v>
+        <v>0.825629720112295</v>
       </c>
       <c r="CZ47" t="n">
         <v>0.8094086508552965</v>
@@ -18248,7 +17988,7 @@
         <v>0.619060055279383</v>
       </c>
       <c r="DS47" t="n">
-        <v>0.731546797344197</v>
+        <v>0.7315467973441968</v>
       </c>
       <c r="DT47" t="n">
         <v>0.8114931001269705</v>
@@ -18271,7 +18011,7 @@
         <v>0.7832210574715042</v>
       </c>
       <c r="F48" t="n">
-        <v>0.7736827889570973</v>
+        <v>0.7736827889570975</v>
       </c>
       <c r="G48" t="n">
         <v>0.8342678665256638</v>
@@ -18304,7 +18044,7 @@
         <v>0.8179376306754761</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.8024043721800191</v>
+        <v>0.802404372180019</v>
       </c>
       <c r="R48" t="n">
         <v>0.8153228695559275</v>
@@ -18319,7 +18059,7 @@
         <v>0.84646960416245</v>
       </c>
       <c r="V48" t="n">
-        <v>0.8333467395532695</v>
+        <v>0.8333467395532693</v>
       </c>
       <c r="W48" t="n">
         <v>0.8331862410704387</v>
@@ -18343,7 +18083,7 @@
         <v>0.8169497600953048</v>
       </c>
       <c r="AD48" t="n">
-        <v>0.8253617855015127</v>
+        <v>0.8253617855015126</v>
       </c>
       <c r="AE48" t="n">
         <v>0.8023301892717514</v>
@@ -18463,7 +18203,7 @@
         <v>0.8219742907656047</v>
       </c>
       <c r="BR48" t="n">
-        <v>0.8328514144082274</v>
+        <v>0.8328514144082273</v>
       </c>
       <c r="BS48" t="n">
         <v>0.7936764530969574</v>
@@ -18511,7 +18251,7 @@
         <v>0.8497573651763914</v>
       </c>
       <c r="CH48" t="n">
-        <v>0.8188512966415621</v>
+        <v>0.818851296641562</v>
       </c>
       <c r="CI48" t="n">
         <v>0.8182655882809325</v>
@@ -18523,7 +18263,7 @@
         <v>0.8245467300980384</v>
       </c>
       <c r="CL48" t="n">
-        <v>0.8154499693810636</v>
+        <v>0.8154499693810637</v>
       </c>
       <c r="CM48" t="n">
         <v>0.8126644198958672</v>
@@ -18547,10 +18287,10 @@
         <v>0.8514847259017272</v>
       </c>
       <c r="CT48" t="n">
-        <v>0.8568795043346634</v>
+        <v>0.8568795043346632</v>
       </c>
       <c r="CU48" t="n">
-        <v>0.8370817015825138</v>
+        <v>0.8370817015825139</v>
       </c>
       <c r="CV48" t="n">
         <v>0.858561455871705</v>
@@ -18565,7 +18305,7 @@
         <v>0.8478367825032808</v>
       </c>
       <c r="CZ48" t="n">
-        <v>0.8298746779665265</v>
+        <v>0.8298746779665263</v>
       </c>
       <c r="DA48" t="n">
         <v>0.8439901168619937</v>
@@ -18580,7 +18320,7 @@
         <v>0.8358499734906921</v>
       </c>
       <c r="DE48" t="n">
-        <v>0.8100646524794575</v>
+        <v>0.8100646524794577</v>
       </c>
       <c r="DF48" t="n">
         <v>0.8520571895832069</v>
@@ -18592,7 +18332,7 @@
         <v>0.8053112582961931</v>
       </c>
       <c r="DI48" t="n">
-        <v>0.8583102020719851</v>
+        <v>0.8583102020719852</v>
       </c>
       <c r="DJ48" t="n">
         <v>0.8482938020002538</v>
@@ -18607,7 +18347,7 @@
         <v>0.8090282309422707</v>
       </c>
       <c r="DN48" t="n">
-        <v>0.8011756332612271</v>
+        <v>0.8011756332612272</v>
       </c>
       <c r="DO48" t="n">
         <v>0.8353814904686767</v>
@@ -18645,7 +18385,7 @@
         <v>0.783954006201527</v>
       </c>
       <c r="F49" t="n">
-        <v>0.7899340625414136</v>
+        <v>0.7899340625414139</v>
       </c>
       <c r="G49" t="n">
         <v>0.8431541147810304</v>
@@ -18663,7 +18403,7 @@
         <v>0.8525926843350999</v>
       </c>
       <c r="L49" t="n">
-        <v>0.8247550080294969</v>
+        <v>0.8247550080294968</v>
       </c>
       <c r="M49" t="n">
         <v>0.8755662199196308</v>
@@ -18681,10 +18421,10 @@
         <v>0.8254507379530885</v>
       </c>
       <c r="R49" t="n">
-        <v>0.8352696043555954</v>
+        <v>0.8352696043555955</v>
       </c>
       <c r="S49" t="n">
-        <v>0.8451932116441492</v>
+        <v>0.8451932116441491</v>
       </c>
       <c r="T49" t="n">
         <v>0.8533881399712268</v>
@@ -18723,7 +18463,7 @@
         <v>0.8262010340404796</v>
       </c>
       <c r="AF49" t="n">
-        <v>0.820041782820659</v>
+        <v>0.8200417828206591</v>
       </c>
       <c r="AG49" t="n">
         <v>0.8396726466467567</v>
@@ -18747,7 +18487,7 @@
         <v>0.8671349070850458</v>
       </c>
       <c r="AN49" t="n">
-        <v>0.8241864053895802</v>
+        <v>0.8241864053895801</v>
       </c>
       <c r="AO49" t="n">
         <v>0.814391318572966</v>
@@ -18777,7 +18517,7 @@
         <v>0.8583360222151073</v>
       </c>
       <c r="AX49" t="n">
-        <v>0.8428358840327047</v>
+        <v>0.8428358840327048</v>
       </c>
       <c r="AY49" t="n">
         <v>0.7938330835308758</v>
@@ -18786,7 +18526,7 @@
         <v>0.8205142141556252</v>
       </c>
       <c r="BA49" t="n">
-        <v>0.851575429980296</v>
+        <v>0.8515754299802962</v>
       </c>
       <c r="BB49" t="n">
         <v>0.8785278195474163</v>
@@ -18798,7 +18538,7 @@
         <v>0.8350731290326475</v>
       </c>
       <c r="BE49" t="n">
-        <v>0.8584540479283764</v>
+        <v>0.8584540479283762</v>
       </c>
       <c r="BF49" t="n">
         <v>0.8407577830510963</v>
@@ -18819,7 +18559,7 @@
         <v>0.8304912780654436</v>
       </c>
       <c r="BL49" t="n">
-        <v>0.8305384043444319</v>
+        <v>0.8305384043444318</v>
       </c>
       <c r="BM49" t="n">
         <v>0.8205571878033655</v>
@@ -18828,7 +18568,7 @@
         <v>0.8576017138393198</v>
       </c>
       <c r="BO49" t="n">
-        <v>0.8392481791635424</v>
+        <v>0.8392481791635426</v>
       </c>
       <c r="BP49" t="n">
         <v>0.8260722412622501</v>
@@ -18897,7 +18637,7 @@
         <v>0.8502294930758343</v>
       </c>
       <c r="CL49" t="n">
-        <v>0.832947108260181</v>
+        <v>0.8329471082601809</v>
       </c>
       <c r="CM49" t="n">
         <v>0.8341215040627762</v>
@@ -18972,7 +18712,7 @@
         <v>0.8746734573619231</v>
       </c>
       <c r="DK49" t="n">
-        <v>0.8638843343321465</v>
+        <v>0.8638843343321467</v>
       </c>
       <c r="DL49" t="n">
         <v>0.8548545181781178</v>
@@ -18981,10 +18721,10 @@
         <v>0.8320049799984104</v>
       </c>
       <c r="DN49" t="n">
-        <v>0.8230378149546714</v>
+        <v>0.8230378149546715</v>
       </c>
       <c r="DO49" t="n">
-        <v>0.8515159125448033</v>
+        <v>0.8515159125448031</v>
       </c>
       <c r="DP49" t="n">
         <v>0.7732906545597389</v>
@@ -19007,7 +18747,7 @@
         <v>0.3956877609124912</v>
       </c>
       <c r="B50" t="n">
-        <v>0.6805745504504062</v>
+        <v>0.6805745504504063</v>
       </c>
       <c r="C50" t="n">
         <v>0.7580119345634287</v>
@@ -19016,7 +18756,7 @@
         <v>0.7955848087810072</v>
       </c>
       <c r="E50" t="n">
-        <v>0.7835685993196795</v>
+        <v>0.7835685993196794</v>
       </c>
       <c r="F50" t="n">
         <v>0.8064782840031713</v>
@@ -19031,7 +18771,7 @@
         <v>0.9042256943518283</v>
       </c>
       <c r="J50" t="n">
-        <v>0.8772361803041606</v>
+        <v>0.8772361803041607</v>
       </c>
       <c r="K50" t="n">
         <v>0.8719234256260467</v>
@@ -19046,7 +18786,7 @@
         <v>0.8680726841183796</v>
       </c>
       <c r="O50" t="n">
-        <v>0.8656537452735196</v>
+        <v>0.8656537452735198</v>
       </c>
       <c r="P50" t="n">
         <v>0.8646865163639335</v>
@@ -19070,7 +18810,7 @@
         <v>0.8748944643972</v>
       </c>
       <c r="W50" t="n">
-        <v>0.8633627518558024</v>
+        <v>0.8633627518558026</v>
       </c>
       <c r="X50" t="n">
         <v>0.8522801635733789</v>
@@ -19085,7 +18825,7 @@
         <v>0.8642802683614037</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.8751124533951511</v>
+        <v>0.8751124533951513</v>
       </c>
       <c r="AC50" t="n">
         <v>0.8568211119912061</v>
@@ -19100,7 +18840,7 @@
         <v>0.8446855298336025</v>
       </c>
       <c r="AG50" t="n">
-        <v>0.8614694898672666</v>
+        <v>0.8614694898672665</v>
       </c>
       <c r="AH50" t="n">
         <v>0.8618567659193307</v>
@@ -19142,7 +18882,7 @@
         <v>0.8429203289708901</v>
       </c>
       <c r="AU50" t="n">
-        <v>0.8504469149441285</v>
+        <v>0.8504469149441286</v>
       </c>
       <c r="AV50" t="n">
         <v>0.863785224454466</v>
@@ -19184,10 +18924,10 @@
         <v>0.8366028038747683</v>
       </c>
       <c r="BI50" t="n">
-        <v>0.8766043433965858</v>
+        <v>0.8766043433965859</v>
       </c>
       <c r="BJ50" t="n">
-        <v>0.8448839641392648</v>
+        <v>0.8448839641392649</v>
       </c>
       <c r="BK50" t="n">
         <v>0.8462227847236057</v>
@@ -19196,7 +18936,7 @@
         <v>0.8517156503093563</v>
       </c>
       <c r="BM50" t="n">
-        <v>0.8414751433154642</v>
+        <v>0.8414751433154644</v>
       </c>
       <c r="BN50" t="n">
         <v>0.8771853936238698</v>
@@ -19211,7 +18951,7 @@
         <v>0.8682597682968155</v>
       </c>
       <c r="BR50" t="n">
-        <v>0.8722294483281996</v>
+        <v>0.8722294483281995</v>
       </c>
       <c r="BS50" t="n">
         <v>0.8559224656819677</v>
@@ -19307,7 +19047,7 @@
         <v>0.8718521361798319</v>
       </c>
       <c r="CX50" t="n">
-        <v>0.859933812660772</v>
+        <v>0.8599338126607721</v>
       </c>
       <c r="CY50" t="n">
         <v>0.88197735241486</v>
@@ -19381,7 +19121,7 @@
         <v>0.3956585494555196</v>
       </c>
       <c r="B51" t="n">
-        <v>0.6647589496388717</v>
+        <v>0.6647589496388718</v>
       </c>
       <c r="C51" t="n">
         <v>0.7632741821175051</v>
@@ -19459,7 +19199,7 @@
         <v>0.8795371180909948</v>
       </c>
       <c r="AB51" t="n">
-        <v>0.887927401311514</v>
+        <v>0.8879274013115142</v>
       </c>
       <c r="AC51" t="n">
         <v>0.8747726844777903</v>
@@ -19516,7 +19256,7 @@
         <v>0.8630016266345854</v>
       </c>
       <c r="AU51" t="n">
-        <v>0.8719620108880053</v>
+        <v>0.8719620108880054</v>
       </c>
       <c r="AV51" t="n">
         <v>0.8741423490045696</v>
@@ -19528,7 +19268,7 @@
         <v>0.8674187936658011</v>
       </c>
       <c r="AY51" t="n">
-        <v>0.826004148894067</v>
+        <v>0.8260041488940671</v>
       </c>
       <c r="AZ51" t="n">
         <v>0.8491975877799205</v>
@@ -19543,7 +19283,7 @@
         <v>0.8644681990109583</v>
       </c>
       <c r="BD51" t="n">
-        <v>0.8721391055362228</v>
+        <v>0.8721391055362229</v>
       </c>
       <c r="BE51" t="n">
         <v>0.8993730992761091</v>
@@ -19555,7 +19295,7 @@
         <v>0.8334159926152431</v>
       </c>
       <c r="BH51" t="n">
-        <v>0.855738978383152</v>
+        <v>0.8557389783831518</v>
       </c>
       <c r="BI51" t="n">
         <v>0.8832364593684584</v>
@@ -19570,10 +19310,10 @@
         <v>0.8700827165748822</v>
       </c>
       <c r="BM51" t="n">
-        <v>0.861367458137008</v>
+        <v>0.8613674581370078</v>
       </c>
       <c r="BN51" t="n">
-        <v>0.8920277185949532</v>
+        <v>0.8920277185949531</v>
       </c>
       <c r="BO51" t="n">
         <v>0.8747815910095436</v>
@@ -19654,7 +19394,7 @@
         <v>0.8812767732257251</v>
       </c>
       <c r="CO51" t="n">
-        <v>0.909292384265766</v>
+        <v>0.9092923842657661</v>
       </c>
       <c r="CP51" t="n">
         <v>0.8865315895724869</v>
@@ -19663,10 +19403,10 @@
         <v>0.8938413536887577</v>
       </c>
       <c r="CR51" t="n">
-        <v>0.9054765150751797</v>
+        <v>0.9054765150751796</v>
       </c>
       <c r="CS51" t="n">
-        <v>0.890705388811234</v>
+        <v>0.8907053888112341</v>
       </c>
       <c r="CT51" t="n">
         <v>0.9138079568390054</v>
@@ -19708,7 +19448,7 @@
         <v>0.8957381145274992</v>
       </c>
       <c r="DG51" t="n">
-        <v>0.8949102910761321</v>
+        <v>0.8949102910761322</v>
       </c>
       <c r="DH51" t="n">
         <v>0.8735752980445183</v>
@@ -19785,7 +19525,7 @@
         <v>0.9004281635079013</v>
       </c>
       <c r="L52" t="n">
-        <v>0.8938255641496186</v>
+        <v>0.8938255641496184</v>
       </c>
       <c r="M52" t="n">
         <v>0.9086708555157714</v>
@@ -19917,16 +19657,16 @@
         <v>0.86858932579131</v>
       </c>
       <c r="BD52" t="n">
-        <v>0.884458071701439</v>
+        <v>0.8844580717014389</v>
       </c>
       <c r="BE52" t="n">
         <v>0.9134651862255481</v>
       </c>
       <c r="BF52" t="n">
-        <v>0.8966446880977268</v>
+        <v>0.8966446880977269</v>
       </c>
       <c r="BG52" t="n">
-        <v>0.8504928600224161</v>
+        <v>0.850492860022416</v>
       </c>
       <c r="BH52" t="n">
         <v>0.8693496013883546</v>
@@ -19953,7 +19693,7 @@
         <v>0.8860509878542714</v>
       </c>
       <c r="BP52" t="n">
-        <v>0.8797594612101289</v>
+        <v>0.8797594612101292</v>
       </c>
       <c r="BQ52" t="n">
         <v>0.9031576863808695</v>
@@ -19992,7 +19732,7 @@
         <v>0.9119915539170332</v>
       </c>
       <c r="CC52" t="n">
-        <v>0.9072420465529532</v>
+        <v>0.907242046552953</v>
       </c>
       <c r="CD52" t="n">
         <v>0.884366419855653</v>
@@ -20010,13 +19750,13 @@
         <v>0.8928587919954597</v>
       </c>
       <c r="CI52" t="n">
-        <v>0.8912645055702118</v>
+        <v>0.8912645055702115</v>
       </c>
       <c r="CJ52" t="n">
         <v>0.9035198335717693</v>
       </c>
       <c r="CK52" t="n">
-        <v>0.9040290775744774</v>
+        <v>0.9040290775744776</v>
       </c>
       <c r="CL52" t="n">
         <v>0.8757720196914235</v>
@@ -20067,7 +19807,7 @@
         <v>0.8862788839830348</v>
       </c>
       <c r="DB52" t="n">
-        <v>0.9037584200751511</v>
+        <v>0.9037584200751512</v>
       </c>
       <c r="DC52" t="n">
         <v>0.8794740719161952</v>
@@ -20085,7 +19825,7 @@
         <v>0.9044247780514337</v>
       </c>
       <c r="DH52" t="n">
-        <v>0.893607122550903</v>
+        <v>0.8936071225509028</v>
       </c>
       <c r="DI52" t="n">
         <v>0.8740643546043247</v>
@@ -20126,16 +19866,16 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>0.3957344967037408</v>
+        <v>0.3957344967037409</v>
       </c>
       <c r="B53" t="n">
         <v>0.6308473535318073</v>
       </c>
       <c r="C53" t="n">
-        <v>0.7758696765578523</v>
+        <v>0.7758696765578524</v>
       </c>
       <c r="D53" t="n">
-        <v>0.8212523000857281</v>
+        <v>0.8212523000857282</v>
       </c>
       <c r="E53" t="n">
         <v>0.7773105099816398</v>
@@ -20153,16 +19893,16 @@
         <v>0.9159126319411969</v>
       </c>
       <c r="J53" t="n">
-        <v>0.8869176078847401</v>
+        <v>0.8869176078847403</v>
       </c>
       <c r="K53" t="n">
-        <v>0.9062133531876696</v>
+        <v>0.9062133531876694</v>
       </c>
       <c r="L53" t="n">
         <v>0.9052822429341503</v>
       </c>
       <c r="M53" t="n">
-        <v>0.902836864776548</v>
+        <v>0.9028368647765479</v>
       </c>
       <c r="N53" t="n">
         <v>0.8977889219326792</v>
@@ -20174,10 +19914,10 @@
         <v>0.9017078674972361</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.898803610822597</v>
+        <v>0.8988036108225971</v>
       </c>
       <c r="R53" t="n">
-        <v>0.879497479197609</v>
+        <v>0.8794974791976092</v>
       </c>
       <c r="S53" t="n">
         <v>0.8956763956952216</v>
@@ -20273,7 +20013,7 @@
         <v>0.9158661872934742</v>
       </c>
       <c r="AX53" t="n">
-        <v>0.8610927802516152</v>
+        <v>0.8610927802516154</v>
       </c>
       <c r="AY53" t="n">
         <v>0.843496744362105</v>
@@ -20291,7 +20031,7 @@
         <v>0.8662256665520661</v>
       </c>
       <c r="BD53" t="n">
-        <v>0.8911924147827057</v>
+        <v>0.8911924147827056</v>
       </c>
       <c r="BE53" t="n">
         <v>0.9213800450591992</v>
@@ -20348,7 +20088,7 @@
         <v>0.9221916506717083</v>
       </c>
       <c r="BW53" t="n">
-        <v>0.9080115718034554</v>
+        <v>0.9080115718034555</v>
       </c>
       <c r="BX53" t="n">
         <v>0.9038633995539905</v>
@@ -20396,7 +20136,7 @@
         <v>0.8862647560627046</v>
       </c>
       <c r="CM53" t="n">
-        <v>0.8932435170880252</v>
+        <v>0.8932435170880253</v>
       </c>
       <c r="CN53" t="n">
         <v>0.9008780047478008</v>
@@ -20411,7 +20151,7 @@
         <v>0.9004729918845522</v>
       </c>
       <c r="CR53" t="n">
-        <v>0.9211754031466028</v>
+        <v>0.9211754031466027</v>
       </c>
       <c r="CS53" t="n">
         <v>0.8726116001032757</v>
@@ -20432,7 +20172,7 @@
         <v>0.9189062912205817</v>
       </c>
       <c r="CY53" t="n">
-        <v>0.8815665658660794</v>
+        <v>0.8815665658660792</v>
       </c>
       <c r="CZ53" t="n">
         <v>0.8894836938486972</v>
@@ -20462,7 +20202,7 @@
         <v>0.9098015818420178</v>
       </c>
       <c r="DI53" t="n">
-        <v>0.8495111843778886</v>
+        <v>0.8495111843778888</v>
       </c>
       <c r="DJ53" t="n">
         <v>0.9458172177282501</v>
@@ -20489,7 +20229,7 @@
         <v>0.8105146224374988</v>
       </c>
       <c r="DR53" t="n">
-        <v>0.8564459203183514</v>
+        <v>0.8564459203183512</v>
       </c>
       <c r="DS53" t="n">
         <v>0.7735419389205463</v>
@@ -20500,13 +20240,13 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>0.3957243117925276</v>
+        <v>0.3957243117925275</v>
       </c>
       <c r="B54" t="n">
         <v>0.6137181666321825</v>
       </c>
       <c r="C54" t="n">
-        <v>0.782131792963714</v>
+        <v>0.7821317929637142</v>
       </c>
       <c r="D54" t="n">
         <v>0.8296523887569358</v>
@@ -20614,10 +20354,10 @@
         <v>0.9089578330915202</v>
       </c>
       <c r="AM54" t="n">
-        <v>0.9062726512423047</v>
+        <v>0.9062726512423046</v>
       </c>
       <c r="AN54" t="n">
-        <v>0.8856739671688011</v>
+        <v>0.885673967168801</v>
       </c>
       <c r="AO54" t="n">
         <v>0.8969164935227008</v>
@@ -20653,7 +20393,7 @@
         <v>0.8431461635391295</v>
       </c>
       <c r="AZ54" t="n">
-        <v>0.8535095393360201</v>
+        <v>0.8535095393360204</v>
       </c>
       <c r="BA54" t="n">
         <v>0.8497612267512442</v>
@@ -20785,7 +20525,7 @@
         <v>0.889649232453362</v>
       </c>
       <c r="CR54" t="n">
-        <v>0.9181917823986124</v>
+        <v>0.9181917823986123</v>
       </c>
       <c r="CS54" t="n">
         <v>0.8450964047979077</v>
@@ -20803,7 +20543,7 @@
         <v>0.890196783858873</v>
       </c>
       <c r="CX54" t="n">
-        <v>0.9270617736295725</v>
+        <v>0.9270617736295726</v>
       </c>
       <c r="CY54" t="n">
         <v>0.8608085830615224</v>
@@ -20976,7 +20716,7 @@
         <v>0.8694809187292235</v>
       </c>
       <c r="AI55" t="n">
-        <v>0.8412604744793392</v>
+        <v>0.841260474479339</v>
       </c>
       <c r="AJ55" t="n">
         <v>0.8471049270374814</v>
@@ -21018,7 +20758,7 @@
         <v>0.8608795224859188</v>
       </c>
       <c r="AW55" t="n">
-        <v>0.8981229777410951</v>
+        <v>0.8981229777410952</v>
       </c>
       <c r="AX55" t="n">
         <v>0.8100393245733259</v>
@@ -21084,7 +20824,7 @@
         <v>0.8839241913936637</v>
       </c>
       <c r="BS55" t="n">
-        <v>0.9522213497736729</v>
+        <v>0.952221349773673</v>
       </c>
       <c r="BT55" t="n">
         <v>0.8588907064350858</v>
@@ -21102,7 +20842,7 @@
         <v>0.8899058895524398</v>
       </c>
       <c r="BY55" t="n">
-        <v>0.9050436994284838</v>
+        <v>0.9050436994284839</v>
       </c>
       <c r="BZ55" t="n">
         <v>0.8601802638687152</v>
@@ -21123,7 +20863,7 @@
         <v>0.8761521378948602</v>
       </c>
       <c r="CF55" t="n">
-        <v>0.8587663767680274</v>
+        <v>0.8587663767680276</v>
       </c>
       <c r="CG55" t="n">
         <v>0.8707736090621916</v>
@@ -21150,7 +20890,7 @@
         <v>0.8896227071912785</v>
       </c>
       <c r="CO55" t="n">
-        <v>0.9062600436481936</v>
+        <v>0.9062600436481935</v>
       </c>
       <c r="CP55" t="n">
         <v>0.8951228243939628</v>
@@ -21180,7 +20920,7 @@
         <v>0.9265905446156881</v>
       </c>
       <c r="CY55" t="n">
-        <v>0.8273633044813469</v>
+        <v>0.8273633044813468</v>
       </c>
       <c r="CZ55" t="n">
         <v>0.8647663859580628</v>
@@ -21201,7 +20941,7 @@
         <v>0.9200564264300078</v>
       </c>
       <c r="DF55" t="n">
-        <v>0.8661486893089261</v>
+        <v>0.8661486893089263</v>
       </c>
       <c r="DG55" t="n">
         <v>0.8649706621963276</v>
@@ -21234,10 +20974,10 @@
         <v>0.8447993669747825</v>
       </c>
       <c r="DQ55" t="n">
-        <v>0.8179733366215435</v>
+        <v>0.8179733366215434</v>
       </c>
       <c r="DR55" t="n">
-        <v>0.8634203279853011</v>
+        <v>0.8634203279853012</v>
       </c>
       <c r="DS55" t="n">
         <v>0.7852153257249083</v>
@@ -21260,7 +21000,7 @@
         <v>0.8427671859803768</v>
       </c>
       <c r="E56" t="n">
-        <v>0.7742612315710836</v>
+        <v>0.7742612315710837</v>
       </c>
       <c r="F56" t="n">
         <v>0.8459416645806331</v>
@@ -21302,7 +21042,7 @@
         <v>0.8486729986972</v>
       </c>
       <c r="S56" t="n">
-        <v>0.8570514351527715</v>
+        <v>0.8570514351527714</v>
       </c>
       <c r="T56" t="n">
         <v>0.8600814898693788</v>
@@ -21344,10 +21084,10 @@
         <v>0.8745517245016756</v>
       </c>
       <c r="AG56" t="n">
-        <v>0.8704306674494052</v>
+        <v>0.8704306674494054</v>
       </c>
       <c r="AH56" t="n">
-        <v>0.8432695695844864</v>
+        <v>0.8432695695844866</v>
       </c>
       <c r="AI56" t="n">
         <v>0.8078350663941192</v>
@@ -21356,13 +21096,13 @@
         <v>0.8186099990082805</v>
       </c>
       <c r="AK56" t="n">
-        <v>0.8956788252058413</v>
+        <v>0.8956788252058414</v>
       </c>
       <c r="AL56" t="n">
         <v>0.8903598784625838</v>
       </c>
       <c r="AM56" t="n">
-        <v>0.8661658796837343</v>
+        <v>0.8661658796837342</v>
       </c>
       <c r="AN56" t="n">
         <v>0.8710105912060486</v>
@@ -21389,10 +21129,10 @@
         <v>0.8838540091746749</v>
       </c>
       <c r="AV56" t="n">
-        <v>0.8368581925321055</v>
+        <v>0.8368581925321057</v>
       </c>
       <c r="AW56" t="n">
-        <v>0.8723454258078305</v>
+        <v>0.8723454258078307</v>
       </c>
       <c r="AX56" t="n">
         <v>0.7638431574777934</v>
@@ -21452,13 +21192,13 @@
         <v>0.8799816361762999</v>
       </c>
       <c r="BQ56" t="n">
-        <v>0.8952690225981772</v>
+        <v>0.8952690225981771</v>
       </c>
       <c r="BR56" t="n">
         <v>0.8598154690176401</v>
       </c>
       <c r="BS56" t="n">
-        <v>0.9483575893463186</v>
+        <v>0.9483575893463189</v>
       </c>
       <c r="BT56" t="n">
         <v>0.8220237021390168</v>
@@ -21467,7 +21207,7 @@
         <v>0.8113397907274044</v>
       </c>
       <c r="BV56" t="n">
-        <v>0.8901383418766022</v>
+        <v>0.890138341876602</v>
       </c>
       <c r="BW56" t="n">
         <v>0.8500568251708955</v>
@@ -21548,7 +21288,7 @@
         <v>0.8094285501694813</v>
       </c>
       <c r="CW56" t="n">
-        <v>0.8465010448451725</v>
+        <v>0.8465010448451726</v>
       </c>
       <c r="CX56" t="n">
         <v>0.9161437336108177</v>
@@ -21560,7 +21300,7 @@
         <v>0.8373859012221435</v>
       </c>
       <c r="DA56" t="n">
-        <v>0.8058293573535011</v>
+        <v>0.8058293573535013</v>
       </c>
       <c r="DB56" t="n">
         <v>0.8676013785592664</v>
@@ -21575,7 +21315,7 @@
         <v>0.9059598716938645</v>
       </c>
       <c r="DF56" t="n">
-        <v>0.8358717621000279</v>
+        <v>0.835871762100028</v>
       </c>
       <c r="DG56" t="n">
         <v>0.8243662698324996</v>
@@ -21590,7 +21330,7 @@
         <v>0.908164852335707</v>
       </c>
       <c r="DK56" t="n">
-        <v>0.8844837736456668</v>
+        <v>0.8844837736456665</v>
       </c>
       <c r="DL56" t="n">
         <v>0.7887111883920203</v>
@@ -21602,7 +21342,7 @@
         <v>0.8655478277744175</v>
       </c>
       <c r="DO56" t="n">
-        <v>0.8699952086862138</v>
+        <v>0.8699952086862139</v>
       </c>
       <c r="DP56" t="n">
         <v>0.8540895091507978</v>
@@ -21622,7 +21362,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>0.3951754544198133</v>
+        <v>0.3951754544198132</v>
       </c>
       <c r="B57" t="n">
         <v>0.5703885420395852</v>
@@ -21703,7 +21443,7 @@
         <v>0.8459894727904487</v>
       </c>
       <c r="AB57" t="n">
-        <v>0.7591034999743952</v>
+        <v>0.7591034999743951</v>
       </c>
       <c r="AC57" t="n">
         <v>0.8738157190433875</v>
@@ -21733,7 +21473,7 @@
         <v>0.8758287613977573</v>
       </c>
       <c r="AL57" t="n">
-        <v>0.8636758966841606</v>
+        <v>0.8636758966841607</v>
       </c>
       <c r="AM57" t="n">
         <v>0.8289999636477288</v>
@@ -21796,7 +21536,7 @@
         <v>0.8504635487157751</v>
       </c>
       <c r="BG57" t="n">
-        <v>0.8804295220268576</v>
+        <v>0.8804295220268578</v>
       </c>
       <c r="BH57" t="n">
         <v>0.797216343704565</v>
@@ -21853,7 +21593,7 @@
         <v>0.8558959808493112</v>
       </c>
       <c r="BZ57" t="n">
-        <v>0.8018007467525633</v>
+        <v>0.8018007467525632</v>
       </c>
       <c r="CA57" t="n">
         <v>0.8269293584231954</v>
@@ -21883,7 +21623,7 @@
         <v>0.8739851553558869</v>
       </c>
       <c r="CJ57" t="n">
-        <v>0.8432251874720312</v>
+        <v>0.8432251874720311</v>
       </c>
       <c r="CK57" t="n">
         <v>0.8125416543028837</v>
@@ -21898,10 +21638,10 @@
         <v>0.8372068874580991</v>
       </c>
       <c r="CO57" t="n">
-        <v>0.8486724062791079</v>
+        <v>0.8486724062791081</v>
       </c>
       <c r="CP57" t="n">
-        <v>0.8497866293517186</v>
+        <v>0.8497866293517184</v>
       </c>
       <c r="CQ57" t="n">
         <v>0.7875258802469287</v>
@@ -21928,7 +21668,7 @@
         <v>0.8944773872417829</v>
       </c>
       <c r="CY57" t="n">
-        <v>0.7166666190706535</v>
+        <v>0.7166666190706538</v>
       </c>
       <c r="CZ57" t="n">
         <v>0.7986377646122956</v>
@@ -21991,7 +21731,7 @@
         <v>0.7944428347249967</v>
       </c>
       <c r="DT57" t="n">
-        <v>0.8325524328532985</v>
+        <v>0.8325524328532986</v>
       </c>
     </row>
     <row r="58">
@@ -22032,7 +21772,7 @@
         <v>0.8223764978448775</v>
       </c>
       <c r="M58" t="n">
-        <v>0.6904543833926122</v>
+        <v>0.6904543833926121</v>
       </c>
       <c r="N58" t="n">
         <v>0.806110998041312</v>
@@ -22044,16 +21784,16 @@
         <v>0.7865472353249782</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.8748933558486609</v>
+        <v>0.8748933558486608</v>
       </c>
       <c r="R58" t="n">
-        <v>0.7766149731550481</v>
+        <v>0.7766149731550479</v>
       </c>
       <c r="S58" t="n">
         <v>0.7697271674220258</v>
       </c>
       <c r="T58" t="n">
-        <v>0.7821267965426389</v>
+        <v>0.7821267965426392</v>
       </c>
       <c r="U58" t="n">
         <v>0.4719775041469282</v>
@@ -22113,7 +21853,7 @@
         <v>0.7782212976783468</v>
       </c>
       <c r="AN58" t="n">
-        <v>0.8143201838928392</v>
+        <v>0.8143201838928393</v>
       </c>
       <c r="AO58" t="n">
         <v>0.8457237705038477</v>
@@ -22137,10 +21877,10 @@
         <v>0.8115306087288255</v>
       </c>
       <c r="AV58" t="n">
-        <v>0.7513113236779164</v>
+        <v>0.7513113236779163</v>
       </c>
       <c r="AW58" t="n">
-        <v>0.781138199813903</v>
+        <v>0.7811381998139031</v>
       </c>
       <c r="AX58" t="n">
         <v>0.6242224446412672</v>
@@ -22191,7 +21931,7 @@
         <v>0.8287576223292683</v>
       </c>
       <c r="BN58" t="n">
-        <v>0.7475413801319941</v>
+        <v>0.7475413801319939</v>
       </c>
       <c r="BO58" t="n">
         <v>0.7728861576357284</v>
@@ -22209,7 +21949,7 @@
         <v>0.9046485998725946</v>
       </c>
       <c r="BT58" t="n">
-        <v>0.7027288951536557</v>
+        <v>0.7027288951536554</v>
       </c>
       <c r="BU58" t="n">
         <v>0.6924842853686298</v>
@@ -22221,7 +21961,7 @@
         <v>0.7615548632861748</v>
       </c>
       <c r="BX58" t="n">
-        <v>0.7929773547683789</v>
+        <v>0.7929773547683788</v>
       </c>
       <c r="BY58" t="n">
         <v>0.810404809355603</v>
@@ -22230,7 +21970,7 @@
         <v>0.7530689823849616</v>
       </c>
       <c r="CA58" t="n">
-        <v>0.7790271864574775</v>
+        <v>0.7790271864574774</v>
       </c>
       <c r="CB58" t="n">
         <v>0.8076389460476909</v>
@@ -22266,13 +22006,13 @@
         <v>0.8356734044150187</v>
       </c>
       <c r="CM58" t="n">
-        <v>0.8050363264949127</v>
+        <v>0.8050363264949126</v>
       </c>
       <c r="CN58" t="n">
         <v>0.7923231836092071</v>
       </c>
       <c r="CO58" t="n">
-        <v>0.8015827903608923</v>
+        <v>0.8015827903608922</v>
       </c>
       <c r="CP58" t="n">
         <v>0.8101992534426118</v>
@@ -22317,10 +22057,10 @@
         <v>0.8485665256907745</v>
       </c>
       <c r="DD58" t="n">
-        <v>0.7178034282096379</v>
+        <v>0.7178034282096382</v>
       </c>
       <c r="DE58" t="n">
-        <v>0.8395742427948062</v>
+        <v>0.8395742427948064</v>
       </c>
       <c r="DF58" t="n">
         <v>0.7418452100118715</v>
@@ -22359,7 +22099,7 @@
         <v>0.8297639605668445</v>
       </c>
       <c r="DR58" t="n">
-        <v>0.8140192443898014</v>
+        <v>0.8140192443898017</v>
       </c>
       <c r="DS58" t="n">
         <v>0.7977370888452486</v>
@@ -22376,13 +22116,13 @@
         <v>0.5524047861584684</v>
       </c>
       <c r="C59" t="n">
-        <v>0.804167273111679</v>
+        <v>0.8041672731116789</v>
       </c>
       <c r="D59" t="n">
         <v>0.848890209430458</v>
       </c>
       <c r="E59" t="n">
-        <v>0.7854458302559059</v>
+        <v>0.785445830255906</v>
       </c>
       <c r="F59" t="n">
         <v>0.7792838233806113</v>
@@ -22430,7 +22170,7 @@
         <v>0.7207888859058218</v>
       </c>
       <c r="U59" t="n">
-        <v>0.3687894903753763</v>
+        <v>0.3687894903753764</v>
       </c>
       <c r="V59" t="n">
         <v>0.5902063081151311</v>
@@ -22481,7 +22221,7 @@
         <v>0.8002703358558895</v>
       </c>
       <c r="AL59" t="n">
-        <v>0.7658026983768532</v>
+        <v>0.7658026983768531</v>
       </c>
       <c r="AM59" t="n">
         <v>0.7124896991047942</v>
@@ -22502,13 +22242,13 @@
         <v>0.808441140031284</v>
       </c>
       <c r="AS59" t="n">
-        <v>0.7429473413894891</v>
+        <v>0.7429473413894889</v>
       </c>
       <c r="AT59" t="n">
         <v>0.8214198832757406</v>
       </c>
       <c r="AU59" t="n">
-        <v>0.7537131487472293</v>
+        <v>0.7537131487472295</v>
       </c>
       <c r="AV59" t="n">
         <v>0.6853482090046306</v>
@@ -22520,7 +22260,7 @@
         <v>0.5317627703705908</v>
       </c>
       <c r="AY59" t="n">
-        <v>0.6869742742415161</v>
+        <v>0.686974274241516</v>
       </c>
       <c r="AZ59" t="n">
         <v>0.6860254304733661</v>
@@ -22532,7 +22272,7 @@
         <v>0.6050342993304068</v>
       </c>
       <c r="BC59" t="n">
-        <v>0.6184443053091434</v>
+        <v>0.6184443053091433</v>
       </c>
       <c r="BD59" t="n">
         <v>0.7311090799699564</v>
@@ -22541,7 +22281,7 @@
         <v>0.7297633064462369</v>
       </c>
       <c r="BF59" t="n">
-        <v>0.7470527449692378</v>
+        <v>0.7470527449692377</v>
       </c>
       <c r="BG59" t="n">
         <v>0.8341201741951968</v>
@@ -22589,7 +22329,7 @@
         <v>0.6094495099369998</v>
       </c>
       <c r="BV59" t="n">
-        <v>0.7540148114019244</v>
+        <v>0.7540148114019243</v>
       </c>
       <c r="BW59" t="n">
         <v>0.6977846048463091</v>
@@ -22598,7 +22338,7 @@
         <v>0.7354343808489644</v>
       </c>
       <c r="BY59" t="n">
-        <v>0.7492419213381546</v>
+        <v>0.7492419213381545</v>
       </c>
       <c r="BZ59" t="n">
         <v>0.68912884067671</v>
@@ -22667,7 +22407,7 @@
         <v>0.6499985107802302</v>
       </c>
       <c r="CV59" t="n">
-        <v>0.5622245281047736</v>
+        <v>0.5622245281047735</v>
       </c>
       <c r="CW59" t="n">
         <v>0.6895340596808575</v>
@@ -22694,7 +22434,7 @@
         <v>0.6379337321211335</v>
       </c>
       <c r="DE59" t="n">
-        <v>0.7853867107587219</v>
+        <v>0.785386710758722</v>
       </c>
       <c r="DF59" t="n">
         <v>0.6754547215260094</v>
@@ -22721,7 +22461,7 @@
         <v>0.7495744625106727</v>
       </c>
       <c r="DN59" t="n">
-        <v>0.7442612224061876</v>
+        <v>0.7442612224061875</v>
       </c>
       <c r="DO59" t="n">
         <v>0.7685566199961344</v>
@@ -22747,7 +22487,7 @@
         <v>0.3943993273623639</v>
       </c>
       <c r="B60" t="n">
-        <v>0.5461342090563639</v>
+        <v>0.5461342090563638</v>
       </c>
       <c r="C60" t="n">
         <v>0.8065894454450512</v>
@@ -22759,7 +22499,7 @@
         <v>0.7917595304497971</v>
       </c>
       <c r="F60" t="n">
-        <v>0.7371153188778637</v>
+        <v>0.7371153188778639</v>
       </c>
       <c r="G60" t="n">
         <v>0.7704802735535077</v>
@@ -22792,7 +22532,7 @@
         <v>0.6381633492793932</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.7872797844909433</v>
+        <v>0.787279784490943</v>
       </c>
       <c r="R60" t="n">
         <v>0.6455122099972387</v>
@@ -22819,7 +22559,7 @@
         <v>0.6898454867489888</v>
       </c>
       <c r="Z60" t="n">
-        <v>0.6970832253132052</v>
+        <v>0.697083225313205</v>
       </c>
       <c r="AA60" t="n">
         <v>0.6708580224793889</v>
@@ -22879,7 +22619,7 @@
         <v>0.6668298305243875</v>
       </c>
       <c r="AT60" t="n">
-        <v>0.7699317301661427</v>
+        <v>0.7699317301661429</v>
       </c>
       <c r="AU60" t="n">
         <v>0.6804571005467974</v>
@@ -22894,7 +22634,7 @@
         <v>0.4289030063015248</v>
       </c>
       <c r="AY60" t="n">
-        <v>0.6118977930891084</v>
+        <v>0.6118977930891085</v>
       </c>
       <c r="AZ60" t="n">
         <v>0.6118514493437575</v>
@@ -22957,7 +22697,7 @@
         <v>0.8029300771314365</v>
       </c>
       <c r="BT60" t="n">
-        <v>0.5175115533230853</v>
+        <v>0.5175115533230852</v>
       </c>
       <c r="BU60" t="n">
         <v>0.5125571513624994</v>
@@ -22990,7 +22730,7 @@
         <v>0.6160623133880765</v>
       </c>
       <c r="CE60" t="n">
-        <v>0.6022352592504566</v>
+        <v>0.6022352592504565</v>
       </c>
       <c r="CF60" t="n">
         <v>0.5926847376958959</v>
@@ -23050,7 +22790,7 @@
         <v>0.7470228470465775</v>
       </c>
       <c r="CY60" t="n">
-        <v>0.436985309482617</v>
+        <v>0.4369853094826171</v>
       </c>
       <c r="CZ60" t="n">
         <v>0.6005228368432566</v>
@@ -23071,22 +22811,22 @@
         <v>0.7158684485461108</v>
       </c>
       <c r="DF60" t="n">
-        <v>0.5951037249790174</v>
+        <v>0.5951037249790175</v>
       </c>
       <c r="DG60" t="n">
         <v>0.5004051085109892</v>
       </c>
       <c r="DH60" t="n">
-        <v>0.7712740419883378</v>
+        <v>0.7712740419883377</v>
       </c>
       <c r="DI60" t="n">
-        <v>0.2931042426406949</v>
+        <v>0.293104242640695</v>
       </c>
       <c r="DJ60" t="n">
         <v>0.6593778417396515</v>
       </c>
       <c r="DK60" t="n">
-        <v>0.64346089031425</v>
+        <v>0.6434608903142499</v>
       </c>
       <c r="DL60" t="n">
         <v>0.5038280918015758</v>
@@ -23101,7 +22841,7 @@
         <v>0.7117302105312289</v>
       </c>
       <c r="DP60" t="n">
-        <v>0.8740031156678432</v>
+        <v>0.8740031156678433</v>
       </c>
       <c r="DQ60" t="n">
         <v>0.8322335552661473</v>
@@ -23145,7 +22885,7 @@
         <v>0.38376138955682</v>
       </c>
       <c r="J61" t="n">
-        <v>0.4259203825366615</v>
+        <v>0.4259203825366614</v>
       </c>
       <c r="K61" t="n">
         <v>0.5659766242745514</v>
@@ -23163,7 +22903,7 @@
         <v>0.5395393300925402</v>
       </c>
       <c r="P61" t="n">
-        <v>0.5406624589832718</v>
+        <v>0.5406624589832719</v>
       </c>
       <c r="Q61" t="n">
         <v>0.7206538300547193</v>
@@ -23247,7 +22987,7 @@
         <v>0.5184022283091514</v>
       </c>
       <c r="AR61" t="n">
-        <v>0.6900548360912131</v>
+        <v>0.6900548360912132</v>
       </c>
       <c r="AS61" t="n">
         <v>0.5746678252521249</v>
@@ -23280,7 +23020,7 @@
         <v>0.3939661431274925</v>
       </c>
       <c r="BC61" t="n">
-        <v>0.422109525254408</v>
+        <v>0.4221095252544081</v>
       </c>
       <c r="BD61" t="n">
         <v>0.5650042847160108</v>
@@ -23310,7 +23050,7 @@
         <v>0.583002099694201</v>
       </c>
       <c r="BM61" t="n">
-        <v>0.6266498539648296</v>
+        <v>0.6266498539648295</v>
       </c>
       <c r="BN61" t="n">
         <v>0.4889550538394306</v>
@@ -23328,7 +23068,7 @@
         <v>0.5252528915424597</v>
       </c>
       <c r="BS61" t="n">
-        <v>0.7279008449512034</v>
+        <v>0.7279008449512033</v>
       </c>
       <c r="BT61" t="n">
         <v>0.4075222608686968</v>
@@ -23373,7 +23113,7 @@
         <v>0.4298692526153433</v>
       </c>
       <c r="CH61" t="n">
-        <v>0.5425901981327741</v>
+        <v>0.5425901981327742</v>
       </c>
       <c r="CI61" t="n">
         <v>0.64334623840372</v>
@@ -23436,13 +23176,13 @@
         <v>0.5301924969932529</v>
       </c>
       <c r="DC61" t="n">
-        <v>0.6513639013205743</v>
+        <v>0.6513639013205742</v>
       </c>
       <c r="DD61" t="n">
         <v>0.4379015552567741</v>
       </c>
       <c r="DE61" t="n">
-        <v>0.6308739428108509</v>
+        <v>0.630873942810851</v>
       </c>
       <c r="DF61" t="n">
         <v>0.5022336954120545</v>
@@ -23537,10 +23277,10 @@
         <v>0.4349787612909114</v>
       </c>
       <c r="P62" t="n">
-        <v>0.4337886919096923</v>
+        <v>0.4337886919096922</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.638772095549847</v>
+        <v>0.6387720955498472</v>
       </c>
       <c r="R62" t="n">
         <v>0.4570710844883328</v>
@@ -23573,7 +23313,7 @@
         <v>0.478586934849924</v>
       </c>
       <c r="AB62" t="n">
-        <v>0.2518091405777992</v>
+        <v>0.2518091405777991</v>
       </c>
       <c r="AC62" t="n">
         <v>0.5498369776760765</v>
@@ -23588,7 +23328,7 @@
         <v>0.4890899076078954</v>
       </c>
       <c r="AG62" t="n">
-        <v>0.4550033677912397</v>
+        <v>0.4550033677912398</v>
       </c>
       <c r="AH62" t="n">
         <v>0.3763946062758786</v>
@@ -23618,7 +23358,7 @@
         <v>0.4632500252733917</v>
       </c>
       <c r="AQ62" t="n">
-        <v>0.4076116985717907</v>
+        <v>0.4076116985717908</v>
       </c>
       <c r="AR62" t="n">
         <v>0.6093881948169845</v>
@@ -23666,7 +23406,7 @@
         <v>0.4838139619017106</v>
       </c>
       <c r="BG62" t="n">
-        <v>0.6644219975722967</v>
+        <v>0.6644219975722969</v>
       </c>
       <c r="BH62" t="n">
         <v>0.3639307643101233</v>
@@ -23735,7 +23475,7 @@
         <v>0.3746257042502641</v>
       </c>
       <c r="CD62" t="n">
-        <v>0.4251364321689156</v>
+        <v>0.4251364321689155</v>
       </c>
       <c r="CE62" t="n">
         <v>0.3984666178512676</v>
@@ -23756,7 +23496,7 @@
         <v>0.4457966608671031</v>
       </c>
       <c r="CK62" t="n">
-        <v>0.3616199206266525</v>
+        <v>0.3616199206266527</v>
       </c>
       <c r="CL62" t="n">
         <v>0.5805851808588351</v>
@@ -23792,10 +23532,10 @@
         <v>0.233187378101863</v>
       </c>
       <c r="CW62" t="n">
-        <v>0.4073498333503376</v>
+        <v>0.4073498333503377</v>
       </c>
       <c r="CX62" t="n">
-        <v>0.5699311402365804</v>
+        <v>0.5699311402365805</v>
       </c>
       <c r="CY62" t="n">
         <v>0.2262241032614331</v>
@@ -23825,7 +23565,7 @@
         <v>0.2834058806948613</v>
       </c>
       <c r="DH62" t="n">
-        <v>0.6081703225108483</v>
+        <v>0.6081703225108485</v>
       </c>
       <c r="DI62" t="n">
         <v>0.1209685087515786</v>
@@ -23846,7 +23586,7 @@
         <v>0.4913123131513731</v>
       </c>
       <c r="DO62" t="n">
-        <v>0.5576663215464065</v>
+        <v>0.5576663215464064</v>
       </c>
       <c r="DP62" t="n">
         <v>0.8609771237373968</v>
@@ -23884,7 +23624,7 @@
         <v>0.5364077512951106</v>
       </c>
       <c r="G63" t="n">
-        <v>0.5217276287476161</v>
+        <v>0.521727628747616</v>
       </c>
       <c r="H63" t="n">
         <v>0.2555170130221591</v>
@@ -23914,7 +23654,7 @@
         <v>0.3258066193958812</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.5438163181474404</v>
+        <v>0.5438163181474405</v>
       </c>
       <c r="R63" t="n">
         <v>0.3527083825249613</v>
@@ -23995,10 +23735,10 @@
         <v>0.2982065145696872</v>
       </c>
       <c r="AR63" t="n">
-        <v>0.5160549610225795</v>
+        <v>0.5160549610225794</v>
       </c>
       <c r="AS63" t="n">
-        <v>0.3612817466431136</v>
+        <v>0.3612817466431135</v>
       </c>
       <c r="AT63" t="n">
         <v>0.5237999448360047</v>
@@ -24112,7 +23852,7 @@
         <v>0.322422518763374</v>
       </c>
       <c r="CE63" t="n">
-        <v>0.2930882445641561</v>
+        <v>0.2930882445641562</v>
       </c>
       <c r="CF63" t="n">
         <v>0.3007417513290626</v>
@@ -24229,7 +23969,7 @@
         <v>0.8131537148994978</v>
       </c>
       <c r="DR63" t="n">
-        <v>0.6314883898884958</v>
+        <v>0.6314883898884956</v>
       </c>
       <c r="DS63" t="n">
         <v>0.805853589046549</v>
@@ -24312,7 +24052,7 @@
         <v>0.2663606060198725</v>
       </c>
       <c r="Y64" t="n">
-        <v>0.2884753978837505</v>
+        <v>0.2884753978837506</v>
       </c>
       <c r="Z64" t="n">
         <v>0.2984117297427507</v>
@@ -24321,7 +24061,7 @@
         <v>0.2648503183960304</v>
       </c>
       <c r="AB64" t="n">
-        <v>0.09012648136015386</v>
+        <v>0.09012648136015387</v>
       </c>
       <c r="AC64" t="n">
         <v>0.3340497093001388</v>
@@ -24441,7 +24181,7 @@
         <v>0.2208848958993192</v>
       </c>
       <c r="BP64" t="n">
-        <v>0.3372768258448957</v>
+        <v>0.3372768258448958</v>
       </c>
       <c r="BQ64" t="n">
         <v>0.3023854690438902</v>
@@ -24465,7 +24205,7 @@
         <v>0.2232504984911121</v>
       </c>
       <c r="BX64" t="n">
-        <v>0.2785729575003943</v>
+        <v>0.2785729575003944</v>
       </c>
       <c r="BY64" t="n">
         <v>0.2625251464027266</v>
@@ -24477,7 +24217,7 @@
         <v>0.2498696136144475</v>
       </c>
       <c r="CB64" t="n">
-        <v>0.2869167221430864</v>
+        <v>0.2869167221430865</v>
       </c>
       <c r="CC64" t="n">
         <v>0.1791359061503787</v>
@@ -24537,7 +24277,7 @@
         <v>0.1547530003130874</v>
       </c>
       <c r="CV64" t="n">
-        <v>0.08278669334535234</v>
+        <v>0.08278669334535235</v>
       </c>
       <c r="CW64" t="n">
         <v>0.2055247368744019</v>
@@ -24653,7 +24393,7 @@
         <v>0.06247901557056894</v>
       </c>
       <c r="N65" t="n">
-        <v>0.2120983683759426</v>
+        <v>0.2120983683759425</v>
       </c>
       <c r="O65" t="n">
         <v>0.1459770711589911</v>
@@ -24695,7 +24435,7 @@
         <v>0.1725347549447805</v>
       </c>
       <c r="AB65" t="n">
-        <v>0.09012648136015386</v>
+        <v>0.09012648136015387</v>
       </c>
       <c r="AC65" t="n">
         <v>0.2319605120911241</v>
@@ -24911,7 +24651,7 @@
         <v>0.08792117977245913</v>
       </c>
       <c r="CV65" t="n">
-        <v>0.08278669334535234</v>
+        <v>0.08278669334535235</v>
       </c>
       <c r="CW65" t="n">
         <v>0.1267876372633077</v>
@@ -24988,13 +24728,13 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>0.3931630120024135</v>
+        <v>0.3931630120024134</v>
       </c>
       <c r="B66" t="n">
-        <v>0.5145738770844119</v>
+        <v>0.5145738770844118</v>
       </c>
       <c r="C66" t="n">
-        <v>0.813925382344265</v>
+        <v>0.8139253823442651</v>
       </c>
       <c r="D66" t="n">
         <v>0.7879521686619827</v>
@@ -25069,7 +24809,7 @@
         <v>0.1010132376394819</v>
       </c>
       <c r="AB66" t="n">
-        <v>0.09012648136015386</v>
+        <v>0.09012648136015387</v>
       </c>
       <c r="AC66" t="n">
         <v>0.1464147569495</v>
@@ -25219,7 +24959,7 @@
         <v>0.1013649708248241</v>
       </c>
       <c r="BZ66" t="n">
-        <v>0.07622821959961545</v>
+        <v>0.07622821959961547</v>
       </c>
       <c r="CA66" t="n">
         <v>0.09759380226758377</v>
@@ -25249,7 +24989,7 @@
         <v>0.1561289765921976</v>
       </c>
       <c r="CJ66" t="n">
-        <v>0.09129748077099567</v>
+        <v>0.0912974807709957</v>
       </c>
       <c r="CK66" t="n">
         <v>0.0530773306499351</v>
@@ -25285,7 +25025,7 @@
         <v>0.04558541220504529</v>
       </c>
       <c r="CV66" t="n">
-        <v>0.08278669334535234</v>
+        <v>0.08278669334535235</v>
       </c>
       <c r="CW66" t="n">
         <v>0.07064675493548334</v>
@@ -25443,7 +25183,7 @@
         <v>0.05368177369184701</v>
       </c>
       <c r="AB67" t="n">
-        <v>0.09012648136015386</v>
+        <v>0.09012648136015387</v>
       </c>
       <c r="AC67" t="n">
         <v>0.08346702048312594</v>
@@ -25509,7 +25249,7 @@
         <v>0.03668774385561227</v>
       </c>
       <c r="AX67" t="n">
-        <v>0.01764827613349335</v>
+        <v>0.01764827613349336</v>
       </c>
       <c r="AY67" t="n">
         <v>0.07934294747113523</v>
@@ -25536,13 +25276,13 @@
         <v>0.06005608356187035</v>
       </c>
       <c r="BG67" t="n">
-        <v>0.1790102914352726</v>
+        <v>0.1790102914352727</v>
       </c>
       <c r="BH67" t="n">
         <v>0.02753275941950321</v>
       </c>
       <c r="BI67" t="n">
-        <v>0.01648000393033355</v>
+        <v>0.01648000393033356</v>
       </c>
       <c r="BJ67" t="n">
         <v>0.0186030449878764</v>
@@ -25560,7 +25300,7 @@
         <v>0.03074893938158007</v>
       </c>
       <c r="BO67" t="n">
-        <v>0.03717238188955368</v>
+        <v>0.03717238188955367</v>
       </c>
       <c r="BP67" t="n">
         <v>0.08550443974189105</v>
@@ -25593,13 +25333,13 @@
         <v>0.05478506687337206</v>
       </c>
       <c r="BZ67" t="n">
-        <v>0.07622821959961545</v>
+        <v>0.07622821959961547</v>
       </c>
       <c r="CA67" t="n">
         <v>0.05346593440544462</v>
       </c>
       <c r="CB67" t="n">
-        <v>0.06856579121103155</v>
+        <v>0.06856579121103154</v>
       </c>
       <c r="CC67" t="n">
         <v>0.05957518687435016</v>
@@ -25620,10 +25360,10 @@
         <v>0.05807042534464118</v>
       </c>
       <c r="CI67" t="n">
-        <v>0.09128669758687129</v>
+        <v>0.09128669758687132</v>
       </c>
       <c r="CJ67" t="n">
-        <v>0.09129748077099567</v>
+        <v>0.0912974807709957</v>
       </c>
       <c r="CK67" t="n">
         <v>0.03019600717737167</v>
@@ -25659,7 +25399,7 @@
         <v>0.02521253757738138</v>
       </c>
       <c r="CV67" t="n">
-        <v>0.08278669334535234</v>
+        <v>0.08278669334535235</v>
       </c>
       <c r="CW67" t="n">
         <v>0.03717601439446865</v>
@@ -25817,7 +25557,7 @@
         <v>0.02913241199904758</v>
       </c>
       <c r="AB68" t="n">
-        <v>0.09012648136015386</v>
+        <v>0.09012648136015387</v>
       </c>
       <c r="AC68" t="n">
         <v>0.04431360985395993</v>
@@ -25871,7 +25611,7 @@
         <v>0.05555163275318919</v>
       </c>
       <c r="AT68" t="n">
-        <v>0.07769421791017103</v>
+        <v>0.07769421791017102</v>
       </c>
       <c r="AU68" t="n">
         <v>0.06075616275773723</v>
@@ -25883,7 +25623,7 @@
         <v>0.02133473576170346</v>
       </c>
       <c r="AX68" t="n">
-        <v>0.01764827613349335</v>
+        <v>0.01764827613349336</v>
       </c>
       <c r="AY68" t="n">
         <v>0.07934294747113523</v>
@@ -25916,7 +25656,7 @@
         <v>0.01956740195277552</v>
       </c>
       <c r="BI68" t="n">
-        <v>0.01648000393033355</v>
+        <v>0.01648000393033356</v>
       </c>
       <c r="BJ68" t="n">
         <v>0.0186030449878764</v>
@@ -25967,13 +25707,13 @@
         <v>0.05478506687337206</v>
       </c>
       <c r="BZ68" t="n">
-        <v>0.07622821959961545</v>
+        <v>0.07622821959961547</v>
       </c>
       <c r="CA68" t="n">
         <v>0.02954639507255635</v>
       </c>
       <c r="CB68" t="n">
-        <v>0.06856579121103155</v>
+        <v>0.06856579121103154</v>
       </c>
       <c r="CC68" t="n">
         <v>0.05957518687435016</v>
@@ -25997,7 +25737,7 @@
         <v>0.04924515769851412</v>
       </c>
       <c r="CJ68" t="n">
-        <v>0.09129748077099567</v>
+        <v>0.0912974807709957</v>
       </c>
       <c r="CK68" t="n">
         <v>0.02087262101417461</v>
@@ -26033,7 +25773,7 @@
         <v>0.01817618090371005</v>
       </c>
       <c r="CV68" t="n">
-        <v>0.08278669334535234</v>
+        <v>0.08278669334535235</v>
       </c>
       <c r="CW68" t="n">
         <v>0.02182141660041219</v>
@@ -26096,7 +25836,7 @@
         <v>0.6566946001552909</v>
       </c>
       <c r="DQ68" t="n">
-        <v>0.7200329200704554</v>
+        <v>0.7200329200704555</v>
       </c>
       <c r="DR68" t="n">
         <v>0.467053918915643</v>
@@ -26191,7 +25931,7 @@
         <v>0.02008422302054496</v>
       </c>
       <c r="AB69" t="n">
-        <v>0.09012648136015386</v>
+        <v>0.09012648136015387</v>
       </c>
       <c r="AC69" t="n">
         <v>0.02538647237635149</v>
@@ -26245,7 +25985,7 @@
         <v>0.05555163275318919</v>
       </c>
       <c r="AT69" t="n">
-        <v>0.07769421791017103</v>
+        <v>0.07769421791017102</v>
       </c>
       <c r="AU69" t="n">
         <v>0.06075616275773723</v>
@@ -26257,7 +25997,7 @@
         <v>0.01591951561861416</v>
       </c>
       <c r="AX69" t="n">
-        <v>0.01764827613349335</v>
+        <v>0.01764827613349336</v>
       </c>
       <c r="AY69" t="n">
         <v>0.07934294747113523</v>
@@ -26290,7 +26030,7 @@
         <v>0.01956740195277552</v>
       </c>
       <c r="BI69" t="n">
-        <v>0.01648000393033355</v>
+        <v>0.01648000393033356</v>
       </c>
       <c r="BJ69" t="n">
         <v>0.0186030449878764</v>
@@ -26341,13 +26081,13 @@
         <v>0.05478506687337206</v>
       </c>
       <c r="BZ69" t="n">
-        <v>0.07622821959961545</v>
+        <v>0.07622821959961547</v>
       </c>
       <c r="CA69" t="n">
         <v>0.0195211802388755</v>
       </c>
       <c r="CB69" t="n">
-        <v>0.06856579121103155</v>
+        <v>0.06856579121103154</v>
       </c>
       <c r="CC69" t="n">
         <v>0.05957518687435016</v>
@@ -26371,7 +26111,7 @@
         <v>0.02755636464488416</v>
       </c>
       <c r="CJ69" t="n">
-        <v>0.09129748077099567</v>
+        <v>0.0912974807709957</v>
       </c>
       <c r="CK69" t="n">
         <v>0.01561496764524501</v>
@@ -26386,7 +26126,7 @@
         <v>0.0573268007425663</v>
       </c>
       <c r="CO69" t="n">
-        <v>0.0196560540162535</v>
+        <v>0.01965605401625351</v>
       </c>
       <c r="CP69" t="n">
         <v>0.07467502618592681</v>
@@ -26407,7 +26147,7 @@
         <v>0.01817618090371005</v>
       </c>
       <c r="CV69" t="n">
-        <v>0.08278669334535234</v>
+        <v>0.08278669334535235</v>
       </c>
       <c r="CW69" t="n">
         <v>0.01580750972388531</v>
@@ -26565,7 +26305,7 @@
         <v>0.02008422302054496</v>
       </c>
       <c r="AB70" t="n">
-        <v>0.09012648136015386</v>
+        <v>0.09012648136015387</v>
       </c>
       <c r="AC70" t="n">
         <v>0.01820767994291349</v>
@@ -26619,7 +26359,7 @@
         <v>0.05555163275318919</v>
       </c>
       <c r="AT70" t="n">
-        <v>0.07769421791017103</v>
+        <v>0.07769421791017102</v>
       </c>
       <c r="AU70" t="n">
         <v>0.06075616275773723</v>
@@ -26631,7 +26371,7 @@
         <v>0.01591951561861416</v>
       </c>
       <c r="AX70" t="n">
-        <v>0.01764827613349335</v>
+        <v>0.01764827613349336</v>
       </c>
       <c r="AY70" t="n">
         <v>0.07934294747113523</v>
@@ -26664,7 +26404,7 @@
         <v>0.01956740195277552</v>
       </c>
       <c r="BI70" t="n">
-        <v>0.01648000393033355</v>
+        <v>0.01648000393033356</v>
       </c>
       <c r="BJ70" t="n">
         <v>0.0186030449878764</v>
@@ -26715,13 +26455,13 @@
         <v>0.05478506687337206</v>
       </c>
       <c r="BZ70" t="n">
-        <v>0.07622821959961545</v>
+        <v>0.07622821959961547</v>
       </c>
       <c r="CA70" t="n">
         <v>0.01478917663642575</v>
       </c>
       <c r="CB70" t="n">
-        <v>0.06856579121103155</v>
+        <v>0.06856579121103154</v>
       </c>
       <c r="CC70" t="n">
         <v>0.05957518687435016</v>
@@ -26745,7 +26485,7 @@
         <v>0.01882744054754126</v>
       </c>
       <c r="CJ70" t="n">
-        <v>0.09129748077099567</v>
+        <v>0.0912974807709957</v>
       </c>
       <c r="CK70" t="n">
         <v>0.01561496764524501</v>
@@ -26781,7 +26521,7 @@
         <v>0.01817618090371005</v>
       </c>
       <c r="CV70" t="n">
-        <v>0.08278669334535234</v>
+        <v>0.08278669334535235</v>
       </c>
       <c r="CW70" t="n">
         <v>0.01580750972388531</v>
@@ -26841,7 +26581,7 @@
         <v>0.06337637248191332</v>
       </c>
       <c r="DP70" t="n">
-        <v>0.5228444532930975</v>
+        <v>0.5228444532930976</v>
       </c>
       <c r="DQ70" t="n">
         <v>0.6519355599055747</v>
@@ -26939,7 +26679,7 @@
         <v>0.02008422302054496</v>
       </c>
       <c r="AB71" t="n">
-        <v>0.09012648136015386</v>
+        <v>0.09012648136015387</v>
       </c>
       <c r="AC71" t="n">
         <v>0.01820767994291349</v>
@@ -26993,7 +26733,7 @@
         <v>0.05555163275318919</v>
       </c>
       <c r="AT71" t="n">
-        <v>0.07769421791017103</v>
+        <v>0.07769421791017102</v>
       </c>
       <c r="AU71" t="n">
         <v>0.06075616275773723</v>
@@ -27005,7 +26745,7 @@
         <v>0.01591951561861416</v>
       </c>
       <c r="AX71" t="n">
-        <v>0.01764827613349335</v>
+        <v>0.01764827613349336</v>
       </c>
       <c r="AY71" t="n">
         <v>0.07934294747113523</v>
@@ -27038,7 +26778,7 @@
         <v>0.01956740195277552</v>
       </c>
       <c r="BI71" t="n">
-        <v>0.01648000393033355</v>
+        <v>0.01648000393033356</v>
       </c>
       <c r="BJ71" t="n">
         <v>0.0186030449878764</v>
@@ -27089,13 +26829,13 @@
         <v>0.05478506687337206</v>
       </c>
       <c r="BZ71" t="n">
-        <v>0.07622821959961545</v>
+        <v>0.07622821959961547</v>
       </c>
       <c r="CA71" t="n">
         <v>0.01478917663642575</v>
       </c>
       <c r="CB71" t="n">
-        <v>0.06856579121103155</v>
+        <v>0.06856579121103154</v>
       </c>
       <c r="CC71" t="n">
         <v>0.05957518687435016</v>
@@ -27119,7 +26859,7 @@
         <v>0.01882744054754126</v>
       </c>
       <c r="CJ71" t="n">
-        <v>0.09129748077099567</v>
+        <v>0.0912974807709957</v>
       </c>
       <c r="CK71" t="n">
         <v>0.01561496764524501</v>
@@ -27155,7 +26895,7 @@
         <v>0.01817618090371005</v>
       </c>
       <c r="CV71" t="n">
-        <v>0.08278669334535234</v>
+        <v>0.08278669334535235</v>
       </c>
       <c r="CW71" t="n">
         <v>0.01580750972388531</v>
@@ -27313,7 +27053,7 @@
         <v>0.02008422302054496</v>
       </c>
       <c r="AB72" t="n">
-        <v>0.09012648136015386</v>
+        <v>0.09012648136015387</v>
       </c>
       <c r="AC72" t="n">
         <v>0.01820767994291349</v>
@@ -27367,7 +27107,7 @@
         <v>0.05555163275318919</v>
       </c>
       <c r="AT72" t="n">
-        <v>0.07769421791017103</v>
+        <v>0.07769421791017102</v>
       </c>
       <c r="AU72" t="n">
         <v>0.06075616275773723</v>
@@ -27379,7 +27119,7 @@
         <v>0.01591951561861416</v>
       </c>
       <c r="AX72" t="n">
-        <v>0.01764827613349335</v>
+        <v>0.01764827613349336</v>
       </c>
       <c r="AY72" t="n">
         <v>0.07934294747113523</v>
@@ -27412,7 +27152,7 @@
         <v>0.01956740195277552</v>
       </c>
       <c r="BI72" t="n">
-        <v>0.01648000393033355</v>
+        <v>0.01648000393033356</v>
       </c>
       <c r="BJ72" t="n">
         <v>0.0186030449878764</v>
@@ -27463,13 +27203,13 @@
         <v>0.05478506687337206</v>
       </c>
       <c r="BZ72" t="n">
-        <v>0.07622821959961545</v>
+        <v>0.07622821959961547</v>
       </c>
       <c r="CA72" t="n">
         <v>0.01478917663642575</v>
       </c>
       <c r="CB72" t="n">
-        <v>0.06856579121103155</v>
+        <v>0.06856579121103154</v>
       </c>
       <c r="CC72" t="n">
         <v>0.05957518687435016</v>
@@ -27493,7 +27233,7 @@
         <v>0.01882744054754126</v>
       </c>
       <c r="CJ72" t="n">
-        <v>0.09129748077099567</v>
+        <v>0.0912974807709957</v>
       </c>
       <c r="CK72" t="n">
         <v>0.01561496764524501</v>
@@ -27529,7 +27269,7 @@
         <v>0.01817618090371005</v>
       </c>
       <c r="CV72" t="n">
-        <v>0.08278669334535234</v>
+        <v>0.08278669334535235</v>
       </c>
       <c r="CW72" t="n">
         <v>0.01580750972388531</v>
@@ -27687,7 +27427,7 @@
         <v>0.02008422302054496</v>
       </c>
       <c r="AB73" t="n">
-        <v>0.09012648136015386</v>
+        <v>0.09012648136015387</v>
       </c>
       <c r="AC73" t="n">
         <v>0.01820767994291349</v>
@@ -27741,7 +27481,7 @@
         <v>0.05555163275318919</v>
       </c>
       <c r="AT73" t="n">
-        <v>0.07769421791017103</v>
+        <v>0.07769421791017102</v>
       </c>
       <c r="AU73" t="n">
         <v>0.06075616275773723</v>
@@ -27753,7 +27493,7 @@
         <v>0.01591951561861416</v>
       </c>
       <c r="AX73" t="n">
-        <v>0.01764827613349335</v>
+        <v>0.01764827613349336</v>
       </c>
       <c r="AY73" t="n">
         <v>0.07934294747113523</v>
@@ -27786,7 +27526,7 @@
         <v>0.01956740195277552</v>
       </c>
       <c r="BI73" t="n">
-        <v>0.01648000393033355</v>
+        <v>0.01648000393033356</v>
       </c>
       <c r="BJ73" t="n">
         <v>0.0186030449878764</v>
@@ -27837,13 +27577,13 @@
         <v>0.05478506687337206</v>
       </c>
       <c r="BZ73" t="n">
-        <v>0.07622821959961545</v>
+        <v>0.07622821959961547</v>
       </c>
       <c r="CA73" t="n">
         <v>0.01478917663642575</v>
       </c>
       <c r="CB73" t="n">
-        <v>0.06856579121103155</v>
+        <v>0.06856579121103154</v>
       </c>
       <c r="CC73" t="n">
         <v>0.05957518687435016</v>
@@ -27867,7 +27607,7 @@
         <v>0.01882744054754126</v>
       </c>
       <c r="CJ73" t="n">
-        <v>0.09129748077099567</v>
+        <v>0.0912974807709957</v>
       </c>
       <c r="CK73" t="n">
         <v>0.01561496764524501</v>
@@ -27903,7 +27643,7 @@
         <v>0.01817618090371005</v>
       </c>
       <c r="CV73" t="n">
-        <v>0.08278669334535234</v>
+        <v>0.08278669334535235</v>
       </c>
       <c r="CW73" t="n">
         <v>0.01580750972388531</v>
@@ -27966,7 +27706,7 @@
         <v>0.2815019815076705</v>
       </c>
       <c r="DQ73" t="n">
-        <v>0.4997487562904102</v>
+        <v>0.4997487562904103</v>
       </c>
       <c r="DR73" t="n">
         <v>0.3142080696754012</v>
@@ -27989,7 +27729,7 @@
         <v>0.7905896227337194</v>
       </c>
       <c r="D74" t="n">
-        <v>0.501543289248134</v>
+        <v>0.5015432892481341</v>
       </c>
       <c r="E74" t="n">
         <v>0.7012212024825046</v>
@@ -28061,7 +27801,7 @@
         <v>0.02008422302054496</v>
       </c>
       <c r="AB74" t="n">
-        <v>0.09012648136015386</v>
+        <v>0.09012648136015387</v>
       </c>
       <c r="AC74" t="n">
         <v>0.01820767994291349</v>
@@ -28115,7 +27855,7 @@
         <v>0.05555163275318919</v>
       </c>
       <c r="AT74" t="n">
-        <v>0.07769421791017103</v>
+        <v>0.07769421791017102</v>
       </c>
       <c r="AU74" t="n">
         <v>0.06075616275773723</v>
@@ -28127,7 +27867,7 @@
         <v>0.01591951561861416</v>
       </c>
       <c r="AX74" t="n">
-        <v>0.01764827613349335</v>
+        <v>0.01764827613349336</v>
       </c>
       <c r="AY74" t="n">
         <v>0.07934294747113523</v>
@@ -28160,7 +27900,7 @@
         <v>0.01956740195277552</v>
       </c>
       <c r="BI74" t="n">
-        <v>0.01648000393033355</v>
+        <v>0.01648000393033356</v>
       </c>
       <c r="BJ74" t="n">
         <v>0.0186030449878764</v>
@@ -28211,13 +27951,13 @@
         <v>0.05478506687337206</v>
       </c>
       <c r="BZ74" t="n">
-        <v>0.07622821959961545</v>
+        <v>0.07622821959961547</v>
       </c>
       <c r="CA74" t="n">
         <v>0.01478917663642575</v>
       </c>
       <c r="CB74" t="n">
-        <v>0.06856579121103155</v>
+        <v>0.06856579121103154</v>
       </c>
       <c r="CC74" t="n">
         <v>0.05957518687435016</v>
@@ -28241,7 +27981,7 @@
         <v>0.01882744054754126</v>
       </c>
       <c r="CJ74" t="n">
-        <v>0.09129748077099567</v>
+        <v>0.0912974807709957</v>
       </c>
       <c r="CK74" t="n">
         <v>0.01561496764524501</v>
@@ -28277,7 +28017,7 @@
         <v>0.01817618090371005</v>
       </c>
       <c r="CV74" t="n">
-        <v>0.08278669334535234</v>
+        <v>0.08278669334535235</v>
       </c>
       <c r="CW74" t="n">
         <v>0.01580750972388531</v>
@@ -28435,7 +28175,7 @@
         <v>0.02008422302054496</v>
       </c>
       <c r="AB75" t="n">
-        <v>0.09012648136015386</v>
+        <v>0.09012648136015387</v>
       </c>
       <c r="AC75" t="n">
         <v>0.01820767994291349</v>
@@ -28489,7 +28229,7 @@
         <v>0.05555163275318919</v>
       </c>
       <c r="AT75" t="n">
-        <v>0.07769421791017103</v>
+        <v>0.07769421791017102</v>
       </c>
       <c r="AU75" t="n">
         <v>0.06075616275773723</v>
@@ -28501,7 +28241,7 @@
         <v>0.01591951561861416</v>
       </c>
       <c r="AX75" t="n">
-        <v>0.01764827613349335</v>
+        <v>0.01764827613349336</v>
       </c>
       <c r="AY75" t="n">
         <v>0.07934294747113523</v>
@@ -28534,7 +28274,7 @@
         <v>0.01956740195277552</v>
       </c>
       <c r="BI75" t="n">
-        <v>0.01648000393033355</v>
+        <v>0.01648000393033356</v>
       </c>
       <c r="BJ75" t="n">
         <v>0.0186030449878764</v>
@@ -28585,13 +28325,13 @@
         <v>0.05478506687337206</v>
       </c>
       <c r="BZ75" t="n">
-        <v>0.07622821959961545</v>
+        <v>0.07622821959961547</v>
       </c>
       <c r="CA75" t="n">
         <v>0.01478917663642575</v>
       </c>
       <c r="CB75" t="n">
-        <v>0.06856579121103155</v>
+        <v>0.06856579121103154</v>
       </c>
       <c r="CC75" t="n">
         <v>0.05957518687435016</v>
@@ -28615,7 +28355,7 @@
         <v>0.01882744054754126</v>
       </c>
       <c r="CJ75" t="n">
-        <v>0.09129748077099567</v>
+        <v>0.0912974807709957</v>
       </c>
       <c r="CK75" t="n">
         <v>0.01561496764524501</v>
@@ -28651,7 +28391,7 @@
         <v>0.01817618090371005</v>
       </c>
       <c r="CV75" t="n">
-        <v>0.08278669334535234</v>
+        <v>0.08278669334535235</v>
       </c>
       <c r="CW75" t="n">
         <v>0.01580750972388531</v>
@@ -28723,7 +28463,7 @@
         <v>0.6108276824037048</v>
       </c>
       <c r="DT75" t="n">
-        <v>0.470066621934362</v>
+        <v>0.4700666219343621</v>
       </c>
     </row>
     <row r="76">
@@ -28809,7 +28549,7 @@
         <v>0.02008422302054496</v>
       </c>
       <c r="AB76" t="n">
-        <v>0.09012648136015386</v>
+        <v>0.09012648136015387</v>
       </c>
       <c r="AC76" t="n">
         <v>0.01820767994291349</v>
@@ -28863,7 +28603,7 @@
         <v>0.05555163275318919</v>
       </c>
       <c r="AT76" t="n">
-        <v>0.07769421791017103</v>
+        <v>0.07769421791017102</v>
       </c>
       <c r="AU76" t="n">
         <v>0.06075616275773723</v>
@@ -28875,7 +28615,7 @@
         <v>0.01591951561861416</v>
       </c>
       <c r="AX76" t="n">
-        <v>0.01764827613349335</v>
+        <v>0.01764827613349336</v>
       </c>
       <c r="AY76" t="n">
         <v>0.07934294747113523</v>
@@ -28908,7 +28648,7 @@
         <v>0.01956740195277552</v>
       </c>
       <c r="BI76" t="n">
-        <v>0.01648000393033355</v>
+        <v>0.01648000393033356</v>
       </c>
       <c r="BJ76" t="n">
         <v>0.0186030449878764</v>
@@ -28959,13 +28699,13 @@
         <v>0.05478506687337206</v>
       </c>
       <c r="BZ76" t="n">
-        <v>0.07622821959961545</v>
+        <v>0.07622821959961547</v>
       </c>
       <c r="CA76" t="n">
         <v>0.01478917663642575</v>
       </c>
       <c r="CB76" t="n">
-        <v>0.06856579121103155</v>
+        <v>0.06856579121103154</v>
       </c>
       <c r="CC76" t="n">
         <v>0.05957518687435016</v>
@@ -28989,7 +28729,7 @@
         <v>0.01882744054754126</v>
       </c>
       <c r="CJ76" t="n">
-        <v>0.09129748077099567</v>
+        <v>0.0912974807709957</v>
       </c>
       <c r="CK76" t="n">
         <v>0.01561496764524501</v>
@@ -29025,7 +28765,7 @@
         <v>0.01817618090371005</v>
       </c>
       <c r="CV76" t="n">
-        <v>0.08278669334535234</v>
+        <v>0.08278669334535235</v>
       </c>
       <c r="CW76" t="n">
         <v>0.01580750972388531</v>
@@ -29183,7 +28923,7 @@
         <v>0.02008422302054496</v>
       </c>
       <c r="AB77" t="n">
-        <v>0.09012648136015386</v>
+        <v>0.09012648136015387</v>
       </c>
       <c r="AC77" t="n">
         <v>0.01820767994291349</v>
@@ -29237,7 +28977,7 @@
         <v>0.05555163275318919</v>
       </c>
       <c r="AT77" t="n">
-        <v>0.07769421791017103</v>
+        <v>0.07769421791017102</v>
       </c>
       <c r="AU77" t="n">
         <v>0.06075616275773723</v>
@@ -29249,7 +28989,7 @@
         <v>0.01591951561861416</v>
       </c>
       <c r="AX77" t="n">
-        <v>0.01764827613349335</v>
+        <v>0.01764827613349336</v>
       </c>
       <c r="AY77" t="n">
         <v>0.07934294747113523</v>
@@ -29282,7 +29022,7 @@
         <v>0.01956740195277552</v>
       </c>
       <c r="BI77" t="n">
-        <v>0.01648000393033355</v>
+        <v>0.01648000393033356</v>
       </c>
       <c r="BJ77" t="n">
         <v>0.0186030449878764</v>
@@ -29333,13 +29073,13 @@
         <v>0.05478506687337206</v>
       </c>
       <c r="BZ77" t="n">
-        <v>0.07622821959961545</v>
+        <v>0.07622821959961547</v>
       </c>
       <c r="CA77" t="n">
         <v>0.01478917663642575</v>
       </c>
       <c r="CB77" t="n">
-        <v>0.06856579121103155</v>
+        <v>0.06856579121103154</v>
       </c>
       <c r="CC77" t="n">
         <v>0.05957518687435016</v>
@@ -29363,7 +29103,7 @@
         <v>0.01882744054754126</v>
       </c>
       <c r="CJ77" t="n">
-        <v>0.09129748077099567</v>
+        <v>0.0912974807709957</v>
       </c>
       <c r="CK77" t="n">
         <v>0.01561496764524501</v>
@@ -29399,7 +29139,7 @@
         <v>0.01817618090371005</v>
       </c>
       <c r="CV77" t="n">
-        <v>0.08278669334535234</v>
+        <v>0.08278669334535235</v>
       </c>
       <c r="CW77" t="n">
         <v>0.01580750972388531</v>
@@ -29557,7 +29297,7 @@
         <v>0.02008422302054496</v>
       </c>
       <c r="AB78" t="n">
-        <v>0.09012648136015386</v>
+        <v>0.09012648136015387</v>
       </c>
       <c r="AC78" t="n">
         <v>0.01820767994291349</v>
@@ -29611,7 +29351,7 @@
         <v>0.05555163275318919</v>
       </c>
       <c r="AT78" t="n">
-        <v>0.07769421791017103</v>
+        <v>0.07769421791017102</v>
       </c>
       <c r="AU78" t="n">
         <v>0.06075616275773723</v>
@@ -29623,7 +29363,7 @@
         <v>0.01591951561861416</v>
       </c>
       <c r="AX78" t="n">
-        <v>0.01764827613349335</v>
+        <v>0.01764827613349336</v>
       </c>
       <c r="AY78" t="n">
         <v>0.07934294747113523</v>
@@ -29656,7 +29396,7 @@
         <v>0.01956740195277552</v>
       </c>
       <c r="BI78" t="n">
-        <v>0.01648000393033355</v>
+        <v>0.01648000393033356</v>
       </c>
       <c r="BJ78" t="n">
         <v>0.0186030449878764</v>
@@ -29707,13 +29447,13 @@
         <v>0.05478506687337206</v>
       </c>
       <c r="BZ78" t="n">
-        <v>0.07622821959961545</v>
+        <v>0.07622821959961547</v>
       </c>
       <c r="CA78" t="n">
         <v>0.01478917663642575</v>
       </c>
       <c r="CB78" t="n">
-        <v>0.06856579121103155</v>
+        <v>0.06856579121103154</v>
       </c>
       <c r="CC78" t="n">
         <v>0.05957518687435016</v>
@@ -29737,7 +29477,7 @@
         <v>0.01882744054754126</v>
       </c>
       <c r="CJ78" t="n">
-        <v>0.09129748077099567</v>
+        <v>0.0912974807709957</v>
       </c>
       <c r="CK78" t="n">
         <v>0.01561496764524501</v>
@@ -29773,7 +29513,7 @@
         <v>0.01817618090371005</v>
       </c>
       <c r="CV78" t="n">
-        <v>0.08278669334535234</v>
+        <v>0.08278669334535235</v>
       </c>
       <c r="CW78" t="n">
         <v>0.01580750972388531</v>
@@ -29856,7 +29596,7 @@
         <v>0.4432388677292275</v>
       </c>
       <c r="C79" t="n">
-        <v>0.7297027742460855</v>
+        <v>0.7297027742460857</v>
       </c>
       <c r="D79" t="n">
         <v>0.1913736818962201</v>
@@ -29931,7 +29671,7 @@
         <v>0.02008422302054496</v>
       </c>
       <c r="AB79" t="n">
-        <v>0.09012648136015386</v>
+        <v>0.09012648136015387</v>
       </c>
       <c r="AC79" t="n">
         <v>0.01820767994291349</v>
@@ -29985,7 +29725,7 @@
         <v>0.05555163275318919</v>
       </c>
       <c r="AT79" t="n">
-        <v>0.07769421791017103</v>
+        <v>0.07769421791017102</v>
       </c>
       <c r="AU79" t="n">
         <v>0.06075616275773723</v>
@@ -29997,7 +29737,7 @@
         <v>0.01591951561861416</v>
       </c>
       <c r="AX79" t="n">
-        <v>0.01764827613349335</v>
+        <v>0.01764827613349336</v>
       </c>
       <c r="AY79" t="n">
         <v>0.07934294747113523</v>
@@ -30030,7 +29770,7 @@
         <v>0.01956740195277552</v>
       </c>
       <c r="BI79" t="n">
-        <v>0.01648000393033355</v>
+        <v>0.01648000393033356</v>
       </c>
       <c r="BJ79" t="n">
         <v>0.0186030449878764</v>
@@ -30081,13 +29821,13 @@
         <v>0.05478506687337206</v>
       </c>
       <c r="BZ79" t="n">
-        <v>0.07622821959961545</v>
+        <v>0.07622821959961547</v>
       </c>
       <c r="CA79" t="n">
         <v>0.01478917663642575</v>
       </c>
       <c r="CB79" t="n">
-        <v>0.06856579121103155</v>
+        <v>0.06856579121103154</v>
       </c>
       <c r="CC79" t="n">
         <v>0.05957518687435016</v>
@@ -30111,7 +29851,7 @@
         <v>0.01882744054754126</v>
       </c>
       <c r="CJ79" t="n">
-        <v>0.09129748077099567</v>
+        <v>0.0912974807709957</v>
       </c>
       <c r="CK79" t="n">
         <v>0.01561496764524501</v>
@@ -30147,7 +29887,7 @@
         <v>0.01817618090371005</v>
       </c>
       <c r="CV79" t="n">
-        <v>0.08278669334535234</v>
+        <v>0.08278669334535235</v>
       </c>
       <c r="CW79" t="n">
         <v>0.01580750972388531</v>
@@ -30305,7 +30045,7 @@
         <v>0.02008422302054496</v>
       </c>
       <c r="AB80" t="n">
-        <v>0.09012648136015386</v>
+        <v>0.09012648136015387</v>
       </c>
       <c r="AC80" t="n">
         <v>0.01820767994291349</v>
@@ -30359,7 +30099,7 @@
         <v>0.05555163275318919</v>
       </c>
       <c r="AT80" t="n">
-        <v>0.07769421791017103</v>
+        <v>0.07769421791017102</v>
       </c>
       <c r="AU80" t="n">
         <v>0.06075616275773723</v>
@@ -30371,7 +30111,7 @@
         <v>0.01591951561861416</v>
       </c>
       <c r="AX80" t="n">
-        <v>0.01764827613349335</v>
+        <v>0.01764827613349336</v>
       </c>
       <c r="AY80" t="n">
         <v>0.07934294747113523</v>
@@ -30404,7 +30144,7 @@
         <v>0.01956740195277552</v>
       </c>
       <c r="BI80" t="n">
-        <v>0.01648000393033355</v>
+        <v>0.01648000393033356</v>
       </c>
       <c r="BJ80" t="n">
         <v>0.0186030449878764</v>
@@ -30455,13 +30195,13 @@
         <v>0.05478506687337206</v>
       </c>
       <c r="BZ80" t="n">
-        <v>0.07622821959961545</v>
+        <v>0.07622821959961547</v>
       </c>
       <c r="CA80" t="n">
         <v>0.01478917663642575</v>
       </c>
       <c r="CB80" t="n">
-        <v>0.06856579121103155</v>
+        <v>0.06856579121103154</v>
       </c>
       <c r="CC80" t="n">
         <v>0.05957518687435016</v>
@@ -30485,7 +30225,7 @@
         <v>0.01882744054754126</v>
       </c>
       <c r="CJ80" t="n">
-        <v>0.09129748077099567</v>
+        <v>0.0912974807709957</v>
       </c>
       <c r="CK80" t="n">
         <v>0.01561496764524501</v>
@@ -30521,7 +30261,7 @@
         <v>0.01817618090371005</v>
       </c>
       <c r="CV80" t="n">
-        <v>0.08278669334535234</v>
+        <v>0.08278669334535235</v>
       </c>
       <c r="CW80" t="n">
         <v>0.01580750972388531</v>
@@ -30587,7 +30327,7 @@
         <v>0.06311641670667917</v>
       </c>
       <c r="DR80" t="n">
-        <v>0.1678555125809485</v>
+        <v>0.1678555125809486</v>
       </c>
       <c r="DS80" t="n">
         <v>0.3769866891979777</v>
@@ -30679,7 +30419,7 @@
         <v>0.02008422302054496</v>
       </c>
       <c r="AB81" t="n">
-        <v>0.09012648136015386</v>
+        <v>0.09012648136015387</v>
       </c>
       <c r="AC81" t="n">
         <v>0.01820767994291349</v>
@@ -30733,7 +30473,7 @@
         <v>0.05555163275318919</v>
       </c>
       <c r="AT81" t="n">
-        <v>0.07769421791017103</v>
+        <v>0.07769421791017102</v>
       </c>
       <c r="AU81" t="n">
         <v>0.06075616275773723</v>
@@ -30745,7 +30485,7 @@
         <v>0.01591951561861416</v>
       </c>
       <c r="AX81" t="n">
-        <v>0.01764827613349335</v>
+        <v>0.01764827613349336</v>
       </c>
       <c r="AY81" t="n">
         <v>0.07934294747113523</v>
@@ -30778,7 +30518,7 @@
         <v>0.01956740195277552</v>
       </c>
       <c r="BI81" t="n">
-        <v>0.01648000393033355</v>
+        <v>0.01648000393033356</v>
       </c>
       <c r="BJ81" t="n">
         <v>0.0186030449878764</v>
@@ -30829,13 +30569,13 @@
         <v>0.05478506687337206</v>
       </c>
       <c r="BZ81" t="n">
-        <v>0.07622821959961545</v>
+        <v>0.07622821959961547</v>
       </c>
       <c r="CA81" t="n">
         <v>0.01478917663642575</v>
       </c>
       <c r="CB81" t="n">
-        <v>0.06856579121103155</v>
+        <v>0.06856579121103154</v>
       </c>
       <c r="CC81" t="n">
         <v>0.05957518687435016</v>
@@ -30859,7 +30599,7 @@
         <v>0.01882744054754126</v>
       </c>
       <c r="CJ81" t="n">
-        <v>0.09129748077099567</v>
+        <v>0.0912974807709957</v>
       </c>
       <c r="CK81" t="n">
         <v>0.01561496764524501</v>
@@ -30895,7 +30635,7 @@
         <v>0.01817618090371005</v>
       </c>
       <c r="CV81" t="n">
-        <v>0.08278669334535234</v>
+        <v>0.08278669334535235</v>
       </c>
       <c r="CW81" t="n">
         <v>0.01580750972388531</v>
@@ -31053,7 +30793,7 @@
         <v>0.02008422302054496</v>
       </c>
       <c r="AB82" t="n">
-        <v>0.09012648136015386</v>
+        <v>0.09012648136015387</v>
       </c>
       <c r="AC82" t="n">
         <v>0.01820767994291349</v>
@@ -31107,7 +30847,7 @@
         <v>0.05555163275318919</v>
       </c>
       <c r="AT82" t="n">
-        <v>0.07769421791017103</v>
+        <v>0.07769421791017102</v>
       </c>
       <c r="AU82" t="n">
         <v>0.06075616275773723</v>
@@ -31119,7 +30859,7 @@
         <v>0.01591951561861416</v>
       </c>
       <c r="AX82" t="n">
-        <v>0.01764827613349335</v>
+        <v>0.01764827613349336</v>
       </c>
       <c r="AY82" t="n">
         <v>0.07934294747113523</v>
@@ -31152,7 +30892,7 @@
         <v>0.01956740195277552</v>
       </c>
       <c r="BI82" t="n">
-        <v>0.01648000393033355</v>
+        <v>0.01648000393033356</v>
       </c>
       <c r="BJ82" t="n">
         <v>0.0186030449878764</v>
@@ -31203,13 +30943,13 @@
         <v>0.05478506687337206</v>
       </c>
       <c r="BZ82" t="n">
-        <v>0.07622821959961545</v>
+        <v>0.07622821959961547</v>
       </c>
       <c r="CA82" t="n">
         <v>0.01478917663642575</v>
       </c>
       <c r="CB82" t="n">
-        <v>0.06856579121103155</v>
+        <v>0.06856579121103154</v>
       </c>
       <c r="CC82" t="n">
         <v>0.05957518687435016</v>
@@ -31233,7 +30973,7 @@
         <v>0.01882744054754126</v>
       </c>
       <c r="CJ82" t="n">
-        <v>0.09129748077099567</v>
+        <v>0.0912974807709957</v>
       </c>
       <c r="CK82" t="n">
         <v>0.01561496764524501</v>
@@ -31269,7 +31009,7 @@
         <v>0.01817618090371005</v>
       </c>
       <c r="CV82" t="n">
-        <v>0.08278669334535234</v>
+        <v>0.08278669334535235</v>
       </c>
       <c r="CW82" t="n">
         <v>0.01580750972388531</v>
@@ -31427,7 +31167,7 @@
         <v>0.02008422302054496</v>
       </c>
       <c r="AB83" t="n">
-        <v>0.09012648136015386</v>
+        <v>0.09012648136015387</v>
       </c>
       <c r="AC83" t="n">
         <v>0.01820767994291349</v>
@@ -31481,7 +31221,7 @@
         <v>0.05555163275318919</v>
       </c>
       <c r="AT83" t="n">
-        <v>0.07769421791017103</v>
+        <v>0.07769421791017102</v>
       </c>
       <c r="AU83" t="n">
         <v>0.06075616275773723</v>
@@ -31493,7 +31233,7 @@
         <v>0.01591951561861416</v>
       </c>
       <c r="AX83" t="n">
-        <v>0.01764827613349335</v>
+        <v>0.01764827613349336</v>
       </c>
       <c r="AY83" t="n">
         <v>0.07934294747113523</v>
@@ -31526,7 +31266,7 @@
         <v>0.01956740195277552</v>
       </c>
       <c r="BI83" t="n">
-        <v>0.01648000393033355</v>
+        <v>0.01648000393033356</v>
       </c>
       <c r="BJ83" t="n">
         <v>0.0186030449878764</v>
@@ -31577,13 +31317,13 @@
         <v>0.05478506687337206</v>
       </c>
       <c r="BZ83" t="n">
-        <v>0.07622821959961545</v>
+        <v>0.07622821959961547</v>
       </c>
       <c r="CA83" t="n">
         <v>0.01478917663642575</v>
       </c>
       <c r="CB83" t="n">
-        <v>0.06856579121103155</v>
+        <v>0.06856579121103154</v>
       </c>
       <c r="CC83" t="n">
         <v>0.05957518687435016</v>
@@ -31607,7 +31347,7 @@
         <v>0.01882744054754126</v>
       </c>
       <c r="CJ83" t="n">
-        <v>0.09129748077099567</v>
+        <v>0.0912974807709957</v>
       </c>
       <c r="CK83" t="n">
         <v>0.01561496764524501</v>
@@ -31643,7 +31383,7 @@
         <v>0.01817618090371005</v>
       </c>
       <c r="CV83" t="n">
-        <v>0.08278669334535234</v>
+        <v>0.08278669334535235</v>
       </c>
       <c r="CW83" t="n">
         <v>0.01580750972388531</v>
@@ -31732,7 +31472,7 @@
         <v>0.06631277401784408</v>
       </c>
       <c r="E84" t="n">
-        <v>0.05976712215455405</v>
+        <v>0.05976712215455404</v>
       </c>
       <c r="F84" t="n">
         <v>0.07595496854550692</v>
@@ -31801,7 +31541,7 @@
         <v>0.02008422302054496</v>
       </c>
       <c r="AB84" t="n">
-        <v>0.09012648136015386</v>
+        <v>0.09012648136015387</v>
       </c>
       <c r="AC84" t="n">
         <v>0.01820767994291349</v>
@@ -31855,7 +31595,7 @@
         <v>0.05555163275318919</v>
       </c>
       <c r="AT84" t="n">
-        <v>0.07769421791017103</v>
+        <v>0.07769421791017102</v>
       </c>
       <c r="AU84" t="n">
         <v>0.06075616275773723</v>
@@ -31867,7 +31607,7 @@
         <v>0.01591951561861416</v>
       </c>
       <c r="AX84" t="n">
-        <v>0.01764827613349335</v>
+        <v>0.01764827613349336</v>
       </c>
       <c r="AY84" t="n">
         <v>0.07934294747113523</v>
@@ -31900,7 +31640,7 @@
         <v>0.01956740195277552</v>
       </c>
       <c r="BI84" t="n">
-        <v>0.01648000393033355</v>
+        <v>0.01648000393033356</v>
       </c>
       <c r="BJ84" t="n">
         <v>0.0186030449878764</v>
@@ -31951,13 +31691,13 @@
         <v>0.05478506687337206</v>
       </c>
       <c r="BZ84" t="n">
-        <v>0.07622821959961545</v>
+        <v>0.07622821959961547</v>
       </c>
       <c r="CA84" t="n">
         <v>0.01478917663642575</v>
       </c>
       <c r="CB84" t="n">
-        <v>0.06856579121103155</v>
+        <v>0.06856579121103154</v>
       </c>
       <c r="CC84" t="n">
         <v>0.05957518687435016</v>
@@ -31981,7 +31721,7 @@
         <v>0.01882744054754126</v>
       </c>
       <c r="CJ84" t="n">
-        <v>0.09129748077099567</v>
+        <v>0.0912974807709957</v>
       </c>
       <c r="CK84" t="n">
         <v>0.01561496764524501</v>
@@ -32017,7 +31757,7 @@
         <v>0.01817618090371005</v>
       </c>
       <c r="CV84" t="n">
-        <v>0.08278669334535234</v>
+        <v>0.08278669334535235</v>
       </c>
       <c r="CW84" t="n">
         <v>0.01580750972388531</v>
@@ -32106,7 +31846,7 @@
         <v>0.06631277401784408</v>
       </c>
       <c r="E85" t="n">
-        <v>0.05976712215455405</v>
+        <v>0.05976712215455404</v>
       </c>
       <c r="F85" t="n">
         <v>0.07595496854550692</v>
@@ -32175,7 +31915,7 @@
         <v>0.02008422302054496</v>
       </c>
       <c r="AB85" t="n">
-        <v>0.09012648136015386</v>
+        <v>0.09012648136015387</v>
       </c>
       <c r="AC85" t="n">
         <v>0.01820767994291349</v>
@@ -32229,7 +31969,7 @@
         <v>0.05555163275318919</v>
       </c>
       <c r="AT85" t="n">
-        <v>0.07769421791017103</v>
+        <v>0.07769421791017102</v>
       </c>
       <c r="AU85" t="n">
         <v>0.06075616275773723</v>
@@ -32241,7 +31981,7 @@
         <v>0.01591951561861416</v>
       </c>
       <c r="AX85" t="n">
-        <v>0.01764827613349335</v>
+        <v>0.01764827613349336</v>
       </c>
       <c r="AY85" t="n">
         <v>0.07934294747113523</v>
@@ -32274,7 +32014,7 @@
         <v>0.01956740195277552</v>
       </c>
       <c r="BI85" t="n">
-        <v>0.01648000393033355</v>
+        <v>0.01648000393033356</v>
       </c>
       <c r="BJ85" t="n">
         <v>0.0186030449878764</v>
@@ -32325,13 +32065,13 @@
         <v>0.05478506687337206</v>
       </c>
       <c r="BZ85" t="n">
-        <v>0.07622821959961545</v>
+        <v>0.07622821959961547</v>
       </c>
       <c r="CA85" t="n">
         <v>0.01478917663642575</v>
       </c>
       <c r="CB85" t="n">
-        <v>0.06856579121103155</v>
+        <v>0.06856579121103154</v>
       </c>
       <c r="CC85" t="n">
         <v>0.05957518687435016</v>
@@ -32355,7 +32095,7 @@
         <v>0.01882744054754126</v>
       </c>
       <c r="CJ85" t="n">
-        <v>0.09129748077099567</v>
+        <v>0.0912974807709957</v>
       </c>
       <c r="CK85" t="n">
         <v>0.01561496764524501</v>
@@ -32391,7 +32131,7 @@
         <v>0.01817618090371005</v>
       </c>
       <c r="CV85" t="n">
-        <v>0.08278669334535234</v>
+        <v>0.08278669334535235</v>
       </c>
       <c r="CW85" t="n">
         <v>0.01580750972388531</v>
@@ -32474,13 +32214,13 @@
         <v>0.4370661699744402</v>
       </c>
       <c r="C86" t="n">
-        <v>0.4967644490435514</v>
+        <v>0.4967644490435513</v>
       </c>
       <c r="D86" t="n">
         <v>0.06631277401784408</v>
       </c>
       <c r="E86" t="n">
-        <v>0.05976712215455405</v>
+        <v>0.05976712215455404</v>
       </c>
       <c r="F86" t="n">
         <v>0.07595496854550692</v>
@@ -32549,7 +32289,7 @@
         <v>0.02008422302054496</v>
       </c>
       <c r="AB86" t="n">
-        <v>0.09012648136015386</v>
+        <v>0.09012648136015387</v>
       </c>
       <c r="AC86" t="n">
         <v>0.01820767994291349</v>
@@ -32603,7 +32343,7 @@
         <v>0.05555163275318919</v>
       </c>
       <c r="AT86" t="n">
-        <v>0.07769421791017103</v>
+        <v>0.07769421791017102</v>
       </c>
       <c r="AU86" t="n">
         <v>0.06075616275773723</v>
@@ -32615,7 +32355,7 @@
         <v>0.01591951561861416</v>
       </c>
       <c r="AX86" t="n">
-        <v>0.01764827613349335</v>
+        <v>0.01764827613349336</v>
       </c>
       <c r="AY86" t="n">
         <v>0.07934294747113523</v>
@@ -32648,7 +32388,7 @@
         <v>0.01956740195277552</v>
       </c>
       <c r="BI86" t="n">
-        <v>0.01648000393033355</v>
+        <v>0.01648000393033356</v>
       </c>
       <c r="BJ86" t="n">
         <v>0.0186030449878764</v>
@@ -32699,13 +32439,13 @@
         <v>0.05478506687337206</v>
       </c>
       <c r="BZ86" t="n">
-        <v>0.07622821959961545</v>
+        <v>0.07622821959961547</v>
       </c>
       <c r="CA86" t="n">
         <v>0.01478917663642575</v>
       </c>
       <c r="CB86" t="n">
-        <v>0.06856579121103155</v>
+        <v>0.06856579121103154</v>
       </c>
       <c r="CC86" t="n">
         <v>0.05957518687435016</v>
@@ -32729,7 +32469,7 @@
         <v>0.01882744054754126</v>
       </c>
       <c r="CJ86" t="n">
-        <v>0.09129748077099567</v>
+        <v>0.0912974807709957</v>
       </c>
       <c r="CK86" t="n">
         <v>0.01561496764524501</v>
@@ -32765,7 +32505,7 @@
         <v>0.01817618090371005</v>
       </c>
       <c r="CV86" t="n">
-        <v>0.08278669334535234</v>
+        <v>0.08278669334535235</v>
       </c>
       <c r="CW86" t="n">
         <v>0.01580750972388531</v>
@@ -32854,7 +32594,7 @@
         <v>0.06631277401784408</v>
       </c>
       <c r="E87" t="n">
-        <v>0.05976712215455405</v>
+        <v>0.05976712215455404</v>
       </c>
       <c r="F87" t="n">
         <v>0.07595496854550692</v>
@@ -32923,7 +32663,7 @@
         <v>0.02008422302054496</v>
       </c>
       <c r="AB87" t="n">
-        <v>0.09012648136015386</v>
+        <v>0.09012648136015387</v>
       </c>
       <c r="AC87" t="n">
         <v>0.01820767994291349</v>
@@ -32977,7 +32717,7 @@
         <v>0.05555163275318919</v>
       </c>
       <c r="AT87" t="n">
-        <v>0.07769421791017103</v>
+        <v>0.07769421791017102</v>
       </c>
       <c r="AU87" t="n">
         <v>0.06075616275773723</v>
@@ -32989,7 +32729,7 @@
         <v>0.01591951561861416</v>
       </c>
       <c r="AX87" t="n">
-        <v>0.01764827613349335</v>
+        <v>0.01764827613349336</v>
       </c>
       <c r="AY87" t="n">
         <v>0.07934294747113523</v>
@@ -33022,7 +32762,7 @@
         <v>0.01956740195277552</v>
       </c>
       <c r="BI87" t="n">
-        <v>0.01648000393033355</v>
+        <v>0.01648000393033356</v>
       </c>
       <c r="BJ87" t="n">
         <v>0.0186030449878764</v>
@@ -33073,13 +32813,13 @@
         <v>0.05478506687337206</v>
       </c>
       <c r="BZ87" t="n">
-        <v>0.07622821959961545</v>
+        <v>0.07622821959961547</v>
       </c>
       <c r="CA87" t="n">
         <v>0.01478917663642575</v>
       </c>
       <c r="CB87" t="n">
-        <v>0.06856579121103155</v>
+        <v>0.06856579121103154</v>
       </c>
       <c r="CC87" t="n">
         <v>0.05957518687435016</v>
@@ -33103,7 +32843,7 @@
         <v>0.01882744054754126</v>
       </c>
       <c r="CJ87" t="n">
-        <v>0.09129748077099567</v>
+        <v>0.0912974807709957</v>
       </c>
       <c r="CK87" t="n">
         <v>0.01561496764524501</v>
@@ -33139,7 +32879,7 @@
         <v>0.01817618090371005</v>
       </c>
       <c r="CV87" t="n">
-        <v>0.08278669334535234</v>
+        <v>0.08278669334535235</v>
       </c>
       <c r="CW87" t="n">
         <v>0.01580750972388531</v>
@@ -33208,7 +32948,7 @@
         <v>0.0824407571331138</v>
       </c>
       <c r="DS87" t="n">
-        <v>0.05258314924107926</v>
+        <v>0.05258314924107925</v>
       </c>
       <c r="DT87" t="n">
         <v>0.4390982147277365</v>
@@ -33228,7 +32968,7 @@
         <v>0.06631277401784408</v>
       </c>
       <c r="E88" t="n">
-        <v>0.05976712215455405</v>
+        <v>0.05976712215455404</v>
       </c>
       <c r="F88" t="n">
         <v>0.07595496854550692</v>
@@ -33297,7 +33037,7 @@
         <v>0.02008422302054496</v>
       </c>
       <c r="AB88" t="n">
-        <v>0.09012648136015386</v>
+        <v>0.09012648136015387</v>
       </c>
       <c r="AC88" t="n">
         <v>0.01820767994291349</v>
@@ -33351,7 +33091,7 @@
         <v>0.05555163275318919</v>
       </c>
       <c r="AT88" t="n">
-        <v>0.07769421791017103</v>
+        <v>0.07769421791017102</v>
       </c>
       <c r="AU88" t="n">
         <v>0.06075616275773723</v>
@@ -33363,7 +33103,7 @@
         <v>0.01591951561861416</v>
       </c>
       <c r="AX88" t="n">
-        <v>0.01764827613349335</v>
+        <v>0.01764827613349336</v>
       </c>
       <c r="AY88" t="n">
         <v>0.07934294747113523</v>
@@ -33396,7 +33136,7 @@
         <v>0.01956740195277552</v>
       </c>
       <c r="BI88" t="n">
-        <v>0.01648000393033355</v>
+        <v>0.01648000393033356</v>
       </c>
       <c r="BJ88" t="n">
         <v>0.0186030449878764</v>
@@ -33447,13 +33187,13 @@
         <v>0.05478506687337206</v>
       </c>
       <c r="BZ88" t="n">
-        <v>0.07622821959961545</v>
+        <v>0.07622821959961547</v>
       </c>
       <c r="CA88" t="n">
         <v>0.01478917663642575</v>
       </c>
       <c r="CB88" t="n">
-        <v>0.06856579121103155</v>
+        <v>0.06856579121103154</v>
       </c>
       <c r="CC88" t="n">
         <v>0.05957518687435016</v>
@@ -33477,7 +33217,7 @@
         <v>0.01882744054754126</v>
       </c>
       <c r="CJ88" t="n">
-        <v>0.09129748077099567</v>
+        <v>0.0912974807709957</v>
       </c>
       <c r="CK88" t="n">
         <v>0.01561496764524501</v>
@@ -33513,7 +33253,7 @@
         <v>0.01817618090371005</v>
       </c>
       <c r="CV88" t="n">
-        <v>0.08278669334535234</v>
+        <v>0.08278669334535235</v>
       </c>
       <c r="CW88" t="n">
         <v>0.01580750972388531</v>
@@ -33582,7 +33322,7 @@
         <v>0.07150685473080465</v>
       </c>
       <c r="DS88" t="n">
-        <v>0.05258314924107926</v>
+        <v>0.05258314924107925</v>
       </c>
       <c r="DT88" t="n">
         <v>0.4384838013463864</v>
@@ -33590,7 +33330,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>0.3919590738442388</v>
+        <v>0.3919590738442387</v>
       </c>
       <c r="B89" t="n">
         <v>0.4347661808013339</v>
@@ -33602,7 +33342,7 @@
         <v>0.06631277401784408</v>
       </c>
       <c r="E89" t="n">
-        <v>0.05976712215455405</v>
+        <v>0.05976712215455404</v>
       </c>
       <c r="F89" t="n">
         <v>0.07595496854550692</v>
@@ -33671,7 +33411,7 @@
         <v>0.02008422302054496</v>
       </c>
       <c r="AB89" t="n">
-        <v>0.09012648136015386</v>
+        <v>0.09012648136015387</v>
       </c>
       <c r="AC89" t="n">
         <v>0.01820767994291349</v>
@@ -33725,7 +33465,7 @@
         <v>0.05555163275318919</v>
       </c>
       <c r="AT89" t="n">
-        <v>0.07769421791017103</v>
+        <v>0.07769421791017102</v>
       </c>
       <c r="AU89" t="n">
         <v>0.06075616275773723</v>
@@ -33737,7 +33477,7 @@
         <v>0.01591951561861416</v>
       </c>
       <c r="AX89" t="n">
-        <v>0.01764827613349335</v>
+        <v>0.01764827613349336</v>
       </c>
       <c r="AY89" t="n">
         <v>0.07934294747113523</v>
@@ -33770,7 +33510,7 @@
         <v>0.01956740195277552</v>
       </c>
       <c r="BI89" t="n">
-        <v>0.01648000393033355</v>
+        <v>0.01648000393033356</v>
       </c>
       <c r="BJ89" t="n">
         <v>0.0186030449878764</v>
@@ -33821,13 +33561,13 @@
         <v>0.05478506687337206</v>
       </c>
       <c r="BZ89" t="n">
-        <v>0.07622821959961545</v>
+        <v>0.07622821959961547</v>
       </c>
       <c r="CA89" t="n">
         <v>0.01478917663642575</v>
       </c>
       <c r="CB89" t="n">
-        <v>0.06856579121103155</v>
+        <v>0.06856579121103154</v>
       </c>
       <c r="CC89" t="n">
         <v>0.05957518687435016</v>
@@ -33851,7 +33591,7 @@
         <v>0.01882744054754126</v>
       </c>
       <c r="CJ89" t="n">
-        <v>0.09129748077099567</v>
+        <v>0.0912974807709957</v>
       </c>
       <c r="CK89" t="n">
         <v>0.01561496764524501</v>
@@ -33887,7 +33627,7 @@
         <v>0.01817618090371005</v>
       </c>
       <c r="CV89" t="n">
-        <v>0.08278669334535234</v>
+        <v>0.08278669334535235</v>
       </c>
       <c r="CW89" t="n">
         <v>0.01580750972388531</v>
@@ -33956,7 +33696,7 @@
         <v>0.06088827089712932</v>
       </c>
       <c r="DS89" t="n">
-        <v>0.05258314924107926</v>
+        <v>0.05258314924107925</v>
       </c>
       <c r="DT89" t="n">
         <v>0.4369777975069369</v>
@@ -33976,7 +33716,7 @@
         <v>0.06631277401784408</v>
       </c>
       <c r="E90" t="n">
-        <v>0.05976712215455405</v>
+        <v>0.05976712215455404</v>
       </c>
       <c r="F90" t="n">
         <v>0.07595496854550692</v>
@@ -34045,7 +33785,7 @@
         <v>0.02008422302054496</v>
       </c>
       <c r="AB90" t="n">
-        <v>0.09012648136015386</v>
+        <v>0.09012648136015387</v>
       </c>
       <c r="AC90" t="n">
         <v>0.01820767994291349</v>
@@ -34099,7 +33839,7 @@
         <v>0.05555163275318919</v>
       </c>
       <c r="AT90" t="n">
-        <v>0.07769421791017103</v>
+        <v>0.07769421791017102</v>
       </c>
       <c r="AU90" t="n">
         <v>0.06075616275773723</v>
@@ -34111,7 +33851,7 @@
         <v>0.01591951561861416</v>
       </c>
       <c r="AX90" t="n">
-        <v>0.01764827613349335</v>
+        <v>0.01764827613349336</v>
       </c>
       <c r="AY90" t="n">
         <v>0.07934294747113523</v>
@@ -34144,7 +33884,7 @@
         <v>0.01956740195277552</v>
       </c>
       <c r="BI90" t="n">
-        <v>0.01648000393033355</v>
+        <v>0.01648000393033356</v>
       </c>
       <c r="BJ90" t="n">
         <v>0.0186030449878764</v>
@@ -34195,13 +33935,13 @@
         <v>0.05478506687337206</v>
       </c>
       <c r="BZ90" t="n">
-        <v>0.07622821959961545</v>
+        <v>0.07622821959961547</v>
       </c>
       <c r="CA90" t="n">
         <v>0.01478917663642575</v>
       </c>
       <c r="CB90" t="n">
-        <v>0.06856579121103155</v>
+        <v>0.06856579121103154</v>
       </c>
       <c r="CC90" t="n">
         <v>0.05957518687435016</v>
@@ -34225,7 +33965,7 @@
         <v>0.01882744054754126</v>
       </c>
       <c r="CJ90" t="n">
-        <v>0.09129748077099567</v>
+        <v>0.0912974807709957</v>
       </c>
       <c r="CK90" t="n">
         <v>0.01561496764524501</v>
@@ -34261,7 +34001,7 @@
         <v>0.01817618090371005</v>
       </c>
       <c r="CV90" t="n">
-        <v>0.08278669334535234</v>
+        <v>0.08278669334535235</v>
       </c>
       <c r="CW90" t="n">
         <v>0.01580750972388531</v>
@@ -34330,7 +34070,7 @@
         <v>0.06088827089712932</v>
       </c>
       <c r="DS90" t="n">
-        <v>0.05258314924107926</v>
+        <v>0.05258314924107925</v>
       </c>
       <c r="DT90" t="n">
         <v>0.4350102742193176</v>
@@ -34350,7 +34090,7 @@
         <v>0.06631277401784408</v>
       </c>
       <c r="E91" t="n">
-        <v>0.05976712215455405</v>
+        <v>0.05976712215455404</v>
       </c>
       <c r="F91" t="n">
         <v>0.07595496854550692</v>
@@ -34419,7 +34159,7 @@
         <v>0.02008422302054496</v>
       </c>
       <c r="AB91" t="n">
-        <v>0.09012648136015386</v>
+        <v>0.09012648136015387</v>
       </c>
       <c r="AC91" t="n">
         <v>0.01820767994291349</v>
@@ -34473,7 +34213,7 @@
         <v>0.05555163275318919</v>
       </c>
       <c r="AT91" t="n">
-        <v>0.07769421791017103</v>
+        <v>0.07769421791017102</v>
       </c>
       <c r="AU91" t="n">
         <v>0.06075616275773723</v>
@@ -34485,7 +34225,7 @@
         <v>0.01591951561861416</v>
       </c>
       <c r="AX91" t="n">
-        <v>0.01764827613349335</v>
+        <v>0.01764827613349336</v>
       </c>
       <c r="AY91" t="n">
         <v>0.07934294747113523</v>
@@ -34518,7 +34258,7 @@
         <v>0.01956740195277552</v>
       </c>
       <c r="BI91" t="n">
-        <v>0.01648000393033355</v>
+        <v>0.01648000393033356</v>
       </c>
       <c r="BJ91" t="n">
         <v>0.0186030449878764</v>
@@ -34569,13 +34309,13 @@
         <v>0.05478506687337206</v>
       </c>
       <c r="BZ91" t="n">
-        <v>0.07622821959961545</v>
+        <v>0.07622821959961547</v>
       </c>
       <c r="CA91" t="n">
         <v>0.01478917663642575</v>
       </c>
       <c r="CB91" t="n">
-        <v>0.06856579121103155</v>
+        <v>0.06856579121103154</v>
       </c>
       <c r="CC91" t="n">
         <v>0.05957518687435016</v>
@@ -34599,7 +34339,7 @@
         <v>0.01882744054754126</v>
       </c>
       <c r="CJ91" t="n">
-        <v>0.09129748077099567</v>
+        <v>0.0912974807709957</v>
       </c>
       <c r="CK91" t="n">
         <v>0.01561496764524501</v>
@@ -34635,7 +34375,7 @@
         <v>0.01817618090371005</v>
       </c>
       <c r="CV91" t="n">
-        <v>0.08278669334535234</v>
+        <v>0.08278669334535235</v>
       </c>
       <c r="CW91" t="n">
         <v>0.01580750972388531</v>
@@ -34704,7 +34444,7 @@
         <v>0.06088827089712932</v>
       </c>
       <c r="DS91" t="n">
-        <v>0.05258314924107926</v>
+        <v>0.05258314924107925</v>
       </c>
       <c r="DT91" t="n">
         <v>0.4329642654895087</v>
@@ -34724,7 +34464,7 @@
         <v>0.06631277401784408</v>
       </c>
       <c r="E92" t="n">
-        <v>0.05976712215455405</v>
+        <v>0.05976712215455404</v>
       </c>
       <c r="F92" t="n">
         <v>0.07595496854550692</v>
@@ -34793,7 +34533,7 @@
         <v>0.02008422302054496</v>
       </c>
       <c r="AB92" t="n">
-        <v>0.09012648136015386</v>
+        <v>0.09012648136015387</v>
       </c>
       <c r="AC92" t="n">
         <v>0.01820767994291349</v>
@@ -34847,7 +34587,7 @@
         <v>0.05555163275318919</v>
       </c>
       <c r="AT92" t="n">
-        <v>0.07769421791017103</v>
+        <v>0.07769421791017102</v>
       </c>
       <c r="AU92" t="n">
         <v>0.06075616275773723</v>
@@ -34859,7 +34599,7 @@
         <v>0.01591951561861416</v>
       </c>
       <c r="AX92" t="n">
-        <v>0.01764827613349335</v>
+        <v>0.01764827613349336</v>
       </c>
       <c r="AY92" t="n">
         <v>0.07934294747113523</v>
@@ -34892,7 +34632,7 @@
         <v>0.01956740195277552</v>
       </c>
       <c r="BI92" t="n">
-        <v>0.01648000393033355</v>
+        <v>0.01648000393033356</v>
       </c>
       <c r="BJ92" t="n">
         <v>0.0186030449878764</v>
@@ -34943,13 +34683,13 @@
         <v>0.05478506687337206</v>
       </c>
       <c r="BZ92" t="n">
-        <v>0.07622821959961545</v>
+        <v>0.07622821959961547</v>
       </c>
       <c r="CA92" t="n">
         <v>0.01478917663642575</v>
       </c>
       <c r="CB92" t="n">
-        <v>0.06856579121103155</v>
+        <v>0.06856579121103154</v>
       </c>
       <c r="CC92" t="n">
         <v>0.05957518687435016</v>
@@ -34973,7 +34713,7 @@
         <v>0.01882744054754126</v>
       </c>
       <c r="CJ92" t="n">
-        <v>0.09129748077099567</v>
+        <v>0.0912974807709957</v>
       </c>
       <c r="CK92" t="n">
         <v>0.01561496764524501</v>
@@ -35009,7 +34749,7 @@
         <v>0.01817618090371005</v>
       </c>
       <c r="CV92" t="n">
-        <v>0.08278669334535234</v>
+        <v>0.08278669334535235</v>
       </c>
       <c r="CW92" t="n">
         <v>0.01580750972388531</v>
@@ -35078,7 +34818,7 @@
         <v>0.06088827089712932</v>
       </c>
       <c r="DS92" t="n">
-        <v>0.05258314924107926</v>
+        <v>0.05258314924107925</v>
       </c>
       <c r="DT92" t="n">
         <v>0.4309893907930546</v>
@@ -35098,7 +34838,7 @@
         <v>0.06631277401784408</v>
       </c>
       <c r="E93" t="n">
-        <v>0.05976712215455405</v>
+        <v>0.05976712215455404</v>
       </c>
       <c r="F93" t="n">
         <v>0.07595496854550692</v>
@@ -35167,7 +34907,7 @@
         <v>0.02008422302054496</v>
       </c>
       <c r="AB93" t="n">
-        <v>0.09012648136015386</v>
+        <v>0.09012648136015387</v>
       </c>
       <c r="AC93" t="n">
         <v>0.01820767994291349</v>
@@ -35221,7 +34961,7 @@
         <v>0.05555163275318919</v>
       </c>
       <c r="AT93" t="n">
-        <v>0.07769421791017103</v>
+        <v>0.07769421791017102</v>
       </c>
       <c r="AU93" t="n">
         <v>0.06075616275773723</v>
@@ -35233,7 +34973,7 @@
         <v>0.01591951561861416</v>
       </c>
       <c r="AX93" t="n">
-        <v>0.01764827613349335</v>
+        <v>0.01764827613349336</v>
       </c>
       <c r="AY93" t="n">
         <v>0.07934294747113523</v>
@@ -35266,7 +35006,7 @@
         <v>0.01956740195277552</v>
       </c>
       <c r="BI93" t="n">
-        <v>0.01648000393033355</v>
+        <v>0.01648000393033356</v>
       </c>
       <c r="BJ93" t="n">
         <v>0.0186030449878764</v>
@@ -35317,13 +35057,13 @@
         <v>0.05478506687337206</v>
       </c>
       <c r="BZ93" t="n">
-        <v>0.07622821959961545</v>
+        <v>0.07622821959961547</v>
       </c>
       <c r="CA93" t="n">
         <v>0.01478917663642575</v>
       </c>
       <c r="CB93" t="n">
-        <v>0.06856579121103155</v>
+        <v>0.06856579121103154</v>
       </c>
       <c r="CC93" t="n">
         <v>0.05957518687435016</v>
@@ -35347,7 +35087,7 @@
         <v>0.01882744054754126</v>
       </c>
       <c r="CJ93" t="n">
-        <v>0.09129748077099567</v>
+        <v>0.0912974807709957</v>
       </c>
       <c r="CK93" t="n">
         <v>0.01561496764524501</v>
@@ -35383,7 +35123,7 @@
         <v>0.01817618090371005</v>
       </c>
       <c r="CV93" t="n">
-        <v>0.08278669334535234</v>
+        <v>0.08278669334535235</v>
       </c>
       <c r="CW93" t="n">
         <v>0.01580750972388531</v>
@@ -35452,7 +35192,7 @@
         <v>0.06088827089712932</v>
       </c>
       <c r="DS93" t="n">
-        <v>0.05258314924107926</v>
+        <v>0.05258314924107925</v>
       </c>
       <c r="DT93" t="n">
         <v>0.4289729000307851</v>
@@ -35472,7 +35212,7 @@
         <v>0.06631277401784408</v>
       </c>
       <c r="E94" t="n">
-        <v>0.05976712215455405</v>
+        <v>0.05976712215455404</v>
       </c>
       <c r="F94" t="n">
         <v>0.07595496854550692</v>
@@ -35541,7 +35281,7 @@
         <v>0.02008422302054496</v>
       </c>
       <c r="AB94" t="n">
-        <v>0.09012648136015386</v>
+        <v>0.09012648136015387</v>
       </c>
       <c r="AC94" t="n">
         <v>0.01820767994291349</v>
@@ -35595,7 +35335,7 @@
         <v>0.05555163275318919</v>
       </c>
       <c r="AT94" t="n">
-        <v>0.07769421791017103</v>
+        <v>0.07769421791017102</v>
       </c>
       <c r="AU94" t="n">
         <v>0.06075616275773723</v>
@@ -35607,7 +35347,7 @@
         <v>0.01591951561861416</v>
       </c>
       <c r="AX94" t="n">
-        <v>0.01764827613349335</v>
+        <v>0.01764827613349336</v>
       </c>
       <c r="AY94" t="n">
         <v>0.07934294747113523</v>
@@ -35640,7 +35380,7 @@
         <v>0.01956740195277552</v>
       </c>
       <c r="BI94" t="n">
-        <v>0.01648000393033355</v>
+        <v>0.01648000393033356</v>
       </c>
       <c r="BJ94" t="n">
         <v>0.0186030449878764</v>
@@ -35691,13 +35431,13 @@
         <v>0.05478506687337206</v>
       </c>
       <c r="BZ94" t="n">
-        <v>0.07622821959961545</v>
+        <v>0.07622821959961547</v>
       </c>
       <c r="CA94" t="n">
         <v>0.01478917663642575</v>
       </c>
       <c r="CB94" t="n">
-        <v>0.06856579121103155</v>
+        <v>0.06856579121103154</v>
       </c>
       <c r="CC94" t="n">
         <v>0.05957518687435016</v>
@@ -35721,7 +35461,7 @@
         <v>0.01882744054754126</v>
       </c>
       <c r="CJ94" t="n">
-        <v>0.09129748077099567</v>
+        <v>0.0912974807709957</v>
       </c>
       <c r="CK94" t="n">
         <v>0.01561496764524501</v>
@@ -35757,7 +35497,7 @@
         <v>0.01817618090371005</v>
       </c>
       <c r="CV94" t="n">
-        <v>0.08278669334535234</v>
+        <v>0.08278669334535235</v>
       </c>
       <c r="CW94" t="n">
         <v>0.01580750972388531</v>
@@ -35826,7 +35566,7 @@
         <v>0.06088827089712932</v>
       </c>
       <c r="DS94" t="n">
-        <v>0.05258314924107926</v>
+        <v>0.05258314924107925</v>
       </c>
       <c r="DT94" t="n">
         <v>0.4266448297824711</v>
@@ -35846,7 +35586,7 @@
         <v>0.06631277401784408</v>
       </c>
       <c r="E95" t="n">
-        <v>0.05976712215455405</v>
+        <v>0.05976712215455404</v>
       </c>
       <c r="F95" t="n">
         <v>0.07595496854550692</v>
@@ -35915,7 +35655,7 @@
         <v>0.02008422302054496</v>
       </c>
       <c r="AB95" t="n">
-        <v>0.09012648136015386</v>
+        <v>0.09012648136015387</v>
       </c>
       <c r="AC95" t="n">
         <v>0.01820767994291349</v>
@@ -35969,7 +35709,7 @@
         <v>0.05555163275318919</v>
       </c>
       <c r="AT95" t="n">
-        <v>0.07769421791017103</v>
+        <v>0.07769421791017102</v>
       </c>
       <c r="AU95" t="n">
         <v>0.06075616275773723</v>
@@ -35981,7 +35721,7 @@
         <v>0.01591951561861416</v>
       </c>
       <c r="AX95" t="n">
-        <v>0.01764827613349335</v>
+        <v>0.01764827613349336</v>
       </c>
       <c r="AY95" t="n">
         <v>0.07934294747113523</v>
@@ -36014,7 +35754,7 @@
         <v>0.01956740195277552</v>
       </c>
       <c r="BI95" t="n">
-        <v>0.01648000393033355</v>
+        <v>0.01648000393033356</v>
       </c>
       <c r="BJ95" t="n">
         <v>0.0186030449878764</v>
@@ -36065,13 +35805,13 @@
         <v>0.05478506687337206</v>
       </c>
       <c r="BZ95" t="n">
-        <v>0.07622821959961545</v>
+        <v>0.07622821959961547</v>
       </c>
       <c r="CA95" t="n">
         <v>0.01478917663642575</v>
       </c>
       <c r="CB95" t="n">
-        <v>0.06856579121103155</v>
+        <v>0.06856579121103154</v>
       </c>
       <c r="CC95" t="n">
         <v>0.05957518687435016</v>
@@ -36095,7 +35835,7 @@
         <v>0.01882744054754126</v>
       </c>
       <c r="CJ95" t="n">
-        <v>0.09129748077099567</v>
+        <v>0.0912974807709957</v>
       </c>
       <c r="CK95" t="n">
         <v>0.01561496764524501</v>
@@ -36131,7 +35871,7 @@
         <v>0.01817618090371005</v>
       </c>
       <c r="CV95" t="n">
-        <v>0.08278669334535234</v>
+        <v>0.08278669334535235</v>
       </c>
       <c r="CW95" t="n">
         <v>0.01580750972388531</v>
@@ -36200,7 +35940,7 @@
         <v>0.06088827089712932</v>
       </c>
       <c r="DS95" t="n">
-        <v>0.05258314924107926</v>
+        <v>0.05258314924107925</v>
       </c>
       <c r="DT95" t="n">
         <v>0.4237609831559585</v>
@@ -36220,7 +35960,7 @@
         <v>0.06631277401784408</v>
       </c>
       <c r="E96" t="n">
-        <v>0.05976712215455405</v>
+        <v>0.05976712215455404</v>
       </c>
       <c r="F96" t="n">
         <v>0.07595496854550692</v>
@@ -36289,7 +36029,7 @@
         <v>0.02008422302054496</v>
       </c>
       <c r="AB96" t="n">
-        <v>0.09012648136015386</v>
+        <v>0.09012648136015387</v>
       </c>
       <c r="AC96" t="n">
         <v>0.01820767994291349</v>
@@ -36343,7 +36083,7 @@
         <v>0.05555163275318919</v>
       </c>
       <c r="AT96" t="n">
-        <v>0.07769421791017103</v>
+        <v>0.07769421791017102</v>
       </c>
       <c r="AU96" t="n">
         <v>0.06075616275773723</v>
@@ -36355,7 +36095,7 @@
         <v>0.01591951561861416</v>
       </c>
       <c r="AX96" t="n">
-        <v>0.01764827613349335</v>
+        <v>0.01764827613349336</v>
       </c>
       <c r="AY96" t="n">
         <v>0.07934294747113523</v>
@@ -36388,7 +36128,7 @@
         <v>0.01956740195277552</v>
       </c>
       <c r="BI96" t="n">
-        <v>0.01648000393033355</v>
+        <v>0.01648000393033356</v>
       </c>
       <c r="BJ96" t="n">
         <v>0.0186030449878764</v>
@@ -36439,13 +36179,13 @@
         <v>0.05478506687337206</v>
       </c>
       <c r="BZ96" t="n">
-        <v>0.07622821959961545</v>
+        <v>0.07622821959961547</v>
       </c>
       <c r="CA96" t="n">
         <v>0.01478917663642575</v>
       </c>
       <c r="CB96" t="n">
-        <v>0.06856579121103155</v>
+        <v>0.06856579121103154</v>
       </c>
       <c r="CC96" t="n">
         <v>0.05957518687435016</v>
@@ -36469,7 +36209,7 @@
         <v>0.01882744054754126</v>
       </c>
       <c r="CJ96" t="n">
-        <v>0.09129748077099567</v>
+        <v>0.0912974807709957</v>
       </c>
       <c r="CK96" t="n">
         <v>0.01561496764524501</v>
@@ -36505,7 +36245,7 @@
         <v>0.01817618090371005</v>
       </c>
       <c r="CV96" t="n">
-        <v>0.08278669334535234</v>
+        <v>0.08278669334535235</v>
       </c>
       <c r="CW96" t="n">
         <v>0.01580750972388531</v>
@@ -36574,7 +36314,7 @@
         <v>0.06088827089712932</v>
       </c>
       <c r="DS96" t="n">
-        <v>0.05258314924107926</v>
+        <v>0.05258314924107925</v>
       </c>
       <c r="DT96" t="n">
         <v>0.4202700512099143</v>
@@ -36585,7 +36325,7 @@
         <v>0.3893953677750887</v>
       </c>
       <c r="B97" t="n">
-        <v>0.4234578780114965</v>
+        <v>0.4234578780114964</v>
       </c>
       <c r="C97" t="n">
         <v>0.05225427637649842</v>
@@ -36594,7 +36334,7 @@
         <v>0.06631277401784408</v>
       </c>
       <c r="E97" t="n">
-        <v>0.05976712215455405</v>
+        <v>0.05976712215455404</v>
       </c>
       <c r="F97" t="n">
         <v>0.07595496854550692</v>
@@ -36663,7 +36403,7 @@
         <v>0.02008422302054496</v>
       </c>
       <c r="AB97" t="n">
-        <v>0.09012648136015386</v>
+        <v>0.09012648136015387</v>
       </c>
       <c r="AC97" t="n">
         <v>0.01820767994291349</v>
@@ -36717,7 +36457,7 @@
         <v>0.05555163275318919</v>
       </c>
       <c r="AT97" t="n">
-        <v>0.07769421791017103</v>
+        <v>0.07769421791017102</v>
       </c>
       <c r="AU97" t="n">
         <v>0.06075616275773723</v>
@@ -36729,7 +36469,7 @@
         <v>0.01591951561861416</v>
       </c>
       <c r="AX97" t="n">
-        <v>0.01764827613349335</v>
+        <v>0.01764827613349336</v>
       </c>
       <c r="AY97" t="n">
         <v>0.07934294747113523</v>
@@ -36762,7 +36502,7 @@
         <v>0.01956740195277552</v>
       </c>
       <c r="BI97" t="n">
-        <v>0.01648000393033355</v>
+        <v>0.01648000393033356</v>
       </c>
       <c r="BJ97" t="n">
         <v>0.0186030449878764</v>
@@ -36813,13 +36553,13 @@
         <v>0.05478506687337206</v>
       </c>
       <c r="BZ97" t="n">
-        <v>0.07622821959961545</v>
+        <v>0.07622821959961547</v>
       </c>
       <c r="CA97" t="n">
         <v>0.01478917663642575</v>
       </c>
       <c r="CB97" t="n">
-        <v>0.06856579121103155</v>
+        <v>0.06856579121103154</v>
       </c>
       <c r="CC97" t="n">
         <v>0.05957518687435016</v>
@@ -36843,7 +36583,7 @@
         <v>0.01882744054754126</v>
       </c>
       <c r="CJ97" t="n">
-        <v>0.09129748077099567</v>
+        <v>0.0912974807709957</v>
       </c>
       <c r="CK97" t="n">
         <v>0.01561496764524501</v>
@@ -36879,7 +36619,7 @@
         <v>0.01817618090371005</v>
       </c>
       <c r="CV97" t="n">
-        <v>0.08278669334535234</v>
+        <v>0.08278669334535235</v>
       </c>
       <c r="CW97" t="n">
         <v>0.01580750972388531</v>
@@ -36948,7 +36688,7 @@
         <v>0.06088827089712932</v>
       </c>
       <c r="DS97" t="n">
-        <v>0.05258314924107926</v>
+        <v>0.05258314924107925</v>
       </c>
       <c r="DT97" t="n">
         <v>0.4163392088563251</v>
@@ -36968,7 +36708,7 @@
         <v>0.06631277401784408</v>
       </c>
       <c r="E98" t="n">
-        <v>0.05976712215455405</v>
+        <v>0.05976712215455404</v>
       </c>
       <c r="F98" t="n">
         <v>0.07595496854550692</v>
@@ -37037,7 +36777,7 @@
         <v>0.02008422302054496</v>
       </c>
       <c r="AB98" t="n">
-        <v>0.09012648136015386</v>
+        <v>0.09012648136015387</v>
       </c>
       <c r="AC98" t="n">
         <v>0.01820767994291349</v>
@@ -37091,7 +36831,7 @@
         <v>0.05555163275318919</v>
       </c>
       <c r="AT98" t="n">
-        <v>0.07769421791017103</v>
+        <v>0.07769421791017102</v>
       </c>
       <c r="AU98" t="n">
         <v>0.06075616275773723</v>
@@ -37103,7 +36843,7 @@
         <v>0.01591951561861416</v>
       </c>
       <c r="AX98" t="n">
-        <v>0.01764827613349335</v>
+        <v>0.01764827613349336</v>
       </c>
       <c r="AY98" t="n">
         <v>0.07934294747113523</v>
@@ -37136,7 +36876,7 @@
         <v>0.01956740195277552</v>
       </c>
       <c r="BI98" t="n">
-        <v>0.01648000393033355</v>
+        <v>0.01648000393033356</v>
       </c>
       <c r="BJ98" t="n">
         <v>0.0186030449878764</v>
@@ -37187,13 +36927,13 @@
         <v>0.05478506687337206</v>
       </c>
       <c r="BZ98" t="n">
-        <v>0.07622821959961545</v>
+        <v>0.07622821959961547</v>
       </c>
       <c r="CA98" t="n">
         <v>0.01478917663642575</v>
       </c>
       <c r="CB98" t="n">
-        <v>0.06856579121103155</v>
+        <v>0.06856579121103154</v>
       </c>
       <c r="CC98" t="n">
         <v>0.05957518687435016</v>
@@ -37217,7 +36957,7 @@
         <v>0.01882744054754126</v>
       </c>
       <c r="CJ98" t="n">
-        <v>0.09129748077099567</v>
+        <v>0.0912974807709957</v>
       </c>
       <c r="CK98" t="n">
         <v>0.01561496764524501</v>
@@ -37253,7 +36993,7 @@
         <v>0.01817618090371005</v>
       </c>
       <c r="CV98" t="n">
-        <v>0.08278669334535234</v>
+        <v>0.08278669334535235</v>
       </c>
       <c r="CW98" t="n">
         <v>0.01580750972388531</v>
@@ -37322,7 +37062,7 @@
         <v>0.06088827089712932</v>
       </c>
       <c r="DS98" t="n">
-        <v>0.05258314924107926</v>
+        <v>0.05258314924107925</v>
       </c>
       <c r="DT98" t="n">
         <v>0.4122273795657306</v>
@@ -37342,7 +37082,7 @@
         <v>0.06631277401784408</v>
       </c>
       <c r="E99" t="n">
-        <v>0.05976712215455405</v>
+        <v>0.05976712215455404</v>
       </c>
       <c r="F99" t="n">
         <v>0.07595496854550692</v>
@@ -37411,7 +37151,7 @@
         <v>0.02008422302054496</v>
       </c>
       <c r="AB99" t="n">
-        <v>0.09012648136015386</v>
+        <v>0.09012648136015387</v>
       </c>
       <c r="AC99" t="n">
         <v>0.01820767994291349</v>
@@ -37465,7 +37205,7 @@
         <v>0.05555163275318919</v>
       </c>
       <c r="AT99" t="n">
-        <v>0.07769421791017103</v>
+        <v>0.07769421791017102</v>
       </c>
       <c r="AU99" t="n">
         <v>0.06075616275773723</v>
@@ -37477,7 +37217,7 @@
         <v>0.01591951561861416</v>
       </c>
       <c r="AX99" t="n">
-        <v>0.01764827613349335</v>
+        <v>0.01764827613349336</v>
       </c>
       <c r="AY99" t="n">
         <v>0.07934294747113523</v>
@@ -37510,7 +37250,7 @@
         <v>0.01956740195277552</v>
       </c>
       <c r="BI99" t="n">
-        <v>0.01648000393033355</v>
+        <v>0.01648000393033356</v>
       </c>
       <c r="BJ99" t="n">
         <v>0.0186030449878764</v>
@@ -37561,13 +37301,13 @@
         <v>0.05478506687337206</v>
       </c>
       <c r="BZ99" t="n">
-        <v>0.07622821959961545</v>
+        <v>0.07622821959961547</v>
       </c>
       <c r="CA99" t="n">
         <v>0.01478917663642575</v>
       </c>
       <c r="CB99" t="n">
-        <v>0.06856579121103155</v>
+        <v>0.06856579121103154</v>
       </c>
       <c r="CC99" t="n">
         <v>0.05957518687435016</v>
@@ -37591,7 +37331,7 @@
         <v>0.01882744054754126</v>
       </c>
       <c r="CJ99" t="n">
-        <v>0.09129748077099567</v>
+        <v>0.0912974807709957</v>
       </c>
       <c r="CK99" t="n">
         <v>0.01561496764524501</v>
@@ -37627,7 +37367,7 @@
         <v>0.01817618090371005</v>
       </c>
       <c r="CV99" t="n">
-        <v>0.08278669334535234</v>
+        <v>0.08278669334535235</v>
       </c>
       <c r="CW99" t="n">
         <v>0.01580750972388531</v>
@@ -37696,7 +37436,7 @@
         <v>0.06088827089712932</v>
       </c>
       <c r="DS99" t="n">
-        <v>0.05258314924107926</v>
+        <v>0.05258314924107925</v>
       </c>
       <c r="DT99" t="n">
         <v>0.4081580564774969</v>
@@ -37716,7 +37456,7 @@
         <v>0.06631277401784408</v>
       </c>
       <c r="E100" t="n">
-        <v>0.05976712215455405</v>
+        <v>0.05976712215455404</v>
       </c>
       <c r="F100" t="n">
         <v>0.07595496854550692</v>
@@ -37785,7 +37525,7 @@
         <v>0.02008422302054496</v>
       </c>
       <c r="AB100" t="n">
-        <v>0.09012648136015386</v>
+        <v>0.09012648136015387</v>
       </c>
       <c r="AC100" t="n">
         <v>0.01820767994291349</v>
@@ -37839,7 +37579,7 @@
         <v>0.05555163275318919</v>
       </c>
       <c r="AT100" t="n">
-        <v>0.07769421791017103</v>
+        <v>0.07769421791017102</v>
       </c>
       <c r="AU100" t="n">
         <v>0.06075616275773723</v>
@@ -37851,7 +37591,7 @@
         <v>0.01591951561861416</v>
       </c>
       <c r="AX100" t="n">
-        <v>0.01764827613349335</v>
+        <v>0.01764827613349336</v>
       </c>
       <c r="AY100" t="n">
         <v>0.07934294747113523</v>
@@ -37884,7 +37624,7 @@
         <v>0.01956740195277552</v>
       </c>
       <c r="BI100" t="n">
-        <v>0.01648000393033355</v>
+        <v>0.01648000393033356</v>
       </c>
       <c r="BJ100" t="n">
         <v>0.0186030449878764</v>
@@ -37935,13 +37675,13 @@
         <v>0.05478506687337206</v>
       </c>
       <c r="BZ100" t="n">
-        <v>0.07622821959961545</v>
+        <v>0.07622821959961547</v>
       </c>
       <c r="CA100" t="n">
         <v>0.01478917663642575</v>
       </c>
       <c r="CB100" t="n">
-        <v>0.06856579121103155</v>
+        <v>0.06856579121103154</v>
       </c>
       <c r="CC100" t="n">
         <v>0.05957518687435016</v>
@@ -37965,7 +37705,7 @@
         <v>0.01882744054754126</v>
       </c>
       <c r="CJ100" t="n">
-        <v>0.09129748077099567</v>
+        <v>0.0912974807709957</v>
       </c>
       <c r="CK100" t="n">
         <v>0.01561496764524501</v>
@@ -38001,7 +37741,7 @@
         <v>0.01817618090371005</v>
       </c>
       <c r="CV100" t="n">
-        <v>0.08278669334535234</v>
+        <v>0.08278669334535235</v>
       </c>
       <c r="CW100" t="n">
         <v>0.01580750972388531</v>
@@ -38070,7 +37810,7 @@
         <v>0.06088827089712932</v>
       </c>
       <c r="DS100" t="n">
-        <v>0.05258314924107926</v>
+        <v>0.05258314924107925</v>
       </c>
       <c r="DT100" t="n">
         <v>0.4042658338440626</v>
@@ -38090,7 +37830,7 @@
         <v>0.06631277401784408</v>
       </c>
       <c r="E101" t="n">
-        <v>0.05976712215455405</v>
+        <v>0.05976712215455404</v>
       </c>
       <c r="F101" t="n">
         <v>0.07595496854550692</v>
@@ -38159,7 +37899,7 @@
         <v>0.02008422302054496</v>
       </c>
       <c r="AB101" t="n">
-        <v>0.09012648136015386</v>
+        <v>0.09012648136015387</v>
       </c>
       <c r="AC101" t="n">
         <v>0.01820767994291349</v>
@@ -38213,7 +37953,7 @@
         <v>0.05555163275318919</v>
       </c>
       <c r="AT101" t="n">
-        <v>0.07769421791017103</v>
+        <v>0.07769421791017102</v>
       </c>
       <c r="AU101" t="n">
         <v>0.06075616275773723</v>
@@ -38225,7 +37965,7 @@
         <v>0.01591951561861416</v>
       </c>
       <c r="AX101" t="n">
-        <v>0.01764827613349335</v>
+        <v>0.01764827613349336</v>
       </c>
       <c r="AY101" t="n">
         <v>0.07934294747113523</v>
@@ -38258,7 +37998,7 @@
         <v>0.01956740195277552</v>
       </c>
       <c r="BI101" t="n">
-        <v>0.01648000393033355</v>
+        <v>0.01648000393033356</v>
       </c>
       <c r="BJ101" t="n">
         <v>0.0186030449878764</v>
@@ -38309,13 +38049,13 @@
         <v>0.05478506687337206</v>
       </c>
       <c r="BZ101" t="n">
-        <v>0.07622821959961545</v>
+        <v>0.07622821959961547</v>
       </c>
       <c r="CA101" t="n">
         <v>0.01478917663642575</v>
       </c>
       <c r="CB101" t="n">
-        <v>0.06856579121103155</v>
+        <v>0.06856579121103154</v>
       </c>
       <c r="CC101" t="n">
         <v>0.05957518687435016</v>
@@ -38339,7 +38079,7 @@
         <v>0.01882744054754126</v>
       </c>
       <c r="CJ101" t="n">
-        <v>0.09129748077099567</v>
+        <v>0.0912974807709957</v>
       </c>
       <c r="CK101" t="n">
         <v>0.01561496764524501</v>
@@ -38375,7 +38115,7 @@
         <v>0.01817618090371005</v>
       </c>
       <c r="CV101" t="n">
-        <v>0.08278669334535234</v>
+        <v>0.08278669334535235</v>
       </c>
       <c r="CW101" t="n">
         <v>0.01580750972388531</v>
@@ -38444,7 +38184,7 @@
         <v>0.06088827089712932</v>
       </c>
       <c r="DS101" t="n">
-        <v>0.05258314924107926</v>
+        <v>0.05258314924107925</v>
       </c>
       <c r="DT101" t="n">
         <v>0.4005987453650778</v>
